--- a/Results/Hydrogen/hydrogen eutrophication freshwater results.xlsx
+++ b/Results/Hydrogen/hydrogen eutrophication freshwater results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007886762567972359</v>
+        <v>0.007886762567972367</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001723738605140728</v>
+        <v>0.001723738605140723</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00128490858711747</v>
+        <v>0.001284908587117467</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001723738605140728</v>
+        <v>0.001723738605140723</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001723738605140728</v>
+        <v>0.001723738605140723</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002719256064629254</v>
+        <v>0.002719256064629246</v>
       </c>
       <c r="H2" t="n">
-        <v>0.005750835857818357</v>
+        <v>0.005750835857818343</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001723738605140728</v>
+        <v>0.001723738605140723</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00224966363809297</v>
+        <v>0.002249663638092962</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003646867655377436</v>
+        <v>0.003646867655377432</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006352062599644219</v>
+        <v>0.0005325579854737561</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.834195374324885e-05</v>
+        <v>1.834195374324886e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.669533465412943e-05</v>
+        <v>1.669533465412946e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.834195374324885e-05</v>
+        <v>1.834195374324886e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.688156968271487e-05</v>
+        <v>1.688156968271497e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.688156968271487e-05</v>
+        <v>1.688156968271492e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.822170357809669e-05</v>
+        <v>1.822170357809673e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.834195374324885e-05</v>
+        <v>1.834195374324886e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.756986977313894e-05</v>
+        <v>1.756986977313907e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.834195374324885e-05</v>
+        <v>1.834195374324886e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.834195374324885e-05</v>
+        <v>1.834195374324886e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.834195374324885e-05</v>
+        <v>1.834195374324886e-05</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.608743501116582e-05</v>
+        <v>3.042947522643254e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>2.788284662730244e-05</v>
+        <v>2.788284662730246e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>2.804921789430067e-05</v>
+        <v>2.804935789017208e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>2.729562415002179e-05</v>
+        <v>2.729562415002186e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>2.939774277767251e-05</v>
+        <v>2.939774277767258e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>5.596718484601367e-05</v>
+        <v>5.596718484601387e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>5.749208406109823e-05</v>
+        <v>5.749208406109796e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>5.531535104105595e-05</v>
+        <v>2.965739125632259e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.134518346566213e-05</v>
+        <v>3.134518346566151e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.277942513546114e-05</v>
+        <v>3.277942513546106e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>3.16178827009664e-05</v>
+        <v>3.161788270096641e-05</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.659485276609277e-05</v>
+        <v>4.659485276609265e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.582276879598296e-05</v>
+        <v>4.582276879598293e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.658543075554205e-05</v>
+        <v>4.658543075554207e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.578283071980752e-05</v>
+        <v>4.578283071980758e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.578283071980752e-05</v>
+        <v>4.578283071980758e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.647460260094068e-05</v>
+        <v>4.647460260094065e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.659485276609277e-05</v>
+        <v>4.659485276609265e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.582276879598296e-05</v>
+        <v>4.582276879598293e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.659485276609277e-05</v>
+        <v>4.659485276609265e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.659485276609277e-05</v>
+        <v>4.659485276609265e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.659485276609277e-05</v>
+        <v>4.659485276609265e-05</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.818599962300047e-05</v>
+        <v>9.818599962300045e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000152191374320476</v>
+        <v>0.0001521913743204762</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001643407242429706</v>
+        <v>0.0001643407242429707</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001372051017462866</v>
+        <v>0.0001372051017462865</v>
       </c>
       <c r="F6" t="n">
-        <v>9.913256586041873e-05</v>
+        <v>9.913256586041877e-05</v>
       </c>
       <c r="G6" t="n">
         <v>0.0001528587818649073</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001529790320300612</v>
+        <v>0.0001529790320300614</v>
       </c>
       <c r="I6" t="n">
         <v>0.0001522069480599497</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001529898004301131</v>
+        <v>0.0001529898004301129</v>
       </c>
       <c r="K6" t="n">
-        <v>9.716819091547213e-05</v>
+        <v>9.716819091547194e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002102149360970527</v>
+        <v>0.0002102149360970529</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001830756538092868</v>
+        <v>0.000183075653809287</v>
       </c>
       <c r="C7" t="n">
         <v>0.0002296290933397731</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0002304011809044709</v>
+        <v>0.0002304011809044708</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002842416618725177</v>
+        <v>0.0002842416618725175</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000229629025041135</v>
+        <v>0.0002296290250411342</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0002302809271447307</v>
+        <v>0.0002302809271447309</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0002304011773098825</v>
+        <v>0.0002304011773098828</v>
       </c>
       <c r="I7" t="n">
         <v>0.0002296290933397731</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0002304011773098825</v>
+        <v>0.0002304011773098828</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001708098947149725</v>
+        <v>0.0002029805846438746</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002304011773098825</v>
+        <v>0.0002304011773098828</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.0001494314001551542</v>
+        <v>-0.0001494314001551528</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.229272773562897e-05</v>
+        <v>-1.229272773562905e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.533546470963287e-06</v>
+        <v>-2.533546470963295e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.229272773562897e-05</v>
+        <v>-1.229272773562905e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.229272773562897e-05</v>
+        <v>-1.229272773562905e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.211539070330468e-05</v>
+        <v>-3.211539070330456e-05</v>
       </c>
       <c r="H8" t="n">
         <v>-8.433716897656397e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.229272773562897e-05</v>
+        <v>-1.229272773562905e-05</v>
       </c>
       <c r="J8" t="n">
         <v>-2.069590189068642e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.320524458559477e-05</v>
+        <v>-5.320524458559476e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>1.466276707006494e-05</v>
+        <v>1.46627670700649e-05</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-4.680292392576584e-05</v>
+        <v>-4.680292392576595e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>9.231732331439999e-06</v>
+        <v>9.231732331439987e-06</v>
       </c>
       <c r="D9" t="n">
         <v>1.302834611979201e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>9.231732331439999e-06</v>
+        <v>9.231732331439987e-06</v>
       </c>
       <c r="F9" t="n">
-        <v>9.231732331439999e-06</v>
+        <v>9.231732331439987e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>8.993115091907587e-07</v>
+        <v>8.993115091907937e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.018947600647778e-05</v>
+        <v>-2.018947600647784e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>9.231732331439999e-06</v>
+        <v>9.231732331439987e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>5.647327839831951e-06</v>
+        <v>5.647327839831961e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>-7.606530535695613e-06</v>
+        <v>-7.606530535695627e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>2.003865204631931e-05</v>
+        <v>2.00386520463193e-05</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.717984789985854e-05</v>
+        <v>6.717984789985818e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001973528699744923</v>
+        <v>0.0001973528699744918</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002490610083368834</v>
+        <v>0.0002490610083368836</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001973528699744923</v>
+        <v>0.0001973528699744918</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001973528699744923</v>
+        <v>0.0001973528699744918</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002715907265270413</v>
+        <v>0.0002715907265270373</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002767046234951621</v>
+        <v>0.0002767046234951612</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001973528699744923</v>
+        <v>0.0001973528699744918</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001777335177881012</v>
+        <v>0.0001777335177881011</v>
       </c>
       <c r="K2" t="n">
-        <v>9.856656579932631e-05</v>
+        <v>9.856656579932639e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001306102829251023</v>
+        <v>0.000294336747306077</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.334851940876805e-06</v>
+        <v>8.334851940876776e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.651487127978398e-06</v>
+        <v>7.651487127978276e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.334851940876805e-06</v>
+        <v>8.334851940876776e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.709129026630433e-06</v>
+        <v>7.709129026630304e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.709129026630429e-06</v>
+        <v>7.709129026630312e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.245430085608281e-06</v>
+        <v>8.245430085608259e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>8.334851940876805e-06</v>
+        <v>8.334851940876776e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.758723852805799e-06</v>
+        <v>7.758723852805699e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>8.334851940876805e-06</v>
+        <v>8.334851940876776e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>8.334851940876805e-06</v>
+        <v>8.334851940876776e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>8.334851940876805e-06</v>
+        <v>8.334851940876776e-06</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.166894661803012e-05</v>
+        <v>2.166894661802999e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.047313286490511e-05</v>
+        <v>1.047313286490496e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.128919648972012e-05</v>
+        <v>2.184287357290896e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.030377714793375e-05</v>
+        <v>1.030377714793362e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.063265876530078e-05</v>
+        <v>1.063265876530064e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>2.157952476276158e-05</v>
+        <v>1.108408839418339e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.234131040119772e-05</v>
+        <v>2.234131040119761e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.059738216138096e-05</v>
+        <v>1.05973821613808e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.177869143992112e-05</v>
+        <v>2.177869143992103e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.095368000145171e-05</v>
+        <v>1.095368000144922e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.123959256166817e-05</v>
+        <v>1.123959256166813e-05</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.309181731968593e-05</v>
+        <v>2.309181731968581e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.251568923161495e-05</v>
+        <v>2.251568923161477e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.308370470599684e-05</v>
+        <v>2.308370470599668e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.253557346899592e-05</v>
+        <v>2.25355734689958e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.253557346899592e-05</v>
+        <v>2.25355734689958e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.300239546441741e-05</v>
+        <v>2.300239546441736e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.309181731968593e-05</v>
+        <v>2.309181731968581e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.251568923161495e-05</v>
+        <v>2.251568923161477e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.309181731968593e-05</v>
+        <v>2.309181731968581e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.309181731968593e-05</v>
+        <v>2.309181731968581e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.309181731968593e-05</v>
+        <v>2.309181731968581e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.949979862628972e-05</v>
+        <v>5.949979862628951e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>9.32729696083725e-05</v>
+        <v>9.327296960837217e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001009281881776293</v>
+        <v>0.0001009281881776291</v>
       </c>
       <c r="E6" t="n">
-        <v>8.388256124743532e-05</v>
+        <v>8.388256124743498e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>6.002805073113808e-05</v>
+        <v>6.002805073113779e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>9.372367947606159e-05</v>
+        <v>9.372367947606124e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>9.381310133132513e-05</v>
+        <v>9.381310133132491e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>9.323697324325914e-05</v>
+        <v>9.323697324325884e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>9.381984487895444e-05</v>
+        <v>9.381984487895421e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.886241141211547e-05</v>
+        <v>5.886241141211531e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001296562152387085</v>
+        <v>0.0001296562152387081</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.205850820651309e-05</v>
+        <v>7.205850820651286e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>8.98905366574882e-05</v>
+        <v>8.989053665748784e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>9.046667016218235e-05</v>
+        <v>9.046667016218198e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001111331581097231</v>
+        <v>0.0001111331581097229</v>
       </c>
       <c r="F7" t="n">
-        <v>8.989053203791608e-05</v>
+        <v>8.989053203791589e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>9.03772428902908e-05</v>
+        <v>9.037724289029049e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>9.046666474555916e-05</v>
+        <v>9.046666474555898e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.98905366574882e-05</v>
+        <v>8.989053665748784e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>9.046666474555916e-05</v>
+        <v>9.046666474555898e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>7.980090883067057e-05</v>
+        <v>7.980090883067007e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>9.046666474555916e-05</v>
+        <v>9.046666474555898e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.102250446940602e-05</v>
+        <v>1.102250446940598e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>9.316363872305405e-06</v>
+        <v>9.316363872305378e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>6.323673287178226e-06</v>
+        <v>6.323673287178175e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>9.316363872305405e-06</v>
+        <v>9.316363872305378e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>9.316363872305405e-06</v>
+        <v>9.316363872305378e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>5.86910946554319e-06</v>
+        <v>5.869109465543182e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>6.395354181659484e-06</v>
+        <v>6.395354181659455e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>9.316363872305405e-06</v>
+        <v>9.316363872305378e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>8.400178322846767e-06</v>
+        <v>8.400178322846728e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>1.028980032552846e-05</v>
+        <v>1.028980032552843e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>9.718547433832221e-06</v>
+        <v>6.239052801862789e-06</v>
       </c>
     </row>
     <row r="9">
@@ -1194,34 +1194,34 @@
         <v>1.143493457788639e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.165817880881255e-05</v>
+        <v>1.165817880881257e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>9.521278482609501e-06</v>
+        <v>9.521278482609439e-06</v>
       </c>
       <c r="E9" t="n">
-        <v>1.165817880881255e-05</v>
+        <v>1.165817880881257e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.165817880881255e-05</v>
+        <v>1.165817880881257e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>9.322853384531171e-06</v>
+        <v>9.322853384531116e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>9.555445772351523e-06</v>
+        <v>9.555445772351499e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>1.165817880881255e-05</v>
+        <v>1.165817880881257e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>1.036821100440161e-05</v>
+        <v>1.036821100440156e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.113659387027644e-05</v>
+        <v>1.113659387027643e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.090546563724733e-05</v>
+        <v>1.090546563724729e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1307,34 +1307,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001493517404076353</v>
+        <v>0.001493517404076354</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002924338229471381</v>
+        <v>0.002924338229471383</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007844913768527624</v>
+        <v>0.0007844913768527612</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000926963536364057</v>
+        <v>0.0009269635363640596</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000926963536364057</v>
+        <v>0.0009269635363640596</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001430281033238762</v>
+        <v>0.001430281033238761</v>
       </c>
       <c r="H2" t="n">
-        <v>0.002572305310437347</v>
+        <v>0.002572305310437346</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000926963536364057</v>
+        <v>0.0009269635363640596</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001996040031621129</v>
+        <v>0.00199604003162113</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001556290536172602</v>
+        <v>0.001556290536172605</v>
       </c>
       <c r="L2" t="n">
         <v>0.001202877379448047</v>
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.693939410370582e-05</v>
+        <v>1.693939410370624e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.807068225818098e-05</v>
+        <v>1.807068225818025e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.693939410370582e-05</v>
+        <v>1.693939410370624e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.584804505979233e-05</v>
+        <v>1.584804505979234e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.584804505979213e-05</v>
+        <v>1.584804505979234e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.683516470790427e-05</v>
+        <v>1.68351647079038e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.693939410370582e-05</v>
+        <v>1.693939410370624e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.626963068875819e-05</v>
+        <v>1.626963068875824e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.693939410370582e-05</v>
+        <v>1.693939410370624e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.693939410370582e-05</v>
+        <v>1.693939410370624e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.693939410370582e-05</v>
+        <v>1.693939410370624e-05</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.424114226252843e-05</v>
+        <v>2.693948576884185e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>2.977405910935371e-05</v>
+        <v>2.977405910935291e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>2.586968139110217e-05</v>
+        <v>2.586973724087588e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>2.462628698887909e-05</v>
+        <v>2.462628698887857e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>2.601089264802469e-05</v>
+        <v>2.601089264802414e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>4.413691286672665e-05</v>
+        <v>4.41369128667264e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>4.636764544845815e-05</v>
+        <v>4.636764544845739e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>4.35713788475802e-05</v>
+        <v>4.35713788475809e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>4.508213702881486e-05</v>
+        <v>4.5082137028815e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>2.742344291659461e-05</v>
+        <v>2.742344291659438e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>2.680914254104223e-05</v>
+        <v>2.680914254104263e-05</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.878848179971161e-05</v>
+        <v>3.878848179971175e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>3.877993895780361e-05</v>
+        <v>3.877993895780344e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>3.877979048389629e-05</v>
+        <v>3.877979048389631e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>3.810345140476696e-05</v>
+        <v>3.810345140476729e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>3.810345140476696e-05</v>
+        <v>3.810345140476729e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>3.868425240390984e-05</v>
+        <v>3.86842524039093e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>3.878848179971161e-05</v>
+        <v>3.878848179971175e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.811871838476352e-05</v>
+        <v>3.811871838476368e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>3.878848179971161e-05</v>
+        <v>3.878848179971175e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>3.878848179971161e-05</v>
+        <v>3.878848179971175e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>3.878848179971161e-05</v>
+        <v>3.878848179971175e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.273186373968515e-05</v>
+        <v>8.27318637396849e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001276171254508199</v>
+        <v>0.0001276171254509637</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001369283285378414</v>
+        <v>0.0001369283285378405</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001146763009428297</v>
+        <v>0.0001146763009428295</v>
       </c>
       <c r="F6" t="n">
-        <v>8.348107485962228e-05</v>
+        <v>8.34810748596222e-05</v>
       </c>
       <c r="G6" t="n">
         <v>0.0001275161690492079</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001276203984450559</v>
+        <v>0.0001276203984450558</v>
       </c>
       <c r="I6" t="n">
         <v>0.0001269506350300622</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001276292203280403</v>
+        <v>0.0001276292203280402</v>
       </c>
       <c r="K6" t="n">
-        <v>8.189803616176143e-05</v>
+        <v>8.189803616176165e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001745102264628055</v>
+        <v>0.0001745102264628054</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001251274422607801</v>
+        <v>0.0001251274422607805</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001563815102004428</v>
+        <v>0.0001563815102004417</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001563900491426293</v>
+        <v>0.0001563900491426294</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001917966216430445</v>
+        <v>0.0001917966216430443</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001557202460860401</v>
+        <v>0.0001557202460860392</v>
       </c>
       <c r="G7" t="n">
         <v>0.0001562858236465471</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001563900530423506</v>
+        <v>0.0001563900530423495</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001557202896274023</v>
+        <v>0.0001557202896274017</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001563900530423506</v>
+        <v>0.0001563900530423495</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001170248467228332</v>
+        <v>0.0001382763719375911</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001563900530423506</v>
+        <v>0.0001563900530423495</v>
       </c>
     </row>
     <row r="8">
@@ -1547,31 +1547,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.831459982409874e-05</v>
+        <v>-1.831459982409875e-05</v>
       </c>
       <c r="C8" t="n">
         <v>-4.368584895002019e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>3.525704919735425e-06</v>
+        <v>3.525704919735399e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>1.31144387873593e-07</v>
+        <v>1.311443878735917e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>1.31144387873593e-07</v>
+        <v>1.311443878735917e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.338834763065901e-05</v>
+        <v>-1.338834763065902e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.083616858746188e-05</v>
+        <v>-3.083616858746193e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.31144387873593e-07</v>
+        <v>1.311443878735917e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.003307847075893e-05</v>
+        <v>-2.003307847075901e-05</v>
       </c>
       <c r="K8" t="n">
         <v>-1.165028686478478e-05</v>
@@ -1587,13 +1587,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.14772090621044e-06</v>
+        <v>1.147720906210452e-06</v>
       </c>
       <c r="C9" t="n">
-        <v>-5.419340034280511e-06</v>
+        <v>-5.419340034280548e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>1.356298497380828e-05</v>
+        <v>1.35629849738083e-05</v>
       </c>
       <c r="E9" t="n">
         <v>1.200466222939515e-05</v>
@@ -1602,22 +1602,22 @@
         <v>1.200466222939515e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.985384889596771e-06</v>
+        <v>4.985384889596758e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.847040234246517e-07</v>
+        <v>-3.847040234246504e-07</v>
       </c>
       <c r="I9" t="n">
         <v>1.200466222939515e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>5.215180668532285e-06</v>
+        <v>5.215180668532293e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>8.832762117756398e-06</v>
+        <v>8.832762117756405e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>7.385320232997555e-06</v>
+        <v>7.385320232997561e-06</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0005526662888826587</v>
+        <v>0.000552666288882658</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001840147929687068</v>
+        <v>0.001840147929687066</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0005339774925564362</v>
+        <v>0.0005339774925564356</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0004465293216036648</v>
+        <v>0.0004465293216036631</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0004465293216036648</v>
+        <v>0.0004465293216036631</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008014372858603221</v>
+        <v>0.0008014372858603168</v>
       </c>
       <c r="H2" t="n">
         <v>0.001321224625876578</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0004465293216036648</v>
+        <v>0.0004465293216036631</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001133756082091974</v>
+        <v>0.001133756082091973</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0004807281313544864</v>
+        <v>0.0004807281313544855</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003798088182379138</v>
+        <v>0.0003798088182379134</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.363993582201222e-05</v>
+        <v>1.363993582201168e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.436077302470193e-05</v>
+        <v>1.436077302470189e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.363993582201222e-05</v>
+        <v>1.363993582201168e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.288004359369014e-05</v>
+        <v>1.288004359368985e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.288004359369013e-05</v>
+        <v>1.288004359369015e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.354043047817835e-05</v>
+        <v>1.354043047817818e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.363993582201222e-05</v>
+        <v>1.363993582201168e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.299998356961119e-05</v>
+        <v>1.299998356961129e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.363993582201222e-05</v>
+        <v>1.363993582201168e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.363993582201222e-05</v>
+        <v>1.363993582201168e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.363993582201222e-05</v>
+        <v>1.363993582201168e-05</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.356439164358192e-05</v>
+        <v>3.35643916435813e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>2.212244710247988e-05</v>
+        <v>2.212244710247978e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.979608609839624e-05</v>
+        <v>3.442235125347531e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.839680074477895e-05</v>
+        <v>1.839680074477874e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.933003798421626e-05</v>
+        <v>1.933003798421592e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.994478048512443e-05</v>
+        <v>1.994478048512409e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.583005497504986e-05</v>
+        <v>3.583005497504935e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.940433357655722e-05</v>
+        <v>1.940433357655697e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.075986295685695e-05</v>
+        <v>2.075986295685676e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.971549456273392e-05</v>
+        <v>1.971549456273372e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.997260935078791e-05</v>
+        <v>1.997260935078749e-05</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.224287754055481e-05</v>
+        <v>3.224287754055475e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>3.222877243640853e-05</v>
+        <v>3.22287724364085e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>3.223468294858892e-05</v>
+        <v>3.223468294858929e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>3.16562891438034e-05</v>
+        <v>3.165628914380311e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>3.16562891438034e-05</v>
+        <v>3.165628914380311e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>3.214337219672091e-05</v>
+        <v>3.2143372196721e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>3.224287754055481e-05</v>
+        <v>3.224287754055475e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.160292528815384e-05</v>
+        <v>3.160292528815386e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>3.224287754055481e-05</v>
+        <v>3.224287754055475e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>3.224287754055481e-05</v>
+        <v>3.224287754055475e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>3.224287754055481e-05</v>
+        <v>3.224287754055475e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.225372336631929e-05</v>
+        <v>7.225372336631871e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001121673200517687</v>
+        <v>0.0001121673200519499</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001203770732511267</v>
+        <v>0.0001203770732511263</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001006309187290137</v>
+        <v>0.0001006309187290131</v>
       </c>
       <c r="F6" t="n">
-        <v>7.291394478995128e-05</v>
+        <v>7.291394478995102e-05</v>
       </c>
       <c r="G6" t="n">
         <v>0.0001120126602565219</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001121121656004848</v>
+        <v>0.0001121121656004845</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001114722133479548</v>
+        <v>0.0001114722133479544</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001121199989249076</v>
+        <v>0.0001121199989249073</v>
       </c>
       <c r="K6" t="n">
-        <v>7.151333233857149e-05</v>
+        <v>7.151333233857106e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001537476414213726</v>
+        <v>0.0001537476414213718</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.451396957580703e-05</v>
+        <v>9.451396957580679e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001180045781836055</v>
+        <v>0.0001180045781836054</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001180186824437627</v>
+        <v>0.0001180186824437621</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001445026389561789</v>
+        <v>0.0001445026389561786</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001173787049877748</v>
+        <v>0.0001173787049877744</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001179191779439179</v>
+        <v>0.0001179191779439176</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001180186832877518</v>
+        <v>0.0001180186832877514</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001173787310353508</v>
+        <v>0.0001173787310353509</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001180186832877518</v>
+        <v>0.0001180186832877514</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001043999594979731</v>
+        <v>0.000104399959497973</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001180186832877518</v>
+        <v>0.0001180186832877514</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.541852675221968e-06</v>
+        <v>-1.541852675221927e-06</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.577371847095101e-05</v>
+        <v>-2.577371847095097e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>4.809680670359892e-06</v>
+        <v>4.809680670359802e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>7.490077612115349e-06</v>
+        <v>7.490077612115362e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>7.490077612115349e-06</v>
+        <v>7.490077612115362e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.397826585785778e-06</v>
+        <v>-3.397826585785766e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.065040683710802e-05</v>
+        <v>-1.065040683710817e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.490077612115349e-06</v>
+        <v>7.490077612115362e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>-5.264866367166404e-06</v>
+        <v>-5.264866367166456e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>6.351166640739052e-06</v>
+        <v>6.351166640738808e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>7.437807774403778e-06</v>
+        <v>7.437807774403644e-06</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.918660350839035e-06</v>
+        <v>5.918660350838814e-06</v>
       </c>
       <c r="C9" t="n">
-        <v>-5.02150750857481e-07</v>
+        <v>-5.021507508574276e-07</v>
       </c>
       <c r="D9" t="n">
-        <v>1.190551847085676e-05</v>
+        <v>1.190551847085677e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.325754235510499e-05</v>
+        <v>1.325754235510501e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.325754235510499e-05</v>
+        <v>1.325754235510501e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>7.277124044652552e-06</v>
+        <v>7.277124044652406e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>5.634237722712148e-06</v>
+        <v>5.634237722711777e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>1.325754235510499e-05</v>
+        <v>1.325754235510501e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>9.649580472118277e-06</v>
+        <v>9.649580472118193e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2646184026081e-05</v>
+        <v>1.264618402608102e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.164050174067838e-05</v>
+        <v>1.16405017406782e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2099,34 +2099,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.580670305238398e-05</v>
+        <v>8.580670305238404e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001056585280350801</v>
+        <v>0.0010565852803508</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0003690627234170361</v>
+        <v>0.0003690627234170349</v>
       </c>
       <c r="E2" t="n">
-        <v>9.056940660134669e-05</v>
+        <v>9.056940660134499e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>9.056940660134669e-05</v>
+        <v>9.056940660134499e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.000427015570162037</v>
+        <v>0.0004270155701620349</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007102151590743163</v>
+        <v>0.0007102151590743149</v>
       </c>
       <c r="I2" t="n">
-        <v>9.056940660134669e-05</v>
+        <v>9.056940660134499e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0004006841763599401</v>
+        <v>0.0004006841763599389</v>
       </c>
       <c r="K2" t="n">
-        <v>8.249897272421809e-05</v>
+        <v>8.249897272421808e-05</v>
       </c>
       <c r="L2" t="n">
         <v>0.0001411465045492352</v>
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.109951313755936e-05</v>
+        <v>1.109951313755932e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.14417587818545e-05</v>
+        <v>1.144175878185452e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.109951313755936e-05</v>
+        <v>1.109951313755932e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.038709675851468e-05</v>
+        <v>1.038709675851463e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.038709675851468e-05</v>
+        <v>1.038709675851463e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.100046555273751e-05</v>
+        <v>1.100046555273746e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.109951313755936e-05</v>
+        <v>1.109951313755932e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.04623154161899e-05</v>
+        <v>1.046231541618994e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.109951313755936e-05</v>
+        <v>1.109951313755932e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.109951313755936e-05</v>
+        <v>1.109951313755932e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.109951313755936e-05</v>
+        <v>1.109951313755932e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.682111342780175e-05</v>
+        <v>1.516717690159872e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.646388746022645e-05</v>
+        <v>1.64638874602205e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.534892936772132e-05</v>
+        <v>1.534892936771656e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.372523848885958e-05</v>
+        <v>1.372523848885961e-05</v>
       </c>
       <c r="F4" t="n">
         <v>1.449588529678327e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.506812931677694e-05</v>
+        <v>2.672206584297987e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.902296984200972e-05</v>
+        <v>2.90229698420098e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.452997918022935e-05</v>
+        <v>2.618391570643236e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.566400829066288e-05</v>
+        <v>2.763774066062817e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.479339639779958e-05</v>
+        <v>1.479339639779955e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.517608087292389e-05</v>
+        <v>1.517608087292586e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.806213287941103e-05</v>
+        <v>2.806213287941102e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.803874145676713e-05</v>
+        <v>2.803874145676705e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.805397023633595e-05</v>
+        <v>2.805397023633582e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.74971945657012e-05</v>
+        <v>2.749719456570115e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.74971945657012e-05</v>
+        <v>2.749719456570115e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.796308529458925e-05</v>
+        <v>2.796308529458916e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.806213287941103e-05</v>
+        <v>2.806213287941102e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.742493515804176e-05</v>
+        <v>2.742493515804168e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.806213287941103e-05</v>
+        <v>2.806213287941102e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.806213287941103e-05</v>
+        <v>2.806213287941102e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.806213287941103e-05</v>
+        <v>2.806213287941102e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.689622580389626e-05</v>
+        <v>6.689622580389604e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001047697913051806</v>
+        <v>0.0001047697913049728</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001125464406348488</v>
+        <v>0.0001125464406348486</v>
       </c>
       <c r="E6" t="n">
-        <v>9.380376688899461e-05</v>
+        <v>9.380376688899454e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>6.750552406497661e-05</v>
+        <v>6.750552406497654e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001046072320737709</v>
+        <v>0.0001046072320737707</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001047062796587331</v>
+        <v>0.000104706279658733</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001040690819372232</v>
+        <v>0.000104069081937223</v>
       </c>
       <c r="J6" t="n">
         <v>0.0001047137104157147</v>
       </c>
       <c r="K6" t="n">
-        <v>6.619388464197332e-05</v>
+        <v>6.619388464197318e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001442020425335731</v>
+        <v>0.0001442020425335729</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.791924133717767e-05</v>
+        <v>7.791924133717753e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>9.740128148733349e-05</v>
+        <v>9.740128148733339e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>9.742467268450563e-05</v>
+        <v>9.742467268450541e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001192963071450991</v>
+        <v>0.000119296307145099</v>
       </c>
       <c r="F7" t="n">
-        <v>9.67874573543373e-05</v>
+        <v>9.678745735433716e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>9.73256253251557e-05</v>
+        <v>9.73256253251555e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>9.742467290997742e-05</v>
+        <v>9.742467290997722e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>9.678747518860814e-05</v>
+        <v>9.678747518860795e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>9.742467290997742e-05</v>
+        <v>9.742467290997722e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>8.566463207270085e-05</v>
+        <v>7.286385291107957e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>9.742467290997742e-05</v>
+        <v>9.742467290997722e-05</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.286895710624466e-06</v>
+        <v>7.286895710624507e-06</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.065112580803958e-05</v>
+        <v>-1.065112580803956e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>5.645784548414428e-06</v>
+        <v>5.645784548414467e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>1.340215330119984e-05</v>
+        <v>1.340215330119992e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.340215330119984e-05</v>
+        <v>1.340215330119992e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>3.152068940621327e-06</v>
+        <v>3.152068940621382e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>-6.837910539397388e-07</v>
+        <v>-6.83791053939668e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.340215330119984e-05</v>
+        <v>1.340215330119992e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>9.241342402308684e-06</v>
+        <v>9.241342402308792e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>1.276296446128584e-05</v>
+        <v>1.276296446128591e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>1.064235194143958e-05</v>
+        <v>1.06423519414396e-05</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.263613452194691e-06</v>
+        <v>8.263613452194655e-06</v>
       </c>
       <c r="C9" t="n">
-        <v>3.674728272220248e-06</v>
+        <v>3.674728272220228e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>1.043267619358148e-05</v>
+        <v>1.043267619358147e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.414139487607292e-05</v>
+        <v>1.414139487607294e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.414139487607292e-05</v>
+        <v>1.414139487607294e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>8.630851052868009e-06</v>
+        <v>8.630851052868034e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>7.868101100630871e-06</v>
+        <v>7.868101100630888e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>1.414139487607292e-05</v>
+        <v>1.414139487607294e-05</v>
       </c>
       <c r="J9" t="n">
         <v>1.414770746548134e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.339977897440073e-05</v>
+        <v>1.339977897440081e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.190783628544544e-05</v>
+        <v>1.190783628544543e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2495,34 +2495,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.488604145089556e-05</v>
+        <v>4.488604145089552e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>6.465742919179263e-05</v>
+        <v>6.465742919179265e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0004018851405982592</v>
+        <v>0.0004018851405982603</v>
       </c>
       <c r="E2" t="n">
-        <v>8.007503068300611e-05</v>
+        <v>8.007503068300615e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>8.007503068300611e-05</v>
+        <v>8.007503068300615e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008298795636990584</v>
+        <v>0.0008298795636990561</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001989710194278252</v>
+        <v>0.001989710194278257</v>
       </c>
       <c r="I2" t="n">
-        <v>8.007503068300611e-05</v>
+        <v>8.007503068300615e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002044132191766199</v>
+        <v>0.002044132191766197</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008910405209275359</v>
+        <v>0.0008910405209275345</v>
       </c>
       <c r="L2" t="n">
         <v>0.001112486247866451</v>
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.837349270442105e-06</v>
+        <v>9.837349270442108e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>9.127457633658468e-06</v>
+        <v>9.127457633658473e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>9.837349270442105e-06</v>
+        <v>9.837349270442108e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>8.901643950412511e-06</v>
+        <v>8.901643950412475e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>8.901643950412486e-06</v>
+        <v>8.901643950412479e-06</v>
       </c>
       <c r="G3" t="n">
         <v>9.724297015790771e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>9.837349270442105e-06</v>
+        <v>9.837349270442108e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>9.110436095070219e-06</v>
+        <v>9.110436095070207e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>9.837349270442105e-06</v>
+        <v>9.837349270442108e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>9.837349270442105e-06</v>
+        <v>9.837349270442108e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>9.837349270442105e-06</v>
+        <v>9.837349270442108e-06</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.700798204576789e-05</v>
+        <v>1.415910374172885e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.284821807415057e-05</v>
+        <v>1.284821807415053e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.384719156960455e-05</v>
+        <v>1.384719156960469e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.202439717600045e-05</v>
+        <v>1.202439717600044e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.335268050129527e-05</v>
+        <v>1.335268050129524e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.404605148707752e-05</v>
+        <v>1.404605148707751e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.881930607923923e-05</v>
+        <v>2.881930607923921e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>2.62810688703959e-05</v>
+        <v>1.343219056635694e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.775250432368672e-05</v>
+        <v>2.775250432368674e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.483065615087985e-05</v>
+        <v>1.483065615087983e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.447982425232474e-05</v>
+        <v>1.447982425232473e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.863322194401426e-05</v>
+        <v>2.863322194401423e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.856438685456273e-05</v>
+        <v>2.856438685456268e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.86246894071568e-05</v>
+        <v>2.862468940715677e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.799765540860323e-05</v>
+        <v>2.799765540860317e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.799765540860323e-05</v>
+        <v>2.799765540860317e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.852016968936294e-05</v>
+        <v>2.85201696893629e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.863322194401426e-05</v>
+        <v>2.863322194401423e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.790630876864235e-05</v>
+        <v>2.790630876864234e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.863322194401426e-05</v>
+        <v>2.863322194401423e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.863322194401426e-05</v>
+        <v>2.863322194401423e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.863322194401426e-05</v>
+        <v>2.863322194401423e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.014954436148255e-05</v>
+        <v>7.014954436148243e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001109760058526559</v>
+        <v>0.0001109760058526557</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001193966754686254</v>
+        <v>0.0001193966754686251</v>
       </c>
       <c r="E6" t="n">
-        <v>9.914891695651639e-05</v>
+        <v>9.914891695651627e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>7.077516926998541e-05</v>
+        <v>7.077516926998523e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001108257126227952</v>
+        <v>0.0001108257126227951</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001109387648774599</v>
+        <v>0.0001109387648774597</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001102118517020746</v>
+        <v>0.0001102118517020745</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001109467811293701</v>
+        <v>0.0001109467811293699</v>
       </c>
       <c r="K6" t="n">
-        <v>6.939186364913313e-05</v>
+        <v>6.939186364913302e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001535465164467382</v>
+        <v>0.0001535465164467378</v>
       </c>
     </row>
     <row r="7">
@@ -2695,16 +2695,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.819109187134974e-05</v>
+        <v>9.819109187134984e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001236309392289295</v>
+        <v>0.0001236309392289296</v>
       </c>
       <c r="D7" t="n">
         <v>0.0001236997775224396</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001524093083138258</v>
+        <v>0.0001524093083138257</v>
       </c>
       <c r="F7" t="n">
         <v>0.0001229728336245097</v>
@@ -2722,7 +2722,7 @@
         <v>0.000123699774318381</v>
       </c>
       <c r="K7" t="n">
-        <v>9.157978900347657e-05</v>
+        <v>9.157978900347667e-05</v>
       </c>
       <c r="L7" t="n">
         <v>0.000123699774318381</v>
@@ -2735,13 +2735,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.196166291639006e-06</v>
+        <v>9.196166291638997e-06</v>
       </c>
       <c r="C8" t="n">
-        <v>9.994870742411498e-06</v>
+        <v>9.994870742411489e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>4.644187887908978e-06</v>
+        <v>4.644187887908977e-06</v>
       </c>
       <c r="E8" t="n">
         <v>1.289375656658076e-05</v>
@@ -2750,22 +2750,22 @@
         <v>1.289375656658076e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.96021863522597e-06</v>
+        <v>-4.960218635225995e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.666815050414503e-05</v>
+        <v>-2.666815050414508e-05</v>
       </c>
       <c r="I8" t="n">
         <v>1.289375656658076e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.516752957764006e-05</v>
+        <v>-2.516752957764005e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.53320864029093e-06</v>
+        <v>-2.533208640291102e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>-8.906522630709405e-06</v>
+        <v>-8.90652263070942e-06</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.581330294689225e-06</v>
+        <v>9.581330294689218e-06</v>
       </c>
       <c r="C9" t="n">
-        <v>1.038798678154148e-05</v>
+        <v>1.038798678154147e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>9.636233938751684e-06</v>
+        <v>9.636233938751678e-06</v>
       </c>
       <c r="E9" t="n">
-        <v>1.345936734419824e-05</v>
+        <v>1.345936734419826e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.345936734419824e-05</v>
+        <v>1.345936734419826e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>5.578654252742994e-06</v>
+        <v>5.578654252742992e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.080114475783106e-06</v>
+        <v>-3.080114475783121e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>1.345936734419824e-05</v>
+        <v>1.345936734419826e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>8.409439203240858e-07</v>
+        <v>8.40943920324098e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>9.046409019730008e-06</v>
+        <v>9.04640901972986e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>3.810551452290245e-06</v>
+        <v>3.810551452290226e-06</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.242629805913575e-05</v>
+        <v>4.242629805913573e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>6.3648764021394e-05</v>
+        <v>6.364876402139405e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>7.816799584446071e-05</v>
+        <v>7.816799584446066e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>7.147146719400678e-05</v>
+        <v>7.147146719400731e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>7.147146719400678e-05</v>
+        <v>7.147146719400731e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001106994204780363</v>
+        <v>0.0001106994204780368</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001613708002425069</v>
+        <v>0.000161370800242507</v>
       </c>
       <c r="I2" t="n">
-        <v>7.147146719400678e-05</v>
+        <v>7.147146719400731e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0005393588531035166</v>
+        <v>0.0005393588531035167</v>
       </c>
       <c r="K2" t="n">
-        <v>5.938448522400895e-05</v>
+        <v>5.938448522400905e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000179712198009314</v>
+        <v>0.0001797121980093141</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.384536544944528e-06</v>
+        <v>8.384536544944543e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>8.23646583797161e-06</v>
+        <v>8.236465837971596e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.384536544944528e-06</v>
+        <v>8.384536544944543e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>8.157893919842588e-06</v>
+        <v>8.157893919842847e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>8.157893919842835e-06</v>
+        <v>8.157893919842847e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.295997780204819e-06</v>
+        <v>8.295997780204828e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>8.384536544944528e-06</v>
+        <v>8.384536544944543e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.813692539055628e-06</v>
+        <v>7.813692539055858e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>8.384536544944528e-06</v>
+        <v>8.384536544944543e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>8.384536544944528e-06</v>
+        <v>8.384536544944543e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>8.384536544944528e-06</v>
+        <v>8.384536544944543e-06</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.06986713090896e-05</v>
+        <v>1.069867130908953e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.051660267520215e-05</v>
+        <v>1.05166026752022e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>2.055832298194936e-05</v>
+        <v>1.069776166772178e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>9.91960695565864e-06</v>
+        <v>9.919606955658816e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>1.015807964063256e-05</v>
+        <v>1.015807964063274e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.06101325443499e-05</v>
+        <v>1.981638634832332e-05</v>
       </c>
       <c r="H4" t="n">
         <v>2.143873324520663e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.012782730320087e-05</v>
+        <v>1.933408110717435e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.111363874808803e-05</v>
+        <v>1.111363874808802e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.068237353304663e-05</v>
+        <v>1.06823735330466e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.073965016353541e-05</v>
+        <v>1.073965016353539e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.351252422654261e-05</v>
+        <v>2.351252422654254e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.347579423339505e-05</v>
+        <v>2.347579423339498e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.350445047179578e-05</v>
+        <v>2.350445047179571e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.307601119519326e-05</v>
+        <v>2.307601119519345e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.307601119519326e-05</v>
+        <v>2.307601119519345e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.342398546180295e-05</v>
+        <v>2.342398546180286e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.351252422654261e-05</v>
+        <v>2.351252422654254e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.294168022065374e-05</v>
+        <v>2.294168022065384e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.351252422654261e-05</v>
+        <v>2.351252422654254e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.351252422654261e-05</v>
+        <v>2.351252422654254e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.351252422654261e-05</v>
+        <v>2.351252422654254e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.050999025028808e-05</v>
+        <v>6.050999025028815e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>9.557001297519477e-05</v>
+        <v>9.557001297519489e-05</v>
       </c>
       <c r="D6" t="n">
         <v>0.0001027086511858812</v>
       </c>
       <c r="E6" t="n">
-        <v>8.545944167149263e-05</v>
+        <v>8.545944167149267e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>6.113199932462821e-05</v>
+        <v>6.113199932462829e-05</v>
       </c>
       <c r="G6" t="n">
         <v>9.537273590932074e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>9.546127467411524e-05</v>
+        <v>9.546127467411521e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>9.48904306681715e-05</v>
+        <v>9.489043066817172e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>9.546814360432478e-05</v>
+        <v>9.546814360432476e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.986075219801001e-05</v>
+        <v>5.986075219800999e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001319708138349821</v>
+        <v>0.0001319708138349819</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.21138484323842e-05</v>
+        <v>7.211384843238426e-05</v>
       </c>
       <c r="C7" t="n">
         <v>9.049889277947954e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>9.053562519907032e-05</v>
+        <v>9.053562519907029e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001112231116610932</v>
+        <v>0.0001112231116610935</v>
       </c>
       <c r="F7" t="n">
-        <v>8.996477374024036e-05</v>
+        <v>8.996477374024038e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>9.044708400788731e-05</v>
+        <v>9.044708400788733e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>9.053562277262699e-05</v>
+        <v>9.053562277262702e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.996477876673824e-05</v>
+        <v>8.996477876673825e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>9.053562277262699e-05</v>
+        <v>9.053562277262702e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>7.986197539258564e-05</v>
+        <v>6.733931997433118e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>9.053562277262699e-05</v>
+        <v>9.053562277262702e-05</v>
       </c>
     </row>
     <row r="8">
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.147139626645095e-06</v>
+        <v>8.147139626645104e-06</v>
       </c>
       <c r="C8" t="n">
-        <v>8.638623041448201e-06</v>
+        <v>8.638623041448192e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>1.036156578322374e-05</v>
+        <v>1.036156578322373e-05</v>
       </c>
       <c r="E8" t="n">
         <v>1.143647752318735e-05</v>
@@ -3146,7 +3146,7 @@
         <v>1.143647752318735e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.602708949150867e-06</v>
+        <v>8.602708949150924e-06</v>
       </c>
       <c r="H8" t="n">
         <v>8.750327940326888e-06</v>
@@ -3155,13 +3155,13 @@
         <v>1.143647752318735e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>3.457333982136694e-06</v>
+        <v>3.457333982136706e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>1.138330987765739e-05</v>
+        <v>1.13833098776577e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>7.590048111066759e-06</v>
+        <v>7.590048111066766e-06</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.538658100091758e-06</v>
+        <v>8.538658100091752e-06</v>
       </c>
       <c r="C9" t="n">
-        <v>9.084671292744858e-06</v>
+        <v>9.084671292744868e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>1.100374108295631e-05</v>
+        <v>1.100374108295632e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.196651774854834e-05</v>
+        <v>1.196651774854836e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.196651774854834e-05</v>
+        <v>1.196651774854836e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>9.696443655477409e-06</v>
+        <v>9.696443655477475e-06</v>
       </c>
       <c r="H9" t="n">
         <v>1.035013480018333e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.196651774854834e-05</v>
+        <v>1.196651774854836e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>1.033263171224547e-05</v>
+        <v>1.033263171224548e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.174246830437892e-05</v>
+        <v>1.174246830437934e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>9.394344108206666e-06</v>
+        <v>9.39434410820668e-06</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.170949703456706e-05</v>
+        <v>4.1709497034567e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>6.564560715821161e-05</v>
+        <v>6.564560715821162e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>7.588601361327209e-05</v>
+        <v>7.588601361327199e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>6.663111812640839e-05</v>
+        <v>6.663111812640797e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>6.663111812640839e-05</v>
+        <v>6.663111812640797e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>7.120098169542848e-05</v>
+        <v>7.120098169542761e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>8.78636736206549e-05</v>
+        <v>8.786367362065479e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>6.663111812640839e-05</v>
+        <v>6.663111812640797e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>8.10478011626809e-05</v>
+        <v>8.104780116268095e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>5.848691758886732e-05</v>
+        <v>5.848691758886718e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>7.486548857938453e-05</v>
+        <v>7.486548857938447e-05</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.408881705338228e-06</v>
+        <v>8.408881705338213e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>8.306435898245093e-06</v>
+        <v>8.306435898245094e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.408881705338228e-06</v>
+        <v>8.408881705338213e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>8.123566143127707e-06</v>
+        <v>8.123566143127667e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>8.123566143127701e-06</v>
+        <v>8.123566143127667e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.321380838247471e-06</v>
+        <v>8.32138083824887e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>8.408881705338228e-06</v>
+        <v>8.408881705338213e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.844850864155542e-06</v>
+        <v>7.84485086415707e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>8.408881705338228e-06</v>
+        <v>8.408881705338213e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>8.408881705338228e-06</v>
+        <v>8.408881705338213e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>8.408881705338228e-06</v>
+        <v>8.408881705338213e-06</v>
       </c>
     </row>
     <row r="4">
@@ -3367,34 +3367,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.975337388189953e-05</v>
+        <v>1.975337388189956e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.041226337359201e-05</v>
+        <v>1.0412263373592e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.057337240111271e-05</v>
+        <v>1.057337240111272e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>9.807059477730666e-06</v>
+        <v>9.807059477730656e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>9.997386805844898e-06</v>
+        <v>9.997386805844886e-06</v>
       </c>
       <c r="G4" t="n">
         <v>1.966587301480876e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.138318543600242e-05</v>
+        <v>2.138318543600235e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>9.967851066869288e-06</v>
+        <v>9.967851066869268e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>2.036389300647255e-05</v>
+        <v>2.036389300647234e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.056506196927123e-05</v>
+        <v>1.056506196927122e-05</v>
       </c>
       <c r="L4" t="n">
         <v>1.054191449098957e-05</v>
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.313647412253272e-05</v>
+        <v>2.313647412253267e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.310110661808778e-05</v>
+        <v>2.310110661808772e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.312839945099953e-05</v>
+        <v>2.312839945099949e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.268750861498316e-05</v>
+        <v>2.268750861498309e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.268750861498316e-05</v>
+        <v>2.268750861498309e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.304897325544192e-05</v>
+        <v>2.304897325544187e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.313647412253272e-05</v>
+        <v>2.313647412253267e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.257244328135003e-05</v>
+        <v>2.257244328134998e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.313647412253272e-05</v>
+        <v>2.313647412253267e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.313647412253272e-05</v>
+        <v>2.313647412253267e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.313647412253272e-05</v>
+        <v>2.313647412253267e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.991987578609608e-05</v>
+        <v>5.99198757860961e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>9.455327574655278e-05</v>
+        <v>9.455327574655274e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001016240919801445</v>
+        <v>0.0001016240919801444</v>
       </c>
       <c r="E6" t="n">
-        <v>8.456207647664619e-05</v>
+        <v>8.456207647664606e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>6.052422431836462e-05</v>
+        <v>6.052422431836452e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>9.43741326325178e-05</v>
+        <v>9.437413263251768e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>9.446163349968261e-05</v>
+        <v>9.446163349968251e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>9.389760265842583e-05</v>
+        <v>9.389760265842578e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>9.446842194500108e-05</v>
+        <v>9.446842194500096e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.92782449027795e-05</v>
+        <v>5.927824490277949e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001305433877666281</v>
+        <v>0.000130543387766628</v>
       </c>
     </row>
     <row r="7">
@@ -3493,28 +3493,28 @@
         <v>8.444203159510621e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>8.447740123165098e-05</v>
+        <v>8.447740123165096e-05</v>
       </c>
       <c r="E7" t="n">
         <v>0.0001036435429506323</v>
       </c>
       <c r="F7" t="n">
-        <v>8.391336416411819e-05</v>
+        <v>8.391336416411829e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>8.438989823246045e-05</v>
+        <v>8.438989823246042e-05</v>
       </c>
       <c r="H7" t="n">
         <v>8.447739909955124e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.391336825836851e-05</v>
+        <v>8.391336825836854e-05</v>
       </c>
       <c r="J7" t="n">
         <v>8.447739909955124e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>7.457102859202694e-05</v>
+        <v>7.416911454038399e-05</v>
       </c>
       <c r="L7" t="n">
         <v>8.447739909955124e-05</v>
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.454334262968742e-06</v>
+        <v>8.454334262968722e-06</v>
       </c>
       <c r="C8" t="n">
-        <v>8.413286332023262e-06</v>
+        <v>8.413286332023254e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>1.01665640306862e-05</v>
+        <v>1.016656403068618e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.121422514896353e-05</v>
+        <v>1.121422514896351e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.121422514896353e-05</v>
+        <v>1.121422514896351e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>9.27253234919483e-06</v>
+        <v>9.272532349194825e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>1.00813508758272e-05</v>
+        <v>1.008135087582718e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.121422514896353e-05</v>
+        <v>1.121422514896351e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.333351312220011e-05</v>
+        <v>1.333351312220007e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.108120669521145e-05</v>
+        <v>1.108120669521147e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>9.522001445174534e-06</v>
+        <v>9.522001445174514e-06</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.830560679853706e-06</v>
+        <v>8.830560679853696e-06</v>
       </c>
       <c r="C9" t="n">
-        <v>8.889379638252908e-06</v>
+        <v>8.889379638252896e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>1.07791770905497e-05</v>
+        <v>1.077917709054967e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.167994529404964e-05</v>
+        <v>1.167994529404962e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.167994529404964e-05</v>
+        <v>1.167994529404962e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>9.815363788981073e-06</v>
+        <v>9.815363788981071e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>1.07456408720184e-05</v>
+        <v>1.074564087201838e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.167994529404964e-05</v>
+        <v>1.167994529404962e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>1.39233854491665e-05</v>
+        <v>1.392338544916648e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.143202489780494e-05</v>
+        <v>1.143202489780499e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.001771722433202e-05</v>
+        <v>1.0017717224332e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.206577201481727e-05</v>
+        <v>4.206577201481813e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>6.249337621558348e-05</v>
+        <v>6.249337621558359e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001209003134259538</v>
+        <v>0.0001209003134259545</v>
       </c>
       <c r="E2" t="n">
-        <v>7.646237682789559e-05</v>
+        <v>7.646237682789606e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>7.646237682789559e-05</v>
+        <v>7.646237682789606e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002868394912550196</v>
+        <v>0.000286839491255016</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001641971716401322</v>
+        <v>0.001641971716401323</v>
       </c>
       <c r="I2" t="n">
-        <v>7.646237682789559e-05</v>
+        <v>7.646237682789606e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>7.273090013936874e-05</v>
+        <v>7.273090013936939e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>6.173354071636903e-05</v>
+        <v>6.173354071636963e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008951274145840716</v>
+        <v>0.000895127414584071</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.758641130132718e-06</v>
+        <v>8.758641130132877e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>8.452798056970309e-06</v>
+        <v>8.452798056970307e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.758641130132718e-06</v>
+        <v>8.758641130132877e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>8.357090327189337e-06</v>
+        <v>8.357090327189433e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>8.357090327189333e-06</v>
+        <v>8.357090327189435e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.663944417741248e-06</v>
+        <v>8.663944417741398e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>8.758641130132718e-06</v>
+        <v>8.758641130132877e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>8.14839121905638e-06</v>
+        <v>8.148391219056495e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>8.758641130132718e-06</v>
+        <v>8.758641130132877e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>8.758641130132718e-06</v>
+        <v>8.758641130132877e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>8.758641130132718e-06</v>
+        <v>8.758641130132877e-06</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.209192599281038e-05</v>
+        <v>1.123684487920267e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.079152798402914e-05</v>
+        <v>1.079152798402918e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.111206838568656e-05</v>
+        <v>1.111206838568608e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.018629367405896e-05</v>
+        <v>1.018629367405906e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.063122640564932e-05</v>
+        <v>1.063122640564941e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>2.199722928041879e-05</v>
+        <v>2.199722928041894e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.385781247096628e-05</v>
+        <v>2.385781247096668e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.062659496812554e-05</v>
+        <v>2.148167608173431e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.277631423414225e-05</v>
+        <v>2.277631423414185e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.101157146511314e-05</v>
+        <v>1.101157146511388e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.149287874907643e-05</v>
+        <v>1.14928787490767e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.530065490494626e-05</v>
+        <v>2.530065490494581e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.525635781853841e-05</v>
+        <v>2.52563578185384e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.529213318252331e-05</v>
+        <v>2.529213318252393e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.481233750126745e-05</v>
+        <v>2.481233750126748e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.481233750126745e-05</v>
+        <v>2.481233750126748e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.520595819255472e-05</v>
+        <v>2.520595819255506e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.530065490494626e-05</v>
+        <v>2.530065490494581e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.469040499387008e-05</v>
+        <v>2.469040499387004e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.530065490494626e-05</v>
+        <v>2.530065490494581e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.530065490494626e-05</v>
+        <v>2.530065490494581e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.530065490494626e-05</v>
+        <v>2.530065490494581e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.49773366949068e-05</v>
+        <v>6.497733669490683e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001028264007099778</v>
+        <v>0.0001028264007099777</v>
       </c>
       <c r="D6" t="n">
         <v>0.0001105654946712359</v>
       </c>
       <c r="E6" t="n">
-        <v>9.191724101985878e-05</v>
+        <v>9.191724101985907e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>6.564180012034844e-05</v>
+        <v>6.564180012034866e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001026412948890557</v>
+        <v>0.0001026412948890563</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001027359916014566</v>
+        <v>0.0001027359916014572</v>
       </c>
       <c r="I6" t="n">
-        <v>0.000102125741690371</v>
+        <v>0.0001021257416903714</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001027434122607914</v>
+        <v>0.0001027434122607912</v>
       </c>
       <c r="K6" t="n">
-        <v>6.427595029460496e-05</v>
+        <v>6.427595029460573e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001421780639802952</v>
+        <v>0.0001421780639802962</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.485050932649168e-05</v>
+        <v>8.485050932649239e-05</v>
       </c>
       <c r="C7" t="n">
         <v>0.0001067368392955384</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001067811249744174</v>
+        <v>0.0001067811249744176</v>
       </c>
       <c r="E7" t="n">
         <v>0.000131478323926355</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001061708617908388</v>
+        <v>0.000106170861790839</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001066864396695547</v>
+        <v>0.0001066864396695552</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001067811363819463</v>
+        <v>0.0001067811363819462</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00010617088647087</v>
+        <v>0.0001061708864708704</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001067811363819463</v>
+        <v>0.0001067811363819462</v>
       </c>
       <c r="K7" t="n">
-        <v>9.355891388515432e-05</v>
+        <v>9.407444013987104e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001067811363819463</v>
+        <v>0.0001067811363819462</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.48942698023742e-06</v>
+        <v>8.489426980237547e-06</v>
       </c>
       <c r="C8" t="n">
-        <v>9.082308957527451e-06</v>
+        <v>9.08230895752746e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>9.876147962468529e-06</v>
+        <v>9.876147962468436e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>1.160351971524695e-05</v>
+        <v>1.160351971524696e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.160351971524695e-05</v>
+        <v>1.160351971524696e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>5.28719646686402e-06</v>
+        <v>5.28719646686423e-06</v>
       </c>
       <c r="H8" t="n">
         <v>-2.084060329792335e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.160351971524695e-05</v>
+        <v>1.160351971524696e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.447509925473364e-05</v>
+        <v>1.447509925473382e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.177614177881251e-05</v>
+        <v>1.177614177881263e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.91556308733535e-06</v>
+        <v>-5.91556308733517e-06</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.845475791233049e-06</v>
+        <v>8.845475791232939e-06</v>
       </c>
       <c r="C9" t="n">
-        <v>9.463900065925749e-06</v>
+        <v>9.463900065925746e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>1.104208810115435e-05</v>
+        <v>1.104208810115461e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.21473759503749e-05</v>
+        <v>1.214737595037491e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.21473759503749e-05</v>
+        <v>1.214737595037491e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>8.637659412456827e-06</v>
+        <v>8.637659412456956e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.438105086129547e-06</v>
+        <v>-1.438105086129491e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>1.21473759503749e-05</v>
+        <v>1.214737595037491e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>1.488924159382147e-05</v>
+        <v>1.488924159382163e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.212076032437457e-05</v>
+        <v>1.212076032437475e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.247354906380082e-06</v>
+        <v>4.247354906380177e-06</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.275446545046744e-05</v>
+        <v>4.275446545046725e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>6.478184777399787e-05</v>
+        <v>6.478184777399779e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>7.633969726299387e-05</v>
+        <v>7.633969726299379e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>7.263516237281882e-05</v>
+        <v>7.263516237281815e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>7.263516237281882e-05</v>
+        <v>7.263516237281815e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>7.150708273396145e-05</v>
+        <v>7.150708273395939e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>8.967227876164013e-05</v>
+        <v>8.967227876163967e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>7.263516237281882e-05</v>
+        <v>7.263516237281815e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>8.231240820507443e-05</v>
+        <v>8.23124082050743e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>6.091754624970604e-05</v>
+        <v>6.091754624970526e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>7.285576828711289e-05</v>
+        <v>7.285576828711251e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.21933664649079e-06</v>
+        <v>8.219336646490663e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>8.108231156662152e-06</v>
+        <v>8.10823115666213e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.21933664649079e-06</v>
+        <v>8.219336646490663e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>8.147208670730111e-06</v>
+        <v>8.147208670730103e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>8.147208670730109e-06</v>
+        <v>8.147208670730104e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.132456939982609e-06</v>
+        <v>8.132456939982428e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>8.21933664649079e-06</v>
+        <v>8.219336646490663e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.659014803274138e-06</v>
+        <v>7.659014803274077e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>8.21933664649079e-06</v>
+        <v>8.219336646490663e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>8.21933664649079e-06</v>
+        <v>8.219336646490663e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>8.21933664649079e-06</v>
+        <v>8.219336646490663e-06</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.950091279287856e-05</v>
+        <v>1.038255428845853e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.025884062545069e-05</v>
+        <v>1.025884062545075e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.042268103125691e-05</v>
+        <v>1.042266885391731e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>9.705273735329589e-06</v>
+        <v>9.705273735329579e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>9.865986649219233e-06</v>
+        <v>9.865986649219224e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.029567458195034e-05</v>
+        <v>1.02956745819503e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.095699622042976e-05</v>
+        <v>2.095699622042962e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>9.822232445241906e-06</v>
+        <v>1.894059094966182e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.063198181937499e-05</v>
+        <v>2.009027210122338e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.042196394172254e-05</v>
+        <v>1.042196394172248e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.039035630542613e-05</v>
+        <v>1.039035630542605e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.270303745590713e-05</v>
+        <v>2.270303745590701e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.266837405259819e-05</v>
+        <v>2.266837405259821e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.26949667812252e-05</v>
+        <v>2.269496678122513e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.231142153777003e-05</v>
+        <v>2.231142153777009e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.231142153777003e-05</v>
+        <v>2.231142153777009e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.261615774939888e-05</v>
+        <v>2.26161577493988e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.270303745590713e-05</v>
+        <v>2.270303745590701e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.214271561269039e-05</v>
+        <v>2.214271561269042e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.270303745590713e-05</v>
+        <v>2.270303745590701e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.270303745590713e-05</v>
+        <v>2.270303745590701e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.270303745590713e-05</v>
+        <v>2.270303745590701e-05</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.913340439749119e-05</v>
+        <v>5.913340439749087e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>9.33654679656689e-05</v>
+        <v>9.336546796566874e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001002904671242648</v>
+        <v>0.0001002904671242644</v>
       </c>
       <c r="E6" t="n">
-        <v>8.349584005451804e-05</v>
+        <v>8.349584005451805e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>5.975909355775125e-05</v>
+        <v>5.975909355775101e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>9.31350993878771e-05</v>
+        <v>9.313509938787646e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>9.322197909442422e-05</v>
+        <v>9.322197909442398e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>9.266165725116869e-05</v>
+        <v>9.266165725116846e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>9.322867847686701e-05</v>
+        <v>9.322867847686677e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.850019162136422e-05</v>
+        <v>5.850019162136394e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001288303458063738</v>
+        <v>0.0001288303458063734</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.077474739463817e-05</v>
+        <v>7.0774747394638e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>8.879672791608331e-05</v>
+        <v>8.87967279160831e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>8.883139329964576e-05</v>
+        <v>8.88313932996455e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001091080507129414</v>
+        <v>0.0001091080507129411</v>
       </c>
       <c r="F7" t="n">
-        <v>8.827106565225008e-05</v>
+        <v>8.827106565224995e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>8.87445116128839e-05</v>
+        <v>8.87445116128836e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>8.883139131939215e-05</v>
+        <v>8.883139131939184e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.827106947617527e-05</v>
+        <v>8.827106947617517e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>8.883139131939215e-05</v>
+        <v>8.883139131939184e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>6.609485300538826e-05</v>
+        <v>7.836930174839685e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>8.883139131939215e-05</v>
+        <v>8.883139131939184e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.021045601403531e-05</v>
+        <v>1.021045601403529e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.475244155910024e-06</v>
+        <v>8.475244155910028e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>9.983262884756875e-06</v>
+        <v>9.983262884756856e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>1.099118639784655e-05</v>
+        <v>1.099118639784656e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.099118639784655e-05</v>
+        <v>1.099118639784656e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>9.396303646650185e-06</v>
+        <v>9.396303646650139e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>9.870447061872621e-06</v>
+        <v>9.870447061872597e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>1.099118639784655e-05</v>
+        <v>1.099118639784656e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.305718758011008e-05</v>
+        <v>1.305718758011002e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.120462770066051e-05</v>
+        <v>1.120462770066053e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>9.444062009579386e-06</v>
+        <v>9.444062009579371e-06</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.057458301984712e-05</v>
+        <v>1.057458301984703e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>8.939420908046032e-06</v>
+        <v>8.939420908046034e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>1.060684046011685e-05</v>
+        <v>1.060684046011682e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.154583738684085e-05</v>
+        <v>1.154583738684084e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.154583738684085e-05</v>
+        <v>1.154583738684084e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>9.94304919942439e-06</v>
+        <v>9.943049199424345e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>1.056209968145314e-05</v>
+        <v>1.056209968145312e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.154583738684085e-05</v>
+        <v>1.154583738684084e-05</v>
       </c>
       <c r="J9" t="n">
         <v>1.366994813148861e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.158929780206406e-05</v>
+        <v>1.158929780206399e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>9.918051158321927e-06</v>
+        <v>9.918051158321869e-06</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.124780401014419e-05</v>
+        <v>4.124780401014429e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>6.505364350951339e-05</v>
+        <v>6.505364350951311e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3866155087026e-05</v>
+        <v>7.386615508702616e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>6.743636250185768e-05</v>
+        <v>6.743636250185749e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>6.743636250185768e-05</v>
+        <v>6.743636250185749e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>7.045924925553209e-05</v>
+        <v>7.045924925553156e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>8.806745098806621e-05</v>
+        <v>8.806745098806643e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>6.743636250185768e-05</v>
+        <v>6.743636250185749e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>8.289557606563371e-05</v>
+        <v>8.289557606563393e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>5.9334417181586e-05</v>
+        <v>5.933441718158613e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>7.356322383212371e-05</v>
+        <v>7.35632238321238e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.348576811218427e-06</v>
+        <v>8.348576811218501e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>8.282875548254269e-06</v>
+        <v>8.282875548254064e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.348576811218427e-06</v>
+        <v>8.348576811218501e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>8.132768829225879e-06</v>
+        <v>8.132768829225821e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>8.132768829225852e-06</v>
+        <v>8.132768829225821e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.261063131443384e-06</v>
+        <v>8.261063131443415e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>8.348576811218427e-06</v>
+        <v>8.348576811218501e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.784426986966762e-06</v>
+        <v>7.784426986966718e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>8.348576811218427e-06</v>
+        <v>8.348576811218503e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>8.348576811218427e-06</v>
+        <v>8.348576811218501e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>8.348576811218427e-06</v>
+        <v>8.348576811218501e-06</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.977484128461581e-05</v>
+        <v>1.056217446711286e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.044884985329112e-05</v>
+        <v>1.044884985329109e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.060278824804405e-05</v>
+        <v>1.060278824804411e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>9.846192567298635e-06</v>
+        <v>9.84619256729853e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>1.003257235838465e-05</v>
+        <v>1.00325723583843e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.968732760484065e-05</v>
+        <v>1.968732760484073e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.137201614508199e-05</v>
+        <v>2.137201614508208e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>9.998024642861177e-06</v>
+        <v>1.921069146036403e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.039043499273447e-05</v>
+        <v>1.081666058731321e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.060271776147423e-05</v>
+        <v>1.060271776147425e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.057251079618734e-05</v>
+        <v>1.057251079618566e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.261385007300734e-05</v>
+        <v>2.261385007300737e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.257851165847221e-05</v>
+        <v>2.257851165847219e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.260577611710753e-05</v>
+        <v>2.260577611710754e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.218521310677646e-05</v>
+        <v>2.218521310677634e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.218521310677646e-05</v>
+        <v>2.218521310677634e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.252633639323219e-05</v>
+        <v>2.252633639323228e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.261385007300734e-05</v>
+        <v>2.261385007300737e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.204970024875566e-05</v>
+        <v>2.204970024875596e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.261385007300734e-05</v>
+        <v>2.261385007300737e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.261385007300734e-05</v>
+        <v>2.261385007300737e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.261385007300734e-05</v>
+        <v>2.261385007300737e-05</v>
       </c>
     </row>
     <row r="6">
@@ -4635,34 +4635,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.889182917449825e-05</v>
+        <v>5.889182917449839e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>9.287545853542745e-05</v>
+        <v>9.287545853542765e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>9.978805890121371e-05</v>
+        <v>9.978805890121382e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>8.3065076620945e-05</v>
+        <v>8.306507662094528e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>5.94870430146216e-05</v>
+        <v>5.94870430146218e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>9.267685375427938e-05</v>
+        <v>9.26768537542794e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>9.276436743412178e-05</v>
+        <v>9.276436743412198e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>9.220021760980281e-05</v>
+        <v>9.220021760980311e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>9.27710243580183e-05</v>
+        <v>9.277102435801865e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.82626293861803e-05</v>
+        <v>5.826262938618041e-05</v>
       </c>
       <c r="L6" t="n">
         <v>0.0001281470660215938</v>
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.69004842334294e-05</v>
+        <v>6.690048423342942e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>8.382312083306714e-05</v>
+        <v>8.382312083306695e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>8.385846121902878e-05</v>
+        <v>8.385846121902868e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001028634501466551</v>
+        <v>0.0001028634501466552</v>
       </c>
       <c r="F7" t="n">
-        <v>8.329430569685304e-05</v>
+        <v>8.329430569685278e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>8.377094556782724e-05</v>
+        <v>8.37709455678271e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>8.385845924760228e-05</v>
+        <v>8.385845924760224e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.329430942335058e-05</v>
+        <v>8.329430942335054e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>8.385845924760228e-05</v>
+        <v>8.385845924760224e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>7.36343090588656e-05</v>
+        <v>7.363430905886561e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>8.385845924760228e-05</v>
+        <v>8.385845924760224e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4715,34 +4715,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.65200180129564e-05</v>
+        <v>1.652001801295638e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.41802013432184e-06</v>
+        <v>8.418020134321807e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>9.866364562813628e-06</v>
+        <v>9.866364562813623e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>1.089760441776238e-05</v>
+        <v>1.08976044177624e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.089760441776238e-05</v>
+        <v>1.08976044177624e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>9.847035344292349e-06</v>
+        <v>9.847035344292333e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>9.727528148513256e-06</v>
+        <v>9.727528148513252e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>1.089760441776238e-05</v>
+        <v>1.08976044177624e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.284269620227351e-05</v>
+        <v>1.284269620227356e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.091110552719502e-05</v>
+        <v>1.091110552719484e-05</v>
       </c>
       <c r="L8" t="n">
         <v>9.253386596663507e-06</v>
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.67645202185162e-05</v>
+        <v>1.676452021851618e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>8.885652528729002e-06</v>
+        <v>8.885652528728929e-06</v>
       </c>
       <c r="D9" t="n">
         <v>1.045592654977794e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.138021696879517e-05</v>
+        <v>1.138021696879519e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.138021696879517e-05</v>
+        <v>1.138021696879519e-05</v>
       </c>
       <c r="G9" t="n">
         <v>1.037140564315364e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.040055628454539e-05</v>
+        <v>1.04005562845454e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.138021696879517e-05</v>
+        <v>1.138021696879519e-05</v>
       </c>
       <c r="J9" t="n">
         <v>1.346564639927498e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.127715880900678e-05</v>
+        <v>1.12771588090066e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>9.738100204243378e-06</v>
+        <v>9.738100204243382e-06</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.006194423608248007</v>
+        <v>0.006194423608248001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0009544972708599504</v>
+        <v>0.0009544972708599526</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001175349319702008</v>
+        <v>0.001175349319702009</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0009544972708599504</v>
+        <v>0.0009544972708599526</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0009544972708599504</v>
+        <v>0.0009544972708599526</v>
       </c>
       <c r="G2" t="n">
         <v>0.002528567394018125</v>
       </c>
       <c r="H2" t="n">
-        <v>0.005056133404127902</v>
+        <v>0.005056133404127914</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0009544972708599504</v>
+        <v>0.0009544972708599526</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001450248346737336</v>
+        <v>0.001450248346737335</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002802366654982227</v>
+        <v>0.002802366654982233</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001026263837836189</v>
+        <v>0.001026263837836188</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.559090208655869e-05</v>
+        <v>1.559090208655884e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.333573116882378e-05</v>
+        <v>1.33357311688237e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.559090208655869e-05</v>
+        <v>1.559090208655884e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.353025544688375e-05</v>
+        <v>1.353025544688371e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.353025544688375e-05</v>
+        <v>1.353025544688371e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.544846136615302e-05</v>
+        <v>1.544846136615303e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.559090208655869e-05</v>
+        <v>1.559090208655884e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.467722758855825e-05</v>
+        <v>1.467722758855828e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.559090208655869e-05</v>
+        <v>1.559090208655884e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.559090208655869e-05</v>
+        <v>1.559090208655884e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.559090208655869e-05</v>
+        <v>1.559090208655884e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.922336112399364e-05</v>
+        <v>4.922336112399373e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>2.161559410584785e-05</v>
+        <v>2.161559410584772e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>2.336999516871648e-05</v>
+        <v>2.336999516871617e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>2.117680543101068e-05</v>
+        <v>2.117680543101061e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>2.386646249800777e-05</v>
+        <v>2.386646249800763e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>2.509725439879632e-05</v>
+        <v>4.908092040358791e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.624984841458536e-05</v>
+        <v>5.067642970303349e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>4.830968662599335e-05</v>
+        <v>4.830968662599325e-05</v>
       </c>
       <c r="J4" t="n">
         <v>4.954659261899382e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>2.661310441011246e-05</v>
+        <v>2.661310441011245e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>2.640658967834735e-05</v>
+        <v>2.640658967834728e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.108471258310925e-05</v>
+        <v>4.10847125831094e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.017103808510894e-05</v>
+        <v>4.017103808510886e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.107594197629007e-05</v>
+        <v>4.107594197629013e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.010987406325718e-05</v>
+        <v>4.010987406325705e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.010987406325718e-05</v>
+        <v>4.010987406325705e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.094227186270352e-05</v>
+        <v>4.09422718627036e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.108471258310925e-05</v>
+        <v>4.10847125831094e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.017103808510894e-05</v>
+        <v>4.017103808510886e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.108471258310925e-05</v>
+        <v>4.10847125831094e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.108471258310925e-05</v>
+        <v>4.10847125831094e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.108471258310925e-05</v>
+        <v>4.10847125831094e-05</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.910466119877659e-05</v>
+        <v>8.910466119877669e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001386193694382788</v>
+        <v>0.0001386193694382791</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001500350131706848</v>
+        <v>0.0001500350131706851</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000124819022048858</v>
+        <v>0.0001248190220488582</v>
       </c>
       <c r="F6" t="n">
-        <v>8.975942308716809e-05</v>
+        <v>8.975942308716816e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001394281360928571</v>
+        <v>0.0001394281360928572</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001395705768132598</v>
+        <v>0.0001395705768132604</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001386569023152621</v>
+        <v>0.0001386569023152623</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001395804948099818</v>
+        <v>0.0001395804948099821</v>
       </c>
       <c r="K6" t="n">
-        <v>8.816723090725994e-05</v>
+        <v>8.816723090726024e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001922864455620158</v>
+        <v>0.0001922864455620163</v>
       </c>
     </row>
     <row r="7">
@@ -5071,13 +5071,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001502318306838186</v>
+        <v>0.0001502318306838188</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001881886422634707</v>
+        <v>0.0001881886422634703</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001891023290225816</v>
+        <v>0.0001891023290225818</v>
       </c>
       <c r="E7" t="n">
         <v>0.0002330442912571235</v>
@@ -5086,22 +5086,22 @@
         <v>0.0001881885791943402</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001889598760410654</v>
+        <v>0.0001889598760410659</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001891023167614711</v>
+        <v>0.0001891023167614712</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001881886422634707</v>
+        <v>0.0001881886422634703</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001891023167614711</v>
+        <v>0.0001891023167614712</v>
       </c>
       <c r="K7" t="n">
         <v>0.0001665806096289135</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001891023167614711</v>
+        <v>0.0001891023167614712</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.0001241207734610626</v>
+        <v>-0.0001241207734610627</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.789016859152202e-07</v>
+        <v>-4.789016859150711e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.85453000167824e-06</v>
+        <v>-3.854530001678296e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.789016859152202e-07</v>
+        <v>-4.789016859150711e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.789016859152202e-07</v>
+        <v>-4.789016859150711e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.408940717584051e-05</v>
+        <v>-3.408940717584041e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>-8.001853105691649e-05</v>
+        <v>-8.001853105691663e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.789016859152202e-07</v>
+        <v>-4.789016859150711e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>-8.213923240934557e-06</v>
+        <v>-8.21392324093447e-06</v>
       </c>
       <c r="K8" t="n">
         <v>-4.14428492554261e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>-9.029268479857842e-05</v>
+        <v>2.082552201313255e-06</v>
       </c>
     </row>
     <row r="9">
@@ -5154,34 +5154,34 @@
         <v>-3.747140597202306e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.235855414738427e-05</v>
+        <v>1.235855414738431e-05</v>
       </c>
       <c r="D9" t="n">
         <v>1.151296878589578e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.235855414738427e-05</v>
+        <v>1.235855414738431e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.235855414738427e-05</v>
+        <v>1.235855414738431e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>-9.469839207503163e-07</v>
+        <v>-9.469839207503256e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.941345121338117e-05</v>
+        <v>-1.941345121338119e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.235855414738427e-05</v>
+        <v>1.235855414738431e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>9.748413739871724e-06</v>
+        <v>9.748413739871772e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.793832615442253e-06</v>
+        <v>-3.793832615442294e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.360804517985076e-05</v>
+        <v>1.394560336206025e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004798763319961989</v>
+        <v>0.004798763319961984</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001367762792828117</v>
+        <v>0.001367762792828118</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001079454390991912</v>
+        <v>0.001079454390991902</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001367762792828117</v>
+        <v>0.001367762792828118</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001367762792828117</v>
+        <v>0.001367762792828118</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002349697532139537</v>
+        <v>0.002349697532139539</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004276609023968242</v>
+        <v>0.004276609023968245</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001367762792828117</v>
+        <v>0.001367762792828118</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001232297110567383</v>
+        <v>0.001232297110567382</v>
       </c>
       <c r="K2" t="n">
         <v>0.002519212619587677</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005173810077377494</v>
+        <v>0.001335846319911896</v>
       </c>
     </row>
     <row r="3">
@@ -5307,10 +5307,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.745227404168355e-05</v>
+        <v>1.745227404168354e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.589391528115496e-05</v>
+        <v>1.589391528115497e-05</v>
       </c>
       <c r="D3" t="n">
         <v>1.745227404168355e-05</v>
@@ -5319,16 +5319,16 @@
         <v>1.606890039462939e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.606890039462941e-05</v>
+        <v>1.606890039462939e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.732900467438983e-05</v>
+        <v>1.732900467438981e-05</v>
       </c>
       <c r="H3" t="n">
         <v>1.745227404168355e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.666111390466096e-05</v>
+        <v>1.666111390466095e-05</v>
       </c>
       <c r="J3" t="n">
         <v>1.745227404168355e-05</v>
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.739174412530629e-05</v>
+        <v>5.011192633619093e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>2.515554676654535e-05</v>
+        <v>2.515554676654524e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>2.555484986407382e-05</v>
+        <v>2.555484986407233e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>2.466877030787453e-05</v>
+        <v>2.466877030787454e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>2.654480873899892e-05</v>
+        <v>2.654480873899886e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>2.726847475801258e-05</v>
+        <v>4.99886569688972e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>5.143002899212622e-05</v>
+        <v>5.14300289921261e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>2.660058398828366e-05</v>
+        <v>4.932076619916849e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.813525288045254e-05</v>
+        <v>5.042251108729147e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>2.872361968985705e-05</v>
+        <v>2.87236196898569e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>2.851042121134924e-05</v>
+        <v>2.85104212113493e-05</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.154134131544753e-05</v>
+        <v>4.154134131544751e-05</v>
       </c>
       <c r="C5" t="n">
         <v>4.075018117842492e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.153309238102981e-05</v>
+        <v>4.153309238102979e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.073512470760102e-05</v>
+        <v>4.073512470760105e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.073512470760102e-05</v>
+        <v>4.073512470760105e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.141807194815382e-05</v>
+        <v>4.141807194815376e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.154134131544753e-05</v>
+        <v>4.154134131544752e-05</v>
       </c>
       <c r="I5" t="n">
         <v>4.075018117842492e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.154134131544753e-05</v>
+        <v>4.154134131544752e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.154134131544753e-05</v>
+        <v>4.154134131544752e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.154134131544753e-05</v>
+        <v>4.154134131544752e-05</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.617887070495941e-05</v>
+        <v>8.617887070495924e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000132671980235912</v>
+        <v>0.0001326719802360631</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001432614680352888</v>
+        <v>0.0001432614680352886</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001197388212617745</v>
+        <v>0.0001197388212617744</v>
       </c>
       <c r="F6" t="n">
-        <v>8.688232054367667e-05</v>
+        <v>8.688232054367655e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001333345919672366</v>
+        <v>0.0001333345919672364</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001334578613345251</v>
+        <v>0.0001334578613345248</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001326667011975078</v>
+        <v>0.0001326667011975077</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001334671530071567</v>
+        <v>0.0001334671530071563</v>
       </c>
       <c r="K6" t="n">
-        <v>8.530063918132694e-05</v>
+        <v>8.53006391813268e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001828447204484158</v>
+        <v>0.0001828447204484153</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001356672141740511</v>
+        <v>0.000135667214174051</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001691406410840505</v>
+        <v>0.00016914064108405</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001699318156544138</v>
+        <v>0.0001699318156544137</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002086811991450567</v>
+        <v>0.0002086811991450562</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001691405915542982</v>
+        <v>0.0001691405915542978</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001698085318537793</v>
+        <v>0.0001698085318537791</v>
       </c>
       <c r="H7" t="n">
-        <v>0.000169931801221073</v>
+        <v>0.0001699318012210726</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001691406410840505</v>
+        <v>0.00016914064108405</v>
       </c>
       <c r="J7" t="n">
-        <v>0.000169931801221073</v>
+        <v>0.0001699318012210726</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001267865661809451</v>
+        <v>0.0001267865661809448</v>
       </c>
       <c r="L7" t="n">
-        <v>0.000169931801221073</v>
+        <v>0.0001699318012210726</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-9.606308793512161e-05</v>
+        <v>-9.606308793512133e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.120156336257551e-05</v>
+        <v>-1.120156336257545e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.85601786368023e-06</v>
+        <v>-2.856017863679775e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.120156336257551e-05</v>
+        <v>-1.120156336257545e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.120156336257551e-05</v>
+        <v>-1.120156336257545e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.360240596678844e-05</v>
+        <v>-3.360240596678845e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>-6.935469907145463e-05</v>
+        <v>-6.935469907145471e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.120156336257551e-05</v>
+        <v>-1.120156336257545e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.46650057440329e-06</v>
+        <v>-4.466500574403272e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.226867607152805e-05</v>
+        <v>-4.226867607152813e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>-8.438645212512765e-05</v>
+        <v>-5.585959638166942e-06</v>
       </c>
     </row>
     <row r="9">
@@ -5547,13 +5547,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-2.551677267356152e-05</v>
+        <v>-2.551677267356136e-05</v>
       </c>
       <c r="C9" t="n">
         <v>9.282398132282894e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>1.244657019165645e-05</v>
+        <v>1.244657019165664e-05</v>
       </c>
       <c r="E9" t="n">
         <v>9.282398132282894e-06</v>
@@ -5562,22 +5562,22 @@
         <v>9.282398132282894e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.671920110117566e-07</v>
+        <v>-1.671920110117829e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.455231044135075e-05</v>
+        <v>-1.455231044135074e-05</v>
       </c>
       <c r="I9" t="n">
         <v>9.282398132282894e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>1.180054657945695e-05</v>
+        <v>1.180054657945696e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.603178843386694e-06</v>
+        <v>-3.603178843386741e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>1.135558218840482e-05</v>
+        <v>1.135558218840481e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003958922778925938</v>
+        <v>0.00395892277892593</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002420548167498275</v>
+        <v>0.002420548167498273</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001010667293359242</v>
+        <v>0.00101066729335924</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002420548167498275</v>
+        <v>0.002420548167498273</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002420548167498275</v>
+        <v>0.002420548167498273</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00214936515232421</v>
+        <v>0.002149365152324204</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003605045249973444</v>
+        <v>0.003605045249973458</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002420548167498275</v>
+        <v>0.002420548167498273</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001373248913517365</v>
+        <v>0.001373248913517361</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002317845473557135</v>
+        <v>0.002317845473557131</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004819047504247925</v>
+        <v>0.004819047504247927</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.186872921843173e-05</v>
+        <v>2.186872921843167e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>2.191271635567959e-05</v>
+        <v>2.191271635567945e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>2.186872921843173e-05</v>
+        <v>2.186872921843167e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>2.203793145559563e-05</v>
+        <v>2.203793145559557e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.203793145559563e-05</v>
+        <v>2.203793145559556e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>2.179494914667287e-05</v>
+        <v>2.179494914667283e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>2.186872921843173e-05</v>
+        <v>2.186872921843167e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>2.139347464051582e-05</v>
+        <v>2.139347464051572e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.186872921843173e-05</v>
+        <v>2.186872921843167e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.186872921843173e-05</v>
+        <v>2.186872921843167e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.186872921843173e-05</v>
+        <v>2.186872921843167e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.372689893949739e-05</v>
+        <v>3.372689893949754e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>3.438511640858985e-05</v>
+        <v>3.438511640858974e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>5.615353886619004e-05</v>
+        <v>5.615353886618951e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>3.373143564014469e-05</v>
+        <v>3.373143564014454e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>3.39240803229292e-05</v>
+        <v>3.392408032292913e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.365311886773872e-05</v>
+        <v>3.365311886773874e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>5.737557483277998e-05</v>
+        <v>5.737557483277972e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>5.565390639966393e-05</v>
+        <v>5.565390639966362e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>5.638968635126291e-05</v>
+        <v>3.472579901643815e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.486087266466957e-05</v>
+        <v>3.486087266466959e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>3.486528069432255e-05</v>
+        <v>3.486528069432251e-05</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.653538181150098e-05</v>
+        <v>4.653538181150105e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.60601272335853e-05</v>
+        <v>4.606012723358505e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.652696503126046e-05</v>
+        <v>4.652696503126034e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.615676524360252e-05</v>
+        <v>4.615676524360243e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.615676524360252e-05</v>
+        <v>4.615676524360243e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.646160173974233e-05</v>
+        <v>4.646160173974218e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.653538181150098e-05</v>
+        <v>4.653538181150102e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.60601272335853e-05</v>
+        <v>4.606012723358505e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.653538181150098e-05</v>
+        <v>4.653538181150102e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.653538181150098e-05</v>
+        <v>4.653538181150102e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.653538181150098e-05</v>
+        <v>4.653538181150102e-05</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.055218609867423e-05</v>
+        <v>9.055218609867419e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001374890219296868</v>
+        <v>0.0001374890219296866</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001476598878193916</v>
+        <v>0.0001476598878193914</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001245387692162511</v>
+        <v>0.0001245387692162508</v>
       </c>
       <c r="F6" t="n">
-        <v>9.163893190642637e-05</v>
+        <v>9.163893190642614e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001377781895127956</v>
+        <v>0.0001377781895127952</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001378519695845538</v>
+        <v>0.0001378519695845534</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001373767150066385</v>
+        <v>0.0001373767150066382</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001378612653419537</v>
+        <v>0.0001378612653419534</v>
       </c>
       <c r="K6" t="n">
-        <v>8.967356833719676e-05</v>
+        <v>8.967356833719663e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001872605485740247</v>
+        <v>0.0001872605485740239</v>
       </c>
     </row>
     <row r="7">
@@ -5866,31 +5866,31 @@
         <v>0.0001350052143024038</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001674110614994613</v>
+        <v>0.0001674110614994612</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001678863239477571</v>
+        <v>0.0001678863239477569</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002053551175414268</v>
+        <v>0.0002053551175414265</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001674110252361522</v>
+        <v>0.000167411025236152</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001678125360056186</v>
+        <v>0.0001678125360056187</v>
       </c>
       <c r="H7" t="n">
         <v>0.0001678863160773772</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001674110614994613</v>
+        <v>0.0001674110614994612</v>
       </c>
       <c r="J7" t="n">
         <v>0.0001678863160773772</v>
       </c>
       <c r="K7" t="n">
-        <v>0.000148834879885193</v>
+        <v>0.0001488348798851929</v>
       </c>
       <c r="L7" t="n">
         <v>0.0001678863160773772</v>
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-7.692330573557159e-05</v>
+        <v>-7.692330573557143e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>-3.503505474845094e-05</v>
+        <v>-3.503505474845091e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.782283342474375e-07</v>
+        <v>-3.782283342474218e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.503505474845094e-05</v>
+        <v>-3.503505474845091e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.503505474845094e-05</v>
+        <v>-3.503505474845091e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.825737936376462e-05</v>
+        <v>-2.82573793637648e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>-5.667127404785101e-05</v>
+        <v>-5.667127404785102e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.503505474845094e-05</v>
+        <v>-3.503505474845091e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>-6.247846772104578e-06</v>
+        <v>-6.247846772104481e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.898366279952353e-05</v>
+        <v>-3.898366279952334e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>-7.701486676359474e-05</v>
+        <v>-7.701486676359455e-05</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.693430530680449e-05</v>
+        <v>-1.693430530680434e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.316738283069477e-06</v>
+        <v>2.316738283069429e-06</v>
       </c>
       <c r="D9" t="n">
         <v>1.424268392594112e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.316738283069477e-06</v>
+        <v>2.316738283069429e-06</v>
       </c>
       <c r="F9" t="n">
-        <v>2.316738283069477e-06</v>
+        <v>2.316738283069429e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>2.937567065407213e-06</v>
+        <v>2.937567065407169e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>-8.610026505162798e-06</v>
+        <v>-8.610026505162777e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>2.316738283069477e-06</v>
+        <v>2.316738283069429e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>1.186316655483537e-05</v>
+        <v>1.18631665548354e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.478360420660703e-06</v>
+        <v>-1.478360420660658e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.689455174898541e-05</v>
+        <v>-1.68945517489853e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0006056877093879674</v>
+        <v>0.0006056877093879689</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002407477064330086</v>
+        <v>0.0002407477064330083</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0004183231040152459</v>
+        <v>0.0004183231040152456</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002407477064330086</v>
+        <v>0.0002407477064330083</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002407477064330086</v>
+        <v>0.0002407477064330083</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0006653874257805863</v>
+        <v>0.0006653874257805857</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001454432271098965</v>
+        <v>0.001454432271098964</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002407477064330086</v>
+        <v>0.0002407477064330083</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008080067291811159</v>
+        <v>0.0008080067291811149</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0005121877297782632</v>
+        <v>0.0005121877297782627</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001252382756515167</v>
+        <v>0.001788191881699813</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.167070376294086e-06</v>
+        <v>9.167070376293997e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>8.096971182419087e-06</v>
+        <v>8.096971182418963e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>9.167070376294086e-06</v>
+        <v>9.167070376293997e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>8.175783005326376e-06</v>
+        <v>8.1757830053266e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>8.175783005326376e-06</v>
+        <v>8.175783005326596e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>9.064377007194062e-06</v>
+        <v>9.064377007194032e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>9.167070376294086e-06</v>
+        <v>9.167070376293997e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>8.50628868040525e-06</v>
+        <v>8.506288680405104e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>9.167070376294086e-06</v>
+        <v>9.167070376293997e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>9.167070376294086e-06</v>
+        <v>9.167070376293997e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>9.167070376294086e-06</v>
+        <v>9.167070376293997e-06</v>
       </c>
     </row>
     <row r="4">
@@ -6142,34 +6142,34 @@
         <v>1.337164248224768e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.196376537109009e-05</v>
+        <v>1.196376537109e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.324448073926824e-05</v>
+        <v>2.691031765637149e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.173839165488917e-05</v>
+        <v>1.173839165488899e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.265696782998481e-05</v>
+        <v>1.265696782998466e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>2.665520393942747e-05</v>
+        <v>1.326894911314767e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.764006984959704e-05</v>
+        <v>2.76400698495969e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>2.609711561263873e-05</v>
+        <v>1.27108607863588e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.688878904168845e-05</v>
+        <v>2.688878904168833e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.341816816433395e-05</v>
+        <v>1.341816816433394e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.386122336083331e-05</v>
+        <v>1.386122336083323e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.630514631111024e-05</v>
+        <v>2.630514631111025e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.564436461522112e-05</v>
+        <v>2.564436461522145e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.629643806049817e-05</v>
+        <v>2.629643806049826e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.564736768175923e-05</v>
+        <v>2.56473676817592e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.564736768175923e-05</v>
+        <v>2.56473676817592e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.620245294201032e-05</v>
+        <v>2.620245294201033e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.630514631111024e-05</v>
+        <v>2.630514631111025e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.564436461522112e-05</v>
+        <v>2.564436461522145e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.630514631111024e-05</v>
+        <v>2.630514631111025e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.630514631111024e-05</v>
+        <v>2.630514631111025e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.630514631111024e-05</v>
+        <v>2.630514631111025e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.675067592279885e-05</v>
+        <v>6.67506759227989e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001048259511993866</v>
+        <v>0.0001048259511993007</v>
       </c>
       <c r="D6" t="n">
         <v>0.0001134929929893224</v>
       </c>
       <c r="E6" t="n">
-        <v>9.423321636443333e-05</v>
+        <v>9.423321636443359e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>6.732407344088195e-05</v>
+        <v>6.732407344088198e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001053625763867454</v>
+        <v>0.0001053625763867455</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001054652697558444</v>
+        <v>0.0001054652697558446</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001048044880599562</v>
+        <v>0.0001048044880599565</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001054728782836744</v>
+        <v>0.0001054728782836746</v>
       </c>
       <c r="K6" t="n">
-        <v>6.603153246628888e-05</v>
+        <v>6.603153246628889e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001459059002767318</v>
+        <v>0.000145905900276732</v>
       </c>
     </row>
     <row r="7">
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.640417345904209e-05</v>
+        <v>9.640417345904198e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001207948806286028</v>
+        <v>0.0001207948806286025</v>
       </c>
       <c r="D7" t="n">
         <v>0.0001214556634295073</v>
@@ -6274,19 +6274,19 @@
         <v>0.0001207948580051659</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001213529689553916</v>
+        <v>0.0001213529689553917</v>
       </c>
       <c r="H7" t="n">
         <v>0.0001214556623244916</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001207948806286028</v>
+        <v>0.0001207948806286025</v>
       </c>
       <c r="J7" t="n">
         <v>0.0001214556623244916</v>
       </c>
       <c r="K7" t="n">
-        <v>8.991136588159173e-05</v>
+        <v>0.0001069407317558629</v>
       </c>
       <c r="L7" t="n">
         <v>0.0001214556623244916</v>
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-3.197427714136667e-07</v>
+        <v>-3.197427714136883e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>9.486442805966318e-06</v>
+        <v>9.486442805966345e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>3.963968348671872e-06</v>
+        <v>3.963968348671868e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>9.486442805966318e-06</v>
+        <v>9.486442805966345e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>9.486442805966318e-06</v>
+        <v>9.486442805966345e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.709443088349325e-06</v>
+        <v>-1.709443088349337e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.861838591977241e-05</v>
+        <v>-1.861838591977246e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>9.486442805966318e-06</v>
+        <v>9.486442805966345e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.477269338977745e-06</v>
+        <v>-3.477269338977749e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>1.709197756986945e-06</v>
+        <v>1.70919775698695e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.247555332760935e-05</v>
+        <v>1.148204585277309e-05</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.691196262515093e-06</v>
+        <v>7.691196262515051e-06</v>
       </c>
       <c r="C9" t="n">
         <v>1.221041437879543e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>9.436175128011774e-06</v>
+        <v>9.436175128011758e-06</v>
       </c>
       <c r="E9" t="n">
-        <v>1.221041437879543e-05</v>
+        <v>1.221041437879544e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.221041437879543e-05</v>
+        <v>1.221041437879544e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>7.077402893185944e-06</v>
+        <v>7.07740289318593e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>2.680844364562195e-07</v>
+        <v>2.68084436456189e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>1.221041437879543e-05</v>
+        <v>1.221041437879544e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>6.411594800135801e-06</v>
+        <v>6.411594800135762e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>8.518189495398201e-06</v>
+        <v>8.518189495398147e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>1.249942126697208e-05</v>
+        <v>-1.30555012861877e-06</v>
       </c>
     </row>
   </sheetData>
@@ -6461,7 +6461,7 @@
         <v>0.0001371580050817831</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001423610220240774</v>
+        <v>0.0001423610220240773</v>
       </c>
       <c r="E2" t="n">
         <v>0.0001371580050817831</v>
@@ -6470,22 +6470,22 @@
         <v>0.0001371580050817831</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001699555984351164</v>
+        <v>0.0001699555984351115</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001642166508622435</v>
+        <v>0.0001642166508622436</v>
       </c>
       <c r="I2" t="n">
         <v>0.0001371580050817831</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002496475261902106</v>
+        <v>0.0002496475261902105</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001141664179590863</v>
+        <v>0.0001141664179590864</v>
       </c>
       <c r="L2" t="n">
-        <v>6.828165478231906e-05</v>
+        <v>6.828165478231897e-05</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.661044615340653e-06</v>
+        <v>7.661044615340675e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.009158382974515e-06</v>
+        <v>7.009158382974494e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.661044615340653e-06</v>
+        <v>7.661044615340675e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.058895386165311e-06</v>
+        <v>7.058895386165313e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.058895386165314e-06</v>
+        <v>7.058895386165326e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.572989604558708e-06</v>
+        <v>7.572989604558646e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.661044615340653e-06</v>
+        <v>7.661044615340675e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.09350596284748e-06</v>
+        <v>7.093505962847453e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.661044615340653e-06</v>
+        <v>7.661044615340675e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.661044615340653e-06</v>
+        <v>7.661044615340675e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.661044615340653e-06</v>
+        <v>7.661044615340675e-06</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.034055784390286e-05</v>
+        <v>2.012651801282909e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>9.669266837254803e-06</v>
+        <v>9.669266837254793e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.036042406840813e-05</v>
+        <v>1.036042243419489e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>9.510268585125198e-06</v>
+        <v>9.510268585125168e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>9.789672149331475e-06</v>
+        <v>9.789672149331462e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.025250283312085e-05</v>
+        <v>1.025250283312086e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.069193157887831e-05</v>
+        <v>1.036380990058047e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>9.773019191409642e-06</v>
+        <v>9.773019191409607e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.065202638829639e-05</v>
+        <v>2.014799286193982e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.030974712624929e-05</v>
+        <v>1.030974712624933e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.035863180247005e-05</v>
+        <v>1.035863180247004e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.148054516808569e-05</v>
+        <v>2.148054516808567e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.091300651559254e-05</v>
+        <v>2.09130065155925e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.147244654831124e-05</v>
+        <v>2.147244654831115e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.093090459511336e-05</v>
+        <v>2.093090459511334e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.093090459511336e-05</v>
+        <v>2.093090459511334e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.139249015730375e-05</v>
+        <v>2.139249015730374e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.148054516808569e-05</v>
+        <v>2.148054516808567e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.091300651559254e-05</v>
+        <v>2.09130065155925e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.148054516808569e-05</v>
+        <v>2.148054516808567e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.148054516808569e-05</v>
+        <v>2.148054516808567e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.148054516808569e-05</v>
+        <v>2.148054516808567e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.712661590851932e-05</v>
+        <v>5.712661590851922e-05</v>
       </c>
       <c r="C6" t="n">
         <v>8.963094714202192e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>9.701530984760793e-05</v>
+        <v>9.701530984760773e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>8.058954478147125e-05</v>
+        <v>8.058954478147121e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>5.762184043205795e-05</v>
+        <v>5.762184043205784e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>9.007660182722987e-05</v>
+        <v>9.007660182722985e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>9.016465683801228e-05</v>
+        <v>9.016465683801216e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>8.959711818551871e-05</v>
+        <v>8.959711818551863e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>9.017114976035856e-05</v>
+        <v>9.017114976035847e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.651291733652931e-05</v>
+        <v>5.651291733652928e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001246756531853628</v>
+        <v>0.0001246756531853626</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.226311886891976e-05</v>
+        <v>7.22631188689196e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>9.026157801865113e-05</v>
+        <v>9.02615780186511e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>9.082912044637227e-05</v>
+        <v>9.082912044637203e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001116863450272444</v>
+        <v>0.0001116863450272442</v>
       </c>
       <c r="F7" t="n">
-        <v>9.026157465444928e-05</v>
+        <v>9.026157465444921e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>9.074106166036246e-05</v>
+        <v>9.074106166036238e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>9.082911667114432e-05</v>
+        <v>9.082911667114413e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>9.026157801865113e-05</v>
+        <v>9.02615780186511e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>9.082911667114432e-05</v>
+        <v>9.082911667114413e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>7.963547244844735e-05</v>
+        <v>7.963547244844714e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>9.082911667114432e-05</v>
+        <v>9.082911667114413e-05</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.000234094472941e-05</v>
+        <v>1.000234094472938e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.000566898101561e-05</v>
+        <v>1.00056689810156e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.495165314728318e-06</v>
+        <v>8.495165314728323e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>1.000566898101561e-05</v>
+        <v>1.00056689810156e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.000566898101561e-05</v>
+        <v>1.00056689810156e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.692404080009304e-06</v>
+        <v>7.692404080009301e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>8.321869643322187e-06</v>
+        <v>8.321869643322192e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>1.000566898101561e-05</v>
+        <v>1.00056689810156e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>5.836114528818369e-06</v>
+        <v>5.836114528818349e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>9.055294967628943e-06</v>
+        <v>9.055294967628931e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>8.768898789065663e-06</v>
+        <v>8.768898789065659e-06</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.057050409697331e-05</v>
+        <v>1.057050409697327e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.140365527189755e-05</v>
+        <v>1.140365527189754e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>9.956710927005031e-06</v>
+        <v>9.956710927005012e-06</v>
       </c>
       <c r="E9" t="n">
-        <v>1.140365527189755e-05</v>
+        <v>1.140365527189754e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.140365527189755e-05</v>
+        <v>1.140365527189754e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>9.620271551608164e-06</v>
+        <v>9.620271551608158e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>9.888666905446858e-06</v>
+        <v>9.888666905446826e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>1.140365527189755e-05</v>
+        <v>1.140365527189754e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>8.875643624068871e-06</v>
+        <v>8.875643624068847e-06</v>
       </c>
       <c r="K9" t="n">
         <v>1.018488781107695e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.075895469201306e-05</v>
+        <v>1.006991324968875e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.997170021913443e-05</v>
+        <v>8.997170021913441e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001790933508991227</v>
+        <v>0.0001790933508991229</v>
       </c>
       <c r="D2" t="n">
-        <v>9.129510400319966e-05</v>
+        <v>9.129510400319986e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001790933508991227</v>
+        <v>0.0001790933508991229</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001790933508991227</v>
+        <v>0.0001790933508991229</v>
       </c>
       <c r="G2" t="n">
-        <v>0.000144524177987894</v>
+        <v>0.0001445241779878967</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001579335231640556</v>
+        <v>0.000157933523164056</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001790933508991227</v>
+        <v>0.0001790933508991229</v>
       </c>
       <c r="J2" t="n">
         <v>0.0001100678600251333</v>
       </c>
       <c r="K2" t="n">
-        <v>9.239215959291068e-05</v>
+        <v>9.239215959291085e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001323052397383751</v>
+        <v>0.0002858860778776771</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.859170173851404e-06</v>
+        <v>7.85917017385136e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.281813580110717e-06</v>
+        <v>7.281813580110761e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.859170173851404e-06</v>
+        <v>7.859170173851361e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.332353398679725e-06</v>
+        <v>7.332353398679785e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.332353398679724e-06</v>
+        <v>7.332353398679742e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.773819652881612e-06</v>
+        <v>7.773819652881675e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.859170173851404e-06</v>
+        <v>7.85917017385136e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.308895517925458e-06</v>
+        <v>7.308895517925536e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.859170173851404e-06</v>
+        <v>7.85917017385136e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.859170173851404e-06</v>
+        <v>7.85917017385136e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.859170173851404e-06</v>
+        <v>7.85917017385136e-06</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.05113282834475e-05</v>
+        <v>1.051132828344737e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>9.985471685011798e-06</v>
+        <v>9.98547168501193e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>2.040710843935742e-05</v>
+        <v>1.044402543999666e-05</v>
       </c>
       <c r="E4" t="n">
         <v>9.825699142338358e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>1.000917176848485e-05</v>
+        <v>1.000917176848498e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.042597776247761e-05</v>
+        <v>2.035404609548427e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.093061471619373e-05</v>
+        <v>2.093061471619375e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>9.961053627521489e-06</v>
+        <v>9.961053627521559e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.077726316669544e-05</v>
+        <v>2.03549504946715e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.045027022611354e-05</v>
+        <v>1.045027022611345e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.057768241866412e-05</v>
+        <v>1.05776824186641e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.159430334231201e-05</v>
+        <v>2.15943033423122e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.104402868638626e-05</v>
+        <v>2.104402868638633e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.158620141350603e-05</v>
+        <v>2.158620141350617e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.10656974605102e-05</v>
+        <v>2.10656974605103e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.10656974605102e-05</v>
+        <v>2.10656974605103e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.150895282134255e-05</v>
+        <v>2.150895282134256e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.159430334231201e-05</v>
+        <v>2.15943033423122e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.104402868638626e-05</v>
+        <v>2.104402868638633e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.159430334231201e-05</v>
+        <v>2.15943033423122e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.159430334231201e-05</v>
+        <v>2.15943033423122e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.159430334231201e-05</v>
+        <v>2.15943033423122e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.706268176195728e-05</v>
+        <v>5.706268176195726e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>8.943624908606363e-05</v>
+        <v>8.943624908614943e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>9.676832954575144e-05</v>
+        <v>9.676832954575156e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>8.0435928556815e-05</v>
+        <v>8.043592855681507e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>5.757261588638858e-05</v>
+        <v>5.75726158863886e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>8.986376313613606e-05</v>
+        <v>8.986376313613607e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>8.994911365711032e-05</v>
+        <v>8.994911365711049e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>8.939883900117965e-05</v>
+        <v>8.939883900117985e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>8.995557678348522e-05</v>
+        <v>8.995557678348523e-05</v>
       </c>
       <c r="K6" t="n">
         <v>5.645179940565223e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001243017416903323</v>
+        <v>0.0001243017416903325</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.850683217484018e-05</v>
+        <v>6.850683217484025e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>8.543542957439e-05</v>
+        <v>8.54354295743902e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>8.598570653867662e-05</v>
+        <v>8.59857065386767e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000105605675565525</v>
+        <v>0.0001056056755655251</v>
       </c>
       <c r="F7" t="n">
-        <v>8.543542650580203e-05</v>
+        <v>8.543542650580219e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>8.590035370934629e-05</v>
+        <v>8.590035370934632e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>8.5985704230316e-05</v>
+        <v>8.598570423031616e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.543542957439e-05</v>
+        <v>8.54354295743902e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>8.5985704230316e-05</v>
+        <v>8.598570423031616e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>7.585837808746644e-05</v>
+        <v>7.544749957943861e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>8.5985704230316e-05</v>
+        <v>8.598570423031616e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.583237595257194e-06</v>
+        <v>9.583237595257162e-06</v>
       </c>
       <c r="C8" t="n">
-        <v>8.968055095708015e-06</v>
+        <v>8.968055095708023e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>9.733834903348762e-06</v>
+        <v>9.733834903348757e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>8.968055095708015e-06</v>
+        <v>8.968055095708023e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>8.968055095708015e-06</v>
+        <v>8.968055095708023e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>8.310415039525309e-06</v>
+        <v>8.310415039525205e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>8.341134065620634e-06</v>
+        <v>8.341134065620625e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>8.968055095708015e-06</v>
+        <v>8.968055095708023e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>9.221871709309101e-06</v>
+        <v>9.221871709309095e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>9.616838159804949e-06</v>
+        <v>9.616838159804952e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>8.832377272309072e-06</v>
+        <v>8.832377272309059e-06</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.037147387539893e-05</v>
+        <v>1.037147387539898e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.104590039574639e-05</v>
+        <v>1.104590039574642e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>1.043284691421168e-05</v>
+        <v>1.043284691421163e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.104590039574639e-05</v>
+        <v>1.104590039574642e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.104590039574639e-05</v>
+        <v>1.104590039574642e-05</v>
       </c>
       <c r="G9" t="n">
         <v>9.851347289435546e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>9.868117362100167e-06</v>
+        <v>9.868117362100223e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>1.104590039574639e-05</v>
+        <v>1.104590039574642e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>1.022499837035612e-05</v>
+        <v>1.022499837035616e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.038523638177254e-05</v>
+        <v>1.03852363817725e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.006732647994621e-05</v>
+        <v>8.724841888205828e-06</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003260648478018182</v>
+        <v>0.003260648478018178</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0006958978737353124</v>
+        <v>0.0006958978737353113</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001071225790579776</v>
+        <v>0.001071225790579777</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0006958978737353124</v>
+        <v>0.0006958978737353113</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0006958978737353124</v>
+        <v>0.0006958978737353113</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002004128555050534</v>
+        <v>0.002004128555050532</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004415548160127142</v>
+        <v>0.004415548160127147</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0006958978737353124</v>
+        <v>0.0006958978737353113</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0013080607913774</v>
+        <v>0.001308060791377404</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001858217122870225</v>
+        <v>0.00185821712287023</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004982132875205744</v>
+        <v>0.004982132875205759</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.349728075125443e-05</v>
+        <v>1.349728075125444e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.14981586509779e-05</v>
+        <v>1.149815865097796e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.349728075125443e-05</v>
+        <v>1.349728075125444e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.166093478368395e-05</v>
+        <v>1.1660934783684e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.166093478368395e-05</v>
+        <v>1.166093478368399e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.336239861793566e-05</v>
+        <v>1.336239861793568e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.349728075125443e-05</v>
+        <v>1.349728075125444e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.263157778304369e-05</v>
+        <v>1.263157778304378e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.349728075125443e-05</v>
+        <v>1.349728075125444e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.349728075125443e-05</v>
+        <v>1.349728075125444e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.349728075125443e-05</v>
+        <v>1.349728075125444e-05</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.159510140242315e-05</v>
+        <v>2.159510140242318e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.845565206804013e-05</v>
+        <v>1.845565206804017e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>2.052540887716718e-05</v>
+        <v>2.052540887716744e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.808319347409868e-05</v>
+        <v>1.808319347409865e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>2.037737063347699e-05</v>
+        <v>2.0377370633477e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>4.254362408354517e-05</v>
+        <v>4.254362408354524e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>4.430360942117263e-05</v>
+        <v>4.43036094211727e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>2.07293984342124e-05</v>
+        <v>4.181280324865321e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>4.310005306790726e-05</v>
+        <v>4.310005306790732e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>2.208672100919098e-05</v>
+        <v>2.2086721009191e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>2.269675685280438e-05</v>
+        <v>2.269675685280442e-05</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.622871804164972e-05</v>
+        <v>3.622871804164975e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>3.536301507343893e-05</v>
+        <v>3.536301507343905e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>3.621997039729033e-05</v>
+        <v>3.621997039729036e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5323984441793e-05</v>
+        <v>3.532398444179309e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5323984441793e-05</v>
+        <v>3.532398444179309e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>3.609383590833095e-05</v>
+        <v>3.609383590833097e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>3.622871804164972e-05</v>
+        <v>3.622871804164975e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.536301507343893e-05</v>
+        <v>3.536301507343905e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>3.622871804164972e-05</v>
+        <v>3.622871804164975e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>3.622871804164972e-05</v>
+        <v>3.622871804164975e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>3.622871804164972e-05</v>
+        <v>3.622871804164975e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7407,34 +7407,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.184532858545358e-05</v>
+        <v>8.184532858545362e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001276246494951754</v>
+        <v>0.0001276246494952798</v>
       </c>
       <c r="D6" t="n">
         <v>0.0001381831916986594</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001148624287180251</v>
+        <v>0.0001148624287180254</v>
       </c>
       <c r="F6" t="n">
-        <v>8.244067877391062e-05</v>
+        <v>8.244067877391082e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001283726066687754</v>
+        <v>0.0001283726066687755</v>
       </c>
       <c r="H6" t="n">
         <v>0.000128507488802101</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001276417858338833</v>
+        <v>0.0001276417858338834</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001285166592525229</v>
+        <v>0.0001285166592525231</v>
       </c>
       <c r="K6" t="n">
-        <v>8.097855500325659e-05</v>
+        <v>8.097855500325666e-05</v>
       </c>
       <c r="L6" t="n">
         <v>0.0001772500169735366</v>
@@ -7450,34 +7450,34 @@
         <v>0.0001351155692758185</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001692918919730495</v>
+        <v>0.0001692918919730498</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001701575960011183</v>
+        <v>0.0001701575960011184</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002097295705020995</v>
+        <v>0.0002097295705020998</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001692918303441684</v>
+        <v>0.0001692918303441687</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001700227128079412</v>
+        <v>0.0001700227128079414</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00017015759494126</v>
+        <v>0.0001701575949412604</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001692918919730495</v>
+        <v>0.0001692918919730498</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00017015759494126</v>
+        <v>0.0001701575949412604</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001490303699443641</v>
+        <v>0.0001498541080958588</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00017015759494126</v>
+        <v>0.0001701575949412604</v>
       </c>
     </row>
     <row r="8">
@@ -7487,19 +7487,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-5.784268538408776e-05</v>
+        <v>-5.78426853840877e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>3.170933983038451e-06</v>
+        <v>3.170933983038455e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.453295310756649e-06</v>
+        <v>-5.453295310756607e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>3.170933983038451e-06</v>
+        <v>3.170933983038455e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>3.170933983038451e-06</v>
+        <v>3.170933983038455e-06</v>
       </c>
       <c r="G8" t="n">
         <v>-2.657814408780584e-05</v>
@@ -7508,16 +7508,16 @@
         <v>-7.793051511974881e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>3.170933983038451e-06</v>
+        <v>3.170933983038455e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>-8.209273163124745e-06</v>
+        <v>-8.209273163124714e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.376205870275952e-05</v>
+        <v>-2.376205870275949e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>1.129476567165023e-05</v>
+        <v>-7.802789830342144e-05</v>
       </c>
     </row>
     <row r="9">
@@ -7527,13 +7527,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.223392209878837e-05</v>
+        <v>-1.223392209878833e-05</v>
       </c>
       <c r="C9" t="n">
         <v>1.236394435118685e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>9.104603741456036e-06</v>
+        <v>9.104603741456065e-06</v>
       </c>
       <c r="E9" t="n">
         <v>1.236394435118685e-05</v>
@@ -7542,22 +7542,22 @@
         <v>1.236394435118685e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>3.720417607154373e-07</v>
+        <v>3.720417607154577e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.032493532392742e-05</v>
+        <v>-2.032493532392737e-05</v>
       </c>
       <c r="I9" t="n">
         <v>1.236394435118685e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>7.991991837777902e-06</v>
+        <v>7.991991837777892e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>1.649185298185343e-06</v>
+        <v>1.649185298185327e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>1.593138562199421e-05</v>
+        <v>-2.038141716907824e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.11834684694207e-05</v>
+        <v>7.118346846942067e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000147517245925199</v>
+        <v>0.0001475172459251992</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007200285803588778</v>
+        <v>0.0007200285803588787</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000147517245925199</v>
+        <v>0.0001475172459251992</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000147517245925199</v>
+        <v>0.0001475172459251992</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0009309615243772285</v>
+        <v>0.0009309615243772303</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0006026361400259359</v>
+        <v>0.0006026361400259348</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000147517245925199</v>
+        <v>0.0001475172459251992</v>
       </c>
       <c r="J2" t="n">
         <v>0.0003540400575296459</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002443275290516775</v>
+        <v>0.0002443275290516772</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002867978356284166</v>
+        <v>0.0001991011344772465</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.364979948887067e-06</v>
+        <v>9.364979948887058e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.883621542086903e-06</v>
+        <v>7.883621542086847e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>9.364979948887067e-06</v>
+        <v>9.364979948887058e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.989807464667257e-06</v>
+        <v>7.989807464667154e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.989807464667257e-06</v>
+        <v>7.989807464667147e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>9.247279459614136e-06</v>
+        <v>9.247279459614134e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>9.364979948887062e-06</v>
+        <v>9.364979948887058e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>8.608724799874137e-06</v>
+        <v>8.6087247998741e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>9.364979948887067e-06</v>
+        <v>9.364979948887058e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>9.364979948887067e-06</v>
+        <v>9.364979948887058e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>9.364979948887067e-06</v>
+        <v>9.364979948887058e-06</v>
       </c>
     </row>
     <row r="4">
@@ -7723,34 +7723,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.337561132507873e-05</v>
+        <v>2.795428521077512e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.135176573208343e-05</v>
+        <v>1.135176573208348e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.36675484392457e-05</v>
+        <v>1.366754843924363e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.115677026604993e-05</v>
+        <v>1.115677026604992e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.250016399041014e-05</v>
+        <v>1.250016399041009e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78365847215022e-05</v>
+        <v>1.325791083580579e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.876178297160519e-05</v>
+        <v>2.876178297160522e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>2.719803006176217e-05</v>
+        <v>2.719803006176216e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.828248641331299e-05</v>
+        <v>1.382621913695215e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.258879756569567e-05</v>
+        <v>1.258879756569572e-05</v>
       </c>
       <c r="L4" t="n">
         <v>1.421807797211517e-05</v>
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.637826972865689e-05</v>
+        <v>2.63782697286569e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.562201457964395e-05</v>
+        <v>2.562201457964401e-05</v>
       </c>
       <c r="D5" t="n">
         <v>2.637016801965547e-05</v>
@@ -7778,22 +7778,22 @@
         <v>2.560824172149306e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.626056923938395e-05</v>
+        <v>2.626056923938398e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.637826972865689e-05</v>
+        <v>2.63782697286569e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.562201457964395e-05</v>
+        <v>2.562201457964401e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.637826972865689e-05</v>
+        <v>2.63782697286569e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.637826972865689e-05</v>
+        <v>2.63782697286569e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.637826972865689e-05</v>
+        <v>2.63782697286569e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7803,19 +7803,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.528739750160772e-05</v>
+        <v>6.528739750160779e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001023427843183595</v>
+        <v>0.0001023427843184464</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001109341231467677</v>
+        <v>0.0001109341231467674</v>
       </c>
       <c r="E6" t="n">
-        <v>9.20001907495616e-05</v>
+        <v>9.200019074956163e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>6.572618795511309e-05</v>
+        <v>6.572618795511297e-05</v>
       </c>
       <c r="G6" t="n">
         <v>0.0001029768609286816</v>
@@ -7824,13 +7824,13 @@
         <v>0.0001030945614179471</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001023383062689416</v>
+        <v>0.0001023383062689414</v>
       </c>
       <c r="J6" t="n">
         <v>0.0001031019916087447</v>
       </c>
       <c r="K6" t="n">
-        <v>6.458511002175869e-05</v>
+        <v>6.458511002175866e-05</v>
       </c>
       <c r="L6" t="n">
         <v>0.000142587305511851</v>
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.090457832905038e-05</v>
+        <v>9.090457832905029e-05</v>
       </c>
       <c r="C7" t="n">
         <v>0.0001136885638832049</v>
@@ -7858,7 +7858,7 @@
         <v>0.0001136885532532981</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001143271185429448</v>
+        <v>0.0001143271185429447</v>
       </c>
       <c r="H7" t="n">
         <v>0.0001144448190322178</v>
@@ -7870,7 +7870,7 @@
         <v>0.0001144448190322178</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001008055209152401</v>
+        <v>8.480344803236531e-05</v>
       </c>
       <c r="L7" t="n">
         <v>0.0001144448190322178</v>
@@ -7886,34 +7886,34 @@
         <v>1.309353056322616e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.178248953820099e-05</v>
+        <v>1.178248953820097e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.310603159872521e-06</v>
+        <v>-4.310603159872563e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>1.178248953820099e-05</v>
+        <v>1.178248953820097e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.178248953820099e-05</v>
+        <v>1.178248953820097e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>-9.13894079487207e-06</v>
+        <v>-9.13894079487211e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>5.56313901985763e-07</v>
+        <v>5.563139019857621e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.178248953820099e-05</v>
+        <v>1.178248953820097e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>6.494101643935428e-06</v>
+        <v>6.494101643935418e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>8.579614817102191e-06</v>
+        <v>8.579614817102201e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>1.032158322583419e-05</v>
+        <v>-4.738903654398917e-05</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.35455128177819e-05</v>
+        <v>1.354551281778188e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.327455710742138e-05</v>
+        <v>1.327455710742139e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>6.457407544474702e-06</v>
+        <v>6.457407544474671e-06</v>
       </c>
       <c r="E9" t="n">
-        <v>1.327455710742138e-05</v>
+        <v>1.327455710742139e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.327455710742138e-05</v>
+        <v>1.327455710742139e-05</v>
       </c>
       <c r="G9" t="n">
         <v>4.400113873609817e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>8.451761878799394e-06</v>
+        <v>8.451761878799386e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>1.327455710742138e-05</v>
+        <v>1.327455710742139e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>1.086049618429921e-05</v>
+        <v>1.08604961842992e-05</v>
       </c>
       <c r="K9" t="n">
         <v>1.17073140143118e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.241931129115605e-05</v>
+        <v>-1.104210132563641e-05</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Hydrogen/hydrogen eutrophication freshwater results.xlsx
+++ b/Results/Hydrogen/hydrogen eutrophication freshwater results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007886762567972367</v>
+        <v>0.007886762567972362</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001723738605140723</v>
+        <v>0.001723738605140722</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001284908587117467</v>
+        <v>0.001284908587117469</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001723738605140723</v>
+        <v>0.001723738605140722</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001723738605140723</v>
+        <v>0.001723738605140722</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002719256064629246</v>
+        <v>0.002719256064629243</v>
       </c>
       <c r="H2" t="n">
-        <v>0.005750835857818343</v>
+        <v>0.005750835857818341</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001723738605140723</v>
+        <v>0.001723738605140722</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002249663638092962</v>
+        <v>0.00224966363809297</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003646867655377432</v>
+        <v>0.003646867655377436</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0005325579854737561</v>
+        <v>0.00635206259964423</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.834195374324886e-05</v>
+        <v>1.834195374324882e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.669533465412946e-05</v>
+        <v>1.669533465412943e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.834195374324886e-05</v>
+        <v>1.834195374324882e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.688156968271497e-05</v>
+        <v>1.688156968271491e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.688156968271492e-05</v>
+        <v>1.688156968271491e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.822170357809673e-05</v>
+        <v>1.822170357809674e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.834195374324886e-05</v>
+        <v>1.834195374324882e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.756986977313907e-05</v>
+        <v>1.756986977313902e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.834195374324886e-05</v>
+        <v>1.834195374324882e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.834195374324886e-05</v>
+        <v>1.834195374324882e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.834195374324886e-05</v>
+        <v>1.834195374324882e-05</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.042947522643254e-05</v>
+        <v>3.042947522643242e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>2.788284662730246e-05</v>
+        <v>2.788284662730234e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>2.804935789017208e-05</v>
+        <v>2.804921789430064e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>2.729562415002186e-05</v>
+        <v>2.729562415002185e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>2.939774277767258e-05</v>
+        <v>2.939774277767257e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>5.596718484601387e-05</v>
+        <v>5.596718484601377e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>5.749208406109796e-05</v>
+        <v>5.749208406109814e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>2.965739125632259e-05</v>
+        <v>5.531535104105604e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.134518346566151e-05</v>
+        <v>5.625238569815289e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.277942513546106e-05</v>
+        <v>3.277942513546286e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>3.161788270096641e-05</v>
+        <v>3.16178827009664e-05</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.659485276609265e-05</v>
+        <v>4.659485276609266e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.582276879598293e-05</v>
+        <v>4.582276879598284e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.658543075554207e-05</v>
+        <v>4.658543075554202e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.578283071980758e-05</v>
+        <v>4.578283071980747e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.578283071980758e-05</v>
+        <v>4.578283071980747e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.647460260094065e-05</v>
+        <v>4.647460260094063e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.659485276609265e-05</v>
+        <v>4.659485276609266e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.582276879598293e-05</v>
+        <v>4.582276879598284e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.659485276609265e-05</v>
+        <v>4.659485276609266e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.659485276609265e-05</v>
+        <v>4.659485276609266e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.659485276609265e-05</v>
+        <v>4.659485276609266e-05</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.818599962300045e-05</v>
+        <v>9.81859996230002e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001521913743204762</v>
+        <v>0.0001521913743205779</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001643407242429707</v>
+        <v>0.0001643407242429704</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001372051017462865</v>
+        <v>0.0001372051017462864</v>
       </c>
       <c r="F6" t="n">
-        <v>9.913256586041877e-05</v>
+        <v>9.913256586041866e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001528587818649073</v>
+        <v>0.0001528587818649071</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001529790320300614</v>
+        <v>0.0001529790320300613</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001522069480599497</v>
+        <v>0.0001522069480599494</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001529898004301129</v>
+        <v>0.0001529898004301128</v>
       </c>
       <c r="K6" t="n">
-        <v>9.716819091547194e-05</v>
+        <v>9.716819091547199e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002102149360970529</v>
+        <v>0.0002102149360970526</v>
       </c>
     </row>
     <row r="7">
@@ -718,10 +718,10 @@
         <v>0.000183075653809287</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0002296290933397731</v>
+        <v>0.0002296290933397728</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0002304011809044708</v>
+        <v>0.0002304011809044706</v>
       </c>
       <c r="E7" t="n">
         <v>0.0002842416618725175</v>
@@ -730,22 +730,22 @@
         <v>0.0002296290250411342</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0002302809271447309</v>
+        <v>0.0002302809271447305</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0002304011773098828</v>
+        <v>0.0002304011773098826</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0002296290933397731</v>
+        <v>0.0002296290933397728</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0002304011773098828</v>
+        <v>0.0002304011773098826</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0002029805846438746</v>
+        <v>0.0001708098947149724</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002304011773098828</v>
+        <v>0.0002304011773098826</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.0001494314001551528</v>
+        <v>-0.0001494314001551532</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.229272773562905e-05</v>
+        <v>-1.22927277356291e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.533546470963295e-06</v>
+        <v>-2.533546470963399e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.229272773562905e-05</v>
+        <v>-1.22927277356291e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.229272773562905e-05</v>
+        <v>-1.22927277356291e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.211539070330456e-05</v>
+        <v>-3.211539070330453e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>-8.433716897656397e-05</v>
+        <v>-8.433716897656401e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.229272773562905e-05</v>
+        <v>-1.22927277356291e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.069590189068642e-05</v>
+        <v>-2.069590189068646e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.320524458559476e-05</v>
+        <v>-5.320524458559455e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>1.46627670700649e-05</v>
+        <v>1.466276707006489e-05</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-4.680292392576595e-05</v>
+        <v>-4.680292392576571e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>9.231732331439987e-06</v>
+        <v>9.231732331439953e-06</v>
       </c>
       <c r="D9" t="n">
         <v>1.302834611979201e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>9.231732331439987e-06</v>
+        <v>9.231732331439953e-06</v>
       </c>
       <c r="F9" t="n">
-        <v>9.231732331439987e-06</v>
+        <v>9.231732331439953e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>8.993115091907937e-07</v>
+        <v>8.993115091907219e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.018947600647784e-05</v>
+        <v>-2.018947600647781e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>9.231732331439987e-06</v>
+        <v>9.231732331439953e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>5.647327839831961e-06</v>
+        <v>5.647327839831935e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>-7.606530535695627e-06</v>
+        <v>-7.60653053569568e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>2.00386520463193e-05</v>
+        <v>-2.325085276427653e-05</v>
       </c>
     </row>
   </sheetData>
@@ -911,34 +911,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.717984789985818e-05</v>
+        <v>6.717984789985841e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001973528699744918</v>
+        <v>0.0001973528699744921</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002490610083368836</v>
+        <v>0.0002490610083368838</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001973528699744918</v>
+        <v>0.0001973528699744921</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001973528699744918</v>
+        <v>0.0001973528699744921</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002715907265270373</v>
+        <v>0.0002715907265270347</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002767046234951612</v>
+        <v>0.0002767046234951623</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001973528699744918</v>
+        <v>0.0001973528699744921</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001777335177881011</v>
+        <v>0.0001777335177881013</v>
       </c>
       <c r="K2" t="n">
-        <v>9.856656579932639e-05</v>
+        <v>9.85665657993265e-05</v>
       </c>
       <c r="L2" t="n">
         <v>0.000294336747306077</v>
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.334851940876776e-06</v>
+        <v>8.3348519408768e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.651487127978276e-06</v>
+        <v>7.65148712797829e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.334851940876776e-06</v>
+        <v>8.3348519408768e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.709129026630304e-06</v>
+        <v>7.709129026630355e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.709129026630312e-06</v>
+        <v>7.709129026630338e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.245430085608259e-06</v>
+        <v>8.245430085608254e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>8.334851940876776e-06</v>
+        <v>8.3348519408768e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.758723852805699e-06</v>
+        <v>7.75872385280574e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>8.334851940876776e-06</v>
+        <v>8.3348519408768e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>8.334851940876776e-06</v>
+        <v>8.3348519408768e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>8.334851940876776e-06</v>
+        <v>8.3348519408768e-06</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.166894661802999e-05</v>
+        <v>1.117351024945195e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.047313286490496e-05</v>
+        <v>1.047313286490503e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184287357290896e-05</v>
+        <v>2.184287357290891e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.030377714793362e-05</v>
+        <v>1.030377714793364e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.063265876530064e-05</v>
+        <v>1.063265876530069e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.108408839418339e-05</v>
+        <v>2.157952476276159e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.234131040119761e-05</v>
+        <v>2.234131040119772e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.05973821613808e-05</v>
+        <v>1.059738216138089e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.177869143992103e-05</v>
+        <v>1.14847625621557e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.095368000144922e-05</v>
+        <v>1.095368000145172e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.123959256166813e-05</v>
+        <v>1.123959256166818e-05</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.309181731968581e-05</v>
+        <v>2.309181731968592e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.251568923161477e-05</v>
+        <v>2.251568923161478e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.308370470599668e-05</v>
+        <v>2.308370470599683e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.25355734689958e-05</v>
+        <v>2.253557346899584e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.25355734689958e-05</v>
+        <v>2.253557346899584e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.300239546441736e-05</v>
+        <v>2.300239546441735e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.309181731968581e-05</v>
+        <v>2.309181731968592e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.251568923161477e-05</v>
+        <v>2.251568923161478e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.309181731968581e-05</v>
+        <v>2.309181731968592e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.309181731968581e-05</v>
+        <v>2.309181731968592e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.309181731968581e-05</v>
+        <v>2.309181731968592e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.949979862628951e-05</v>
+        <v>5.949979862628964e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>9.327296960837217e-05</v>
+        <v>9.327296960845963e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001009281881776291</v>
+        <v>0.0001009281881776294</v>
       </c>
       <c r="E6" t="n">
-        <v>8.388256124743498e-05</v>
+        <v>8.388256124743514e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>6.002805073113779e-05</v>
+        <v>6.002805073113805e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>9.372367947606124e-05</v>
+        <v>9.372367947606159e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>9.381310133132491e-05</v>
+        <v>9.381310133132512e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>9.323697324325884e-05</v>
+        <v>9.323697324325911e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>9.381984487895421e-05</v>
+        <v>9.381984487895429e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.886241141211531e-05</v>
+        <v>5.886241141211546e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001296562152387081</v>
+        <v>0.0001296562152387085</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.205850820651286e-05</v>
+        <v>7.205850820651292e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>8.989053665748784e-05</v>
+        <v>8.989053665748806e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>9.046667016218198e-05</v>
+        <v>9.046667016218204e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001111331581097229</v>
+        <v>0.0001111331581097231</v>
       </c>
       <c r="F7" t="n">
-        <v>8.989053203791589e-05</v>
+        <v>8.989053203791566e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>9.037724289029049e-05</v>
+        <v>9.037724289029062e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>9.046666474555898e-05</v>
+        <v>9.046666474555923e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.989053665748784e-05</v>
+        <v>8.989053665748806e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>9.046666474555898e-05</v>
+        <v>9.046666474555923e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>7.980090883067007e-05</v>
+        <v>7.980090883067043e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>9.046666474555898e-05</v>
+        <v>9.046666474555923e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1154,34 +1154,34 @@
         <v>1.102250446940598e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>9.316363872305378e-06</v>
+        <v>9.316363872305442e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>6.323673287178175e-06</v>
+        <v>6.323673287178183e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>9.316363872305378e-06</v>
+        <v>9.316363872305442e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>9.316363872305378e-06</v>
+        <v>9.316363872305442e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>5.869109465543182e-06</v>
+        <v>5.869109465543178e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>6.395354181659455e-06</v>
+        <v>6.395354181659436e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>9.316363872305378e-06</v>
+        <v>9.316363872305442e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>8.400178322846728e-06</v>
+        <v>8.40017832284675e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>1.028980032552843e-05</v>
+        <v>1.028980032552838e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>6.239052801862789e-06</v>
+        <v>6.23905280186274e-06</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.143493457788639e-05</v>
+        <v>1.143493457788636e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.165817880881257e-05</v>
+        <v>1.165817880881259e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>9.521278482609439e-06</v>
+        <v>9.521278482609442e-06</v>
       </c>
       <c r="E9" t="n">
-        <v>1.165817880881257e-05</v>
+        <v>1.165817880881259e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.165817880881257e-05</v>
+        <v>1.165817880881259e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>9.322853384531116e-06</v>
+        <v>9.322853384531133e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>9.555445772351499e-06</v>
+        <v>9.555445772351475e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>1.165817880881257e-05</v>
+        <v>1.165817880881259e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>1.036821100440156e-05</v>
+        <v>1.036821100440157e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.113659387027643e-05</v>
+        <v>1.113659387027641e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.090546563724729e-05</v>
+        <v>9.490948286135879e-06</v>
       </c>
     </row>
   </sheetData>
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001493517404076354</v>
+        <v>0.001493517404076352</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002924338229471383</v>
+        <v>0.00292433822947138</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007844913768527612</v>
+        <v>0.0007844913768527618</v>
       </c>
       <c r="E2" t="n">
         <v>0.0009269635363640596</v>
@@ -1322,7 +1322,7 @@
         <v>0.0009269635363640596</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001430281033238761</v>
+        <v>0.001430281033238762</v>
       </c>
       <c r="H2" t="n">
         <v>0.002572305310437346</v>
@@ -1331,10 +1331,10 @@
         <v>0.0009269635363640596</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00199604003162113</v>
+        <v>0.001996040031621128</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001556290536172605</v>
+        <v>0.001556290536172602</v>
       </c>
       <c r="L2" t="n">
         <v>0.001202877379448047</v>
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.693939410370624e-05</v>
+        <v>1.693939410370625e-05</v>
       </c>
       <c r="C3" t="n">
         <v>1.807068225818025e-05</v>
@@ -1356,22 +1356,22 @@
         <v>1.693939410370624e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.584804505979234e-05</v>
+        <v>1.584804505979243e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.584804505979234e-05</v>
+        <v>1.584804505979243e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.68351647079038e-05</v>
+        <v>1.683516470790391e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.693939410370624e-05</v>
+        <v>1.693939410370625e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.626963068875824e-05</v>
+        <v>1.626963068875825e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.693939410370624e-05</v>
+        <v>1.693939410370625e-05</v>
       </c>
       <c r="K3" t="n">
         <v>1.693939410370624e-05</v>
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.693948576884185e-05</v>
+        <v>4.424114226252883e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>2.977405910935291e-05</v>
+        <v>2.977405910935293e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>2.586973724087588e-05</v>
+        <v>2.586968139110197e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>2.462628698887857e-05</v>
+        <v>2.462628698887852e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>2.601089264802414e-05</v>
+        <v>2.601089264802408e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>4.41369128667264e-05</v>
+        <v>2.683525637303943e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>4.636764544845739e-05</v>
+        <v>4.636764544845738e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>4.35713788475809e-05</v>
+        <v>2.626972235389388e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5082137028815e-05</v>
+        <v>4.508213702881493e-05</v>
       </c>
       <c r="K4" t="n">
         <v>2.742344291659438e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>2.680914254104263e-05</v>
+        <v>2.680914254104262e-05</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.878848179971175e-05</v>
+        <v>3.878848179971176e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>3.877993895780344e-05</v>
+        <v>3.877993895780347e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>3.877979048389631e-05</v>
+        <v>3.877979048389628e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>3.810345140476729e-05</v>
+        <v>3.81034514047673e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>3.810345140476729e-05</v>
+        <v>3.81034514047673e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>3.86842524039093e-05</v>
+        <v>3.868425240390929e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>3.878848179971175e-05</v>
+        <v>3.878848179971176e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.811871838476368e-05</v>
+        <v>3.811871838476373e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>3.878848179971175e-05</v>
+        <v>3.878848179971176e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>3.878848179971175e-05</v>
+        <v>3.878848179971176e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>3.878848179971175e-05</v>
+        <v>3.878848179971176e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.27318637396849e-05</v>
+        <v>8.27318637396851e-05</v>
       </c>
       <c r="C6" t="n">
         <v>0.0001276171254509637</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001369283285378405</v>
+        <v>0.0001369283285378408</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001146763009428295</v>
+        <v>0.0001146763009428296</v>
       </c>
       <c r="F6" t="n">
-        <v>8.34810748596222e-05</v>
+        <v>8.348107485962236e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001275161690492079</v>
+        <v>0.000127516169049208</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001276203984450558</v>
+        <v>0.000127620398445056</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001269506350300622</v>
+        <v>0.0001269506350300625</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001276292203280402</v>
+        <v>0.0001276292203280404</v>
       </c>
       <c r="K6" t="n">
-        <v>8.189803616176165e-05</v>
+        <v>8.189803616176176e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001745102264628054</v>
+        <v>0.0001745102264628059</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001251274422607805</v>
+        <v>0.0001251274422607804</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001563815102004417</v>
+        <v>0.0001563815102004416</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001563900491426294</v>
+        <v>0.0001563900491426297</v>
       </c>
       <c r="E7" t="n">
         <v>0.0001917966216430443</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001557202460860392</v>
+        <v>0.0001557202460860391</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001562858236465471</v>
+        <v>0.0001562858236465473</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001563900530423495</v>
+        <v>0.0001563900530423498</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001557202896274017</v>
+        <v>0.0001557202896274018</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001563900530423495</v>
+        <v>0.0001563900530423498</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001382763719375911</v>
+        <v>0.0001382763719375912</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001563900530423495</v>
+        <v>0.0001563900530423498</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.831459982409875e-05</v>
+        <v>-1.831459982409869e-05</v>
       </c>
       <c r="C8" t="n">
         <v>-4.368584895002019e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>3.525704919735399e-06</v>
+        <v>3.525704919735415e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>1.311443878735917e-07</v>
+        <v>1.311443878736002e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>1.311443878735917e-07</v>
+        <v>1.311443878736002e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.338834763065902e-05</v>
+        <v>-1.338834763065899e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.083616858746193e-05</v>
+        <v>-3.083616858746192e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.311443878735917e-07</v>
+        <v>1.311443878735994e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.003307847075901e-05</v>
+        <v>-2.003307847075898e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.165028686478478e-05</v>
+        <v>-1.165028686478475e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.27074267218589e-06</v>
+        <v>-6.270742672185873e-06</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.147720906210452e-06</v>
+        <v>1.147720906210487e-06</v>
       </c>
       <c r="C9" t="n">
-        <v>-5.419340034280548e-06</v>
+        <v>-5.419340034280557e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>1.35629849738083e-05</v>
+        <v>1.356298497380831e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.200466222939515e-05</v>
+        <v>1.200466222939514e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.200466222939515e-05</v>
+        <v>1.200466222939514e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.985384889596758e-06</v>
+        <v>4.985384889596764e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.847040234246504e-07</v>
+        <v>-3.847040234246267e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>1.200466222939515e-05</v>
+        <v>1.200466222939514e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>5.215180668532293e-06</v>
+        <v>5.2151806685323e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>8.832762117756405e-06</v>
+        <v>8.83276211775645e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>7.385320232997561e-06</v>
+        <v>7.385320232997569e-06</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.000552666288882658</v>
+        <v>0.000552666288882657</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001840147929687066</v>
+        <v>0.001840147929687068</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0005339774925564356</v>
+        <v>0.0005339774925564358</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0004465293216036631</v>
+        <v>0.0004465293216036643</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0004465293216036631</v>
+        <v>0.0004465293216036643</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008014372858603168</v>
+        <v>0.0008014372858603239</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001321224625876578</v>
+        <v>0.001321224625876579</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0004465293216036631</v>
+        <v>0.0004465293216036643</v>
       </c>
       <c r="J2" t="n">
         <v>0.001133756082091973</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0004807281313544855</v>
+        <v>0.0004807281313544849</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003798088182379134</v>
+        <v>0.0003798088182379137</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.363993582201168e-05</v>
+        <v>1.363993582201214e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.436077302470189e-05</v>
+        <v>1.436077302470192e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.363993582201168e-05</v>
+        <v>1.363993582201214e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.288004359368985e-05</v>
+        <v>1.288004359369012e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.288004359369015e-05</v>
+        <v>1.288004359369012e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.354043047817818e-05</v>
+        <v>1.354043047817827e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.363993582201168e-05</v>
+        <v>1.363993582201214e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.299998356961129e-05</v>
+        <v>1.299998356961119e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.363993582201168e-05</v>
+        <v>1.363993582201214e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.363993582201168e-05</v>
+        <v>1.363993582201214e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.363993582201168e-05</v>
+        <v>1.363993582201214e-05</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.35643916435813e-05</v>
+        <v>3.356439164358161e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>2.212244710247978e-05</v>
+        <v>2.212244710247976e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>3.442235125347531e-05</v>
+        <v>3.442235125347648e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.839680074477874e-05</v>
+        <v>1.839680074477895e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.933003798421592e-05</v>
+        <v>1.93300379842162e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.994478048512409e-05</v>
+        <v>3.346488629974765e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.583005497504935e-05</v>
+        <v>3.583005497504968e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.940433357655697e-05</v>
+        <v>1.940433357655722e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.075986295685676e-05</v>
+        <v>2.075986295685672e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.971549456273372e-05</v>
+        <v>1.971549456273395e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.997260935078749e-05</v>
+        <v>1.997260935078768e-05</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.224287754055475e-05</v>
+        <v>3.224287754055485e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>3.22287724364085e-05</v>
+        <v>3.222877243640855e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>3.223468294858929e-05</v>
+        <v>3.223468294858887e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>3.165628914380311e-05</v>
+        <v>3.165628914380343e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>3.165628914380311e-05</v>
+        <v>3.165628914380343e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2143372196721e-05</v>
+        <v>3.214337219672089e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>3.224287754055475e-05</v>
+        <v>3.224287754055485e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.160292528815386e-05</v>
+        <v>3.160292528815384e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>3.224287754055475e-05</v>
+        <v>3.224287754055485e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>3.224287754055475e-05</v>
+        <v>3.224287754055485e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>3.224287754055475e-05</v>
+        <v>3.224287754055485e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.225372336631871e-05</v>
+        <v>7.225372336631914e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001121673200519499</v>
+        <v>0.0001121673200517688</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001203770732511263</v>
+        <v>0.0001203770732511265</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001006309187290131</v>
+        <v>0.0001006309187290137</v>
       </c>
       <c r="F6" t="n">
-        <v>7.291394478995102e-05</v>
+        <v>7.291394478995127e-05</v>
       </c>
       <c r="G6" t="n">
         <v>0.0001120126602565219</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001121121656004845</v>
+        <v>0.0001121121656004848</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001114722133479544</v>
+        <v>0.0001114722133479547</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001121199989249073</v>
+        <v>0.0001121199989249076</v>
       </c>
       <c r="K6" t="n">
-        <v>7.151333233857106e-05</v>
+        <v>7.15133323385712e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001537476414213718</v>
+        <v>0.0001537476414213723</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.451396957580679e-05</v>
+        <v>9.451396957580699e-05</v>
       </c>
       <c r="C7" t="n">
         <v>0.0001180045781836054</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001180186824437621</v>
+        <v>0.0001180186824437628</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001445026389561786</v>
+        <v>0.000144502638956179</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001173787049877744</v>
+        <v>0.0001173787049877748</v>
       </c>
       <c r="G7" t="n">
         <v>0.0001179191779439176</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001180186832877514</v>
+        <v>0.0001180186832877518</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001173787310353509</v>
+        <v>0.0001173787310353508</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001180186832877514</v>
+        <v>0.0001180186832877518</v>
       </c>
       <c r="K7" t="n">
-        <v>0.000104399959497973</v>
+        <v>0.0001043999594979729</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001180186832877514</v>
+        <v>0.0001180186832877518</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.541852675221927e-06</v>
+        <v>-1.541852675221837e-06</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.577371847095097e-05</v>
+        <v>-2.5773718470951e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>4.809680670359802e-06</v>
+        <v>4.809680670359917e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>7.490077612115362e-06</v>
+        <v>7.490077612115387e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>7.490077612115362e-06</v>
+        <v>7.490077612115387e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.397826585785766e-06</v>
+        <v>-3.397826585785862e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.065040683710817e-05</v>
+        <v>-1.065040683710808e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>7.490077612115362e-06</v>
+        <v>7.490077612115387e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>-5.264866367166456e-06</v>
+        <v>-5.264866367166427e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>6.351166640738808e-06</v>
+        <v>6.351166640739123e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>7.437807774403644e-06</v>
+        <v>7.437807774403734e-06</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.918660350838814e-06</v>
+        <v>5.918660350838962e-06</v>
       </c>
       <c r="C9" t="n">
-        <v>-5.021507508574276e-07</v>
+        <v>-5.02150750857442e-07</v>
       </c>
       <c r="D9" t="n">
-        <v>1.190551847085677e-05</v>
+        <v>1.190551847085668e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.325754235510501e-05</v>
+        <v>1.325754235510504e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.325754235510501e-05</v>
+        <v>1.325754235510504e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>7.277124044652406e-06</v>
+        <v>7.277124044652434e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>5.634237722711777e-06</v>
+        <v>5.634237722712052e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>1.325754235510501e-05</v>
+        <v>1.325754235510504e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>9.649580472118193e-06</v>
+        <v>9.649580472118271e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>1.264618402608102e-05</v>
+        <v>1.264618402608101e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.16405017406782e-05</v>
+        <v>1.164050174067835e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.580670305238404e-05</v>
+        <v>8.580670305238399e-05</v>
       </c>
       <c r="C2" t="n">
         <v>0.0010565852803508</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0003690627234170349</v>
+        <v>0.0003690627234170346</v>
       </c>
       <c r="E2" t="n">
-        <v>9.056940660134499e-05</v>
+        <v>9.056940660134501e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>9.056940660134499e-05</v>
+        <v>9.056940660134501e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0004270155701620349</v>
+        <v>0.0004270155701620355</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007102151590743149</v>
+        <v>0.0007102151590743136</v>
       </c>
       <c r="I2" t="n">
-        <v>9.056940660134499e-05</v>
+        <v>9.056940660134501e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0004006841763599389</v>
+        <v>0.0004006841763599399</v>
       </c>
       <c r="K2" t="n">
-        <v>8.249897272421808e-05</v>
+        <v>8.249897272421783e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001411465045492352</v>
+        <v>0.000141146504549235</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.109951313755932e-05</v>
+        <v>1.109951313755928e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.144175878185452e-05</v>
+        <v>1.144175878185446e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.109951313755932e-05</v>
+        <v>1.109951313755927e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.038709675851463e-05</v>
+        <v>1.03870967585146e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.038709675851463e-05</v>
+        <v>1.038709675851461e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.100046555273746e-05</v>
+        <v>1.100046555273742e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.109951313755932e-05</v>
+        <v>1.109951313755927e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.046231541618994e-05</v>
+        <v>1.046231541618995e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.109951313755932e-05</v>
+        <v>1.109951313755927e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.109951313755932e-05</v>
+        <v>1.109951313755927e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.109951313755932e-05</v>
+        <v>1.109951313755927e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.516717690159872e-05</v>
+        <v>1.516717690159862e-05</v>
       </c>
       <c r="C4" t="n">
         <v>1.64638874602205e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.534892936771656e-05</v>
+        <v>1.534892859811808e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.372523848885961e-05</v>
+        <v>1.372523848885951e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.449588529678327e-05</v>
+        <v>1.44958852967832e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>2.672206584297987e-05</v>
+        <v>2.67220658429799e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.90229698420098e-05</v>
+        <v>2.902296984200974e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>2.618391570643236e-05</v>
+        <v>2.618391570643232e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.763774066062817e-05</v>
+        <v>2.76377406606281e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.479339639779955e-05</v>
+        <v>1.479339639779858e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.517608087292586e-05</v>
+        <v>1.517608087292389e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.806213287941102e-05</v>
+        <v>2.806213287941095e-05</v>
       </c>
       <c r="C5" t="n">
         <v>2.803874145676705e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.805397023633582e-05</v>
+        <v>2.805397023633576e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.749719456570115e-05</v>
+        <v>2.749719456570111e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.749719456570115e-05</v>
+        <v>2.749719456570111e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.796308529458916e-05</v>
+        <v>2.796308529458915e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.806213287941102e-05</v>
+        <v>2.806213287941095e-05</v>
       </c>
       <c r="I5" t="n">
         <v>2.742493515804168e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.806213287941102e-05</v>
+        <v>2.806213287941095e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.806213287941102e-05</v>
+        <v>2.806213287941095e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.806213287941102e-05</v>
+        <v>2.806213287941095e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.689622580389604e-05</v>
+        <v>6.689622580389599e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001047697913049728</v>
+        <v>0.0001047697913051804</v>
       </c>
       <c r="D6" t="n">
         <v>0.0001125464406348486</v>
       </c>
       <c r="E6" t="n">
-        <v>9.380376688899454e-05</v>
+        <v>9.380376688899456e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>6.750552406497654e-05</v>
+        <v>6.750552406497646e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001046072320737707</v>
+        <v>0.0001046072320737706</v>
       </c>
       <c r="H6" t="n">
-        <v>0.000104706279658733</v>
+        <v>0.0001047062796587331</v>
       </c>
       <c r="I6" t="n">
-        <v>0.000104069081937223</v>
+        <v>0.0001040690819372231</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001047137104157147</v>
+        <v>0.0001047137104157146</v>
       </c>
       <c r="K6" t="n">
-        <v>6.619388464197318e-05</v>
+        <v>6.61938846419731e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001442020425335729</v>
+        <v>0.0001442020425335728</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.791924133717753e-05</v>
+        <v>7.791924133717752e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>9.740128148733339e-05</v>
+        <v>9.740128148733318e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>9.742467268450541e-05</v>
+        <v>9.742467268450536e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000119296307145099</v>
+        <v>0.0001192963071450988</v>
       </c>
       <c r="F7" t="n">
-        <v>9.678745735433716e-05</v>
+        <v>9.678745735433709e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>9.73256253251555e-05</v>
+        <v>9.73256253251553e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>9.742467290997722e-05</v>
+        <v>9.74246729099772e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>9.678747518860795e-05</v>
+        <v>9.678747518860788e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>9.742467290997722e-05</v>
+        <v>9.74246729099772e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>7.286385291107957e-05</v>
+        <v>8.56646320727007e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>9.742467290997722e-05</v>
+        <v>9.74246729099772e-05</v>
       </c>
     </row>
     <row r="8">
@@ -2339,34 +2339,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.286895710624507e-06</v>
+        <v>7.286895710624502e-06</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.065112580803956e-05</v>
+        <v>-1.065112580803959e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>5.645784548414467e-06</v>
+        <v>5.64578454841445e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>1.340215330119992e-05</v>
+        <v>1.340215330119991e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.340215330119992e-05</v>
+        <v>1.340215330119991e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>3.152068940621382e-06</v>
+        <v>3.152068940621349e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>-6.83791053939668e-07</v>
+        <v>-6.837910539396596e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.340215330119992e-05</v>
+        <v>1.340215330119991e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>9.241342402308792e-06</v>
+        <v>9.241342402308745e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>1.276296446128591e-05</v>
+        <v>1.27629644612859e-05</v>
       </c>
       <c r="L8" t="n">
         <v>1.06423519414396e-05</v>
@@ -2379,34 +2379,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.263613452194655e-06</v>
+        <v>8.263613452194674e-06</v>
       </c>
       <c r="C9" t="n">
-        <v>3.674728272220228e-06</v>
+        <v>3.674728272220222e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>1.043267619358147e-05</v>
+        <v>1.043267619358144e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.414139487607294e-05</v>
+        <v>1.414139487607292e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.414139487607294e-05</v>
+        <v>1.414139487607292e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>8.630851052868034e-06</v>
+        <v>8.630851052868014e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>7.868101100630888e-06</v>
+        <v>7.868101100630875e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>1.414139487607294e-05</v>
+        <v>1.414139487607292e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>1.414770746548134e-05</v>
+        <v>1.414770746548133e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.339977897440081e-05</v>
+        <v>1.339977897440083e-05</v>
       </c>
       <c r="L9" t="n">
         <v>1.190783628544543e-05</v>
@@ -2495,34 +2495,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.488604145089552e-05</v>
+        <v>4.488604145089558e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>6.465742919179265e-05</v>
+        <v>6.465742919179273e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0004018851405982603</v>
+        <v>0.0004018851405982591</v>
       </c>
       <c r="E2" t="n">
-        <v>8.007503068300615e-05</v>
+        <v>8.007503068300592e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>8.007503068300615e-05</v>
+        <v>8.007503068300592e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008298795636990561</v>
+        <v>0.0008298795636990617</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001989710194278257</v>
+        <v>0.001989710194278254</v>
       </c>
       <c r="I2" t="n">
-        <v>8.007503068300615e-05</v>
+        <v>8.007503068300592e-05</v>
       </c>
       <c r="J2" t="n">
         <v>0.002044132191766197</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008910405209275345</v>
+        <v>0.0008910405209275354</v>
       </c>
       <c r="L2" t="n">
         <v>0.001112486247866451</v>
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.837349270442108e-06</v>
+        <v>9.837349270442137e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>9.127457633658473e-06</v>
+        <v>9.127457633658525e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>9.837349270442108e-06</v>
+        <v>9.837349270442137e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>8.901643950412475e-06</v>
+        <v>8.901643950412474e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>8.901643950412479e-06</v>
+        <v>8.901643950412472e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>9.724297015790771e-06</v>
+        <v>9.724297015790779e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>9.837349270442108e-06</v>
+        <v>9.837349270442137e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>9.110436095070207e-06</v>
+        <v>9.110436095070172e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>9.837349270442108e-06</v>
+        <v>9.837349270442137e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>9.837349270442108e-06</v>
+        <v>9.837349270442137e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>9.837349270442108e-06</v>
+        <v>9.837349270442137e-06</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.415910374172885e-05</v>
+        <v>1.415910374172894e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.284821807415053e-05</v>
+        <v>1.284821807415048e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.384719156960469e-05</v>
+        <v>1.38472194813548e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.202439717600044e-05</v>
+        <v>1.202439717600041e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.335268050129524e-05</v>
+        <v>1.335268050129527e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.404605148707751e-05</v>
+        <v>1.404605148707756e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.881930607923921e-05</v>
+        <v>2.88193060792393e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.343219056635694e-05</v>
+        <v>2.62810688703959e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.775250432368674e-05</v>
+        <v>1.521486260132705e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.483065615087983e-05</v>
+        <v>1.483065615087982e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.447982425232473e-05</v>
+        <v>1.447982425232475e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.863322194401423e-05</v>
+        <v>2.863322194401431e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.856438685456268e-05</v>
+        <v>2.856438685456274e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.862468940715677e-05</v>
+        <v>2.862468940715691e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.799765540860317e-05</v>
+        <v>2.79976554086032e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.799765540860317e-05</v>
+        <v>2.79976554086032e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.85201696893629e-05</v>
+        <v>2.852016968936293e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.863322194401423e-05</v>
+        <v>2.863322194401431e-05</v>
       </c>
       <c r="I5" t="n">
         <v>2.790630876864234e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.863322194401423e-05</v>
+        <v>2.863322194401431e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.863322194401423e-05</v>
+        <v>2.863322194401431e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.863322194401423e-05</v>
+        <v>2.863322194401431e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.014954436148243e-05</v>
+        <v>7.014954436148254e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001109760058526557</v>
+        <v>0.0001109760058527498</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001193966754686251</v>
+        <v>0.0001193966754686252</v>
       </c>
       <c r="E6" t="n">
-        <v>9.914891695651627e-05</v>
+        <v>9.914891695651643e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>7.077516926998523e-05</v>
+        <v>7.077516926998536e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001108257126227951</v>
+        <v>0.0001108257126227953</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001109387648774597</v>
+        <v>0.0001109387648774599</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001102118517020745</v>
+        <v>0.0001102118517020746</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001109467811293699</v>
+        <v>0.00011094678112937</v>
       </c>
       <c r="K6" t="n">
-        <v>6.939186364913302e-05</v>
+        <v>6.939186364913315e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001535465164467378</v>
+        <v>0.0001535465164467381</v>
       </c>
     </row>
     <row r="7">
@@ -2695,19 +2695,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.819109187134984e-05</v>
+        <v>9.819109187134972e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001236309392289296</v>
+        <v>0.0001236309392289293</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001236997775224396</v>
+        <v>0.0001236997775224394</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001524093083138257</v>
+        <v>0.0001524093083138256</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001229728336245097</v>
+        <v>0.0001229728336245096</v>
       </c>
       <c r="G7" t="n">
         <v>0.0001235867220637296</v>
@@ -2716,13 +2716,13 @@
         <v>0.000123699774318381</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001229728611430091</v>
+        <v>0.000122972861143009</v>
       </c>
       <c r="J7" t="n">
         <v>0.000123699774318381</v>
       </c>
       <c r="K7" t="n">
-        <v>9.157978900347667e-05</v>
+        <v>0.0001089199448758951</v>
       </c>
       <c r="L7" t="n">
         <v>0.000123699774318381</v>
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.196166291638997e-06</v>
+        <v>9.196166291639008e-06</v>
       </c>
       <c r="C8" t="n">
-        <v>9.994870742411489e-06</v>
+        <v>9.994870742411503e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>4.644187887908977e-06</v>
+        <v>4.644187887909004e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>1.289375656658076e-05</v>
+        <v>1.289375656658078e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.289375656658076e-05</v>
+        <v>1.289375656658078e-05</v>
       </c>
       <c r="G8" t="n">
         <v>-4.960218635225995e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.666815050414508e-05</v>
+        <v>-2.666815050414504e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.289375656658076e-05</v>
+        <v>1.289375656658078e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.516752957764005e-05</v>
+        <v>-2.516752957763999e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.533208640291102e-06</v>
+        <v>-2.533208640291087e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>-8.90652263070942e-06</v>
+        <v>-8.906522630709396e-06</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.581330294689218e-06</v>
+        <v>9.581330294689221e-06</v>
       </c>
       <c r="C9" t="n">
         <v>1.038798678154147e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>9.636233938751678e-06</v>
+        <v>9.636233938751682e-06</v>
       </c>
       <c r="E9" t="n">
-        <v>1.345936734419826e-05</v>
+        <v>1.345936734419825e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.345936734419826e-05</v>
+        <v>1.345936734419825e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>5.578654252742992e-06</v>
+        <v>5.57865425274298e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.080114475783121e-06</v>
+        <v>-3.080114475783112e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>1.345936734419826e-05</v>
+        <v>1.345936734419825e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>8.40943920324098e-07</v>
+        <v>8.40943920324087e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>9.04640901972986e-06</v>
+        <v>9.046409019729837e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>3.810551452290226e-06</v>
+        <v>3.810551452290242e-06</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.242629805913573e-05</v>
+        <v>4.242629805913569e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>6.364876402139405e-05</v>
+        <v>6.364876402139399e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>7.816799584446066e-05</v>
+        <v>7.816799584446071e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>7.147146719400731e-05</v>
+        <v>7.147146719400688e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>7.147146719400731e-05</v>
+        <v>7.147146719400688e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001106994204780368</v>
+        <v>0.0001106994204780353</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000161370800242507</v>
+        <v>0.0001613708002425069</v>
       </c>
       <c r="I2" t="n">
-        <v>7.147146719400731e-05</v>
+        <v>7.147146719400688e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0005393588531035167</v>
+        <v>0.0005393588531035166</v>
       </c>
       <c r="K2" t="n">
-        <v>5.938448522400905e-05</v>
+        <v>5.9384485224009e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001797121980093141</v>
+        <v>0.0001797121980093142</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.384536544944543e-06</v>
+        <v>8.384536544944514e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>8.236465837971596e-06</v>
+        <v>8.236465837971622e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.384536544944543e-06</v>
+        <v>8.384536544944514e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>8.157893919842847e-06</v>
+        <v>8.157893919842854e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>8.157893919842847e-06</v>
+        <v>8.157893919842852e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.295997780204828e-06</v>
+        <v>8.295997780204838e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>8.384536544944543e-06</v>
+        <v>8.384536544944514e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.813692539055858e-06</v>
+        <v>7.813692539055843e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>8.384536544944543e-06</v>
+        <v>8.384536544944514e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>8.384536544944543e-06</v>
+        <v>8.384536544944514e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>8.384536544944543e-06</v>
+        <v>8.384536544944514e-06</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.069867130908953e-05</v>
+        <v>1.069867130908958e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.05166026752022e-05</v>
+        <v>1.051660267520216e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.069776166772178e-05</v>
+        <v>2.055832298194946e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>9.919606955658816e-06</v>
+        <v>9.919606955658811e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>1.015807964063274e-05</v>
+        <v>1.01580796406328e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.981638634832332e-05</v>
+        <v>1.061013254434987e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.143873324520663e-05</v>
+        <v>2.143873324520656e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.933408110717435e-05</v>
+        <v>1.933408110717414e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.111363874808802e-05</v>
+        <v>2.050791922019393e-05</v>
       </c>
       <c r="K4" t="n">
         <v>1.06823735330466e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.073965016353539e-05</v>
+        <v>1.073965016353538e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.351252422654254e-05</v>
+        <v>2.351252422654252e-05</v>
       </c>
       <c r="C5" t="n">
         <v>2.347579423339498e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.350445047179571e-05</v>
+        <v>2.350445047179568e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.307601119519345e-05</v>
+        <v>2.307601119519342e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.307601119519345e-05</v>
+        <v>2.307601119519342e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.342398546180286e-05</v>
+        <v>2.342398546180283e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.351252422654254e-05</v>
+        <v>2.351252422654252e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.294168022065384e-05</v>
+        <v>2.294168022065391e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.351252422654254e-05</v>
+        <v>2.351252422654252e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.351252422654254e-05</v>
+        <v>2.351252422654252e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.351252422654254e-05</v>
+        <v>2.351252422654252e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3054,34 +3054,34 @@
         <v>6.050999025028815e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>9.557001297519489e-05</v>
+        <v>9.557001297509007e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001027086511858812</v>
+        <v>0.0001027086511858814</v>
       </c>
       <c r="E6" t="n">
-        <v>8.545944167149267e-05</v>
+        <v>8.545944167149259e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>6.113199932462829e-05</v>
+        <v>6.113199932462803e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>9.537273590932074e-05</v>
+        <v>9.537273590932075e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>9.546127467411521e-05</v>
+        <v>9.54612746741151e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>9.489043066817172e-05</v>
+        <v>9.489043066817156e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>9.546814360432476e-05</v>
+        <v>9.546814360432488e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.986075219800999e-05</v>
+        <v>5.986075219801001e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001319708138349819</v>
+        <v>0.0001319708138349817</v>
       </c>
     </row>
     <row r="7">
@@ -3094,34 +3094,34 @@
         <v>7.211384843238426e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>9.049889277947954e-05</v>
+        <v>9.049889277947937e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>9.053562519907029e-05</v>
+        <v>9.053562519907018e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001112231116610935</v>
+        <v>0.0001112231116610934</v>
       </c>
       <c r="F7" t="n">
-        <v>8.996477374024038e-05</v>
+        <v>8.996477374024044e-05</v>
       </c>
       <c r="G7" t="n">
         <v>9.044708400788733e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>9.053562277262702e-05</v>
+        <v>9.053562277262688e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.996477876673825e-05</v>
+        <v>8.996477876673832e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>9.053562277262702e-05</v>
+        <v>9.053562277262688e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>6.733931997433118e-05</v>
+        <v>7.986197539258555e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>9.053562277262702e-05</v>
+        <v>9.053562277262688e-05</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.147139626645104e-06</v>
+        <v>8.14713962664509e-06</v>
       </c>
       <c r="C8" t="n">
-        <v>8.638623041448192e-06</v>
+        <v>8.638623041448185e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>1.036156578322373e-05</v>
+        <v>1.036156578322371e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.143647752318735e-05</v>
+        <v>1.143647752318736e-05</v>
       </c>
       <c r="F8" t="n">
         <v>1.143647752318735e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.602708949150924e-06</v>
+        <v>8.602708949150912e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>8.750327940326888e-06</v>
+        <v>8.750327940326893e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>1.143647752318735e-05</v>
+        <v>1.143647752318736e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>3.457333982136706e-06</v>
+        <v>3.457333982136705e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>1.13833098776577e-05</v>
+        <v>1.138330987765744e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>7.590048111066766e-06</v>
+        <v>7.590048111066774e-06</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.538658100091752e-06</v>
+        <v>8.538658100091747e-06</v>
       </c>
       <c r="C9" t="n">
-        <v>9.084671292744868e-06</v>
+        <v>9.084671292744855e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>1.100374108295632e-05</v>
+        <v>1.100374108295631e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.196651774854836e-05</v>
+        <v>1.196651774854835e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.196651774854836e-05</v>
+        <v>1.196651774854835e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>9.696443655477475e-06</v>
+        <v>9.696443655477414e-06</v>
       </c>
       <c r="H9" t="n">
         <v>1.035013480018333e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.196651774854836e-05</v>
+        <v>1.196651774854835e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>1.033263171224548e-05</v>
+        <v>1.033263171224546e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.174246830437934e-05</v>
+        <v>1.174246830437909e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>9.39434410820668e-06</v>
+        <v>9.39434410820667e-06</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.1709497034567e-05</v>
+        <v>4.170949703456696e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>6.564560715821162e-05</v>
+        <v>6.564560715821159e-05</v>
       </c>
       <c r="D2" t="n">
         <v>7.588601361327199e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>6.663111812640797e-05</v>
+        <v>6.663111812640805e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>6.663111812640797e-05</v>
+        <v>6.663111812640805e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>7.120098169542761e-05</v>
+        <v>7.120098169542848e-05</v>
       </c>
       <c r="H2" t="n">
         <v>8.786367362065479e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>6.663111812640797e-05</v>
+        <v>6.663111812640805e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>8.104780116268095e-05</v>
+        <v>8.10478011626809e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>5.848691758886718e-05</v>
+        <v>5.848691758886705e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>7.486548857938447e-05</v>
+        <v>7.486548857938441e-05</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.408881705338213e-06</v>
+        <v>8.408881705338018e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>8.306435898245094e-06</v>
+        <v>8.306435898245113e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.408881705338213e-06</v>
+        <v>8.408881705338018e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>8.123566143127667e-06</v>
+        <v>8.123566143127685e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>8.123566143127667e-06</v>
+        <v>8.123566143127685e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.32138083824887e-06</v>
+        <v>8.321380838247115e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>8.408881705338213e-06</v>
+        <v>8.408881705338018e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.84485086415707e-06</v>
+        <v>7.844850864155464e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>8.408881705338213e-06</v>
+        <v>8.408881705338018e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>8.408881705338213e-06</v>
+        <v>8.408881705338018e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>8.408881705338213e-06</v>
+        <v>8.408881705338018e-06</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.975337388189956e-05</v>
+        <v>1.975337388189941e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.0412263373592e-05</v>
+        <v>1.041226337359198e-05</v>
       </c>
       <c r="D4" t="n">
         <v>1.057337240111272e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>9.807059477730656e-06</v>
+        <v>9.807059477730693e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>9.997386805844886e-06</v>
+        <v>9.997386805845007e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.966587301480876e-05</v>
+        <v>1.966587301480872e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.138318543600235e-05</v>
+        <v>1.054007395468282e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>9.967851066869268e-06</v>
+        <v>1.918934304071686e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.036389300647234e-05</v>
+        <v>1.078805997923003e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.056506196927122e-05</v>
+        <v>1.056506196927127e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.054191449098957e-05</v>
+        <v>1.054191449098941e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.313647412253267e-05</v>
+        <v>2.313647412253273e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.310110661808772e-05</v>
+        <v>2.310110661808776e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.312839945099949e-05</v>
+        <v>2.312839945099954e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.268750861498309e-05</v>
+        <v>2.268750861498315e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.268750861498309e-05</v>
+        <v>2.268750861498315e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.304897325544187e-05</v>
+        <v>2.304897325544182e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.313647412253267e-05</v>
+        <v>2.313647412253273e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.257244328134998e-05</v>
+        <v>2.257244328135003e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.313647412253267e-05</v>
+        <v>2.313647412253273e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.313647412253267e-05</v>
+        <v>2.313647412253273e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.313647412253267e-05</v>
+        <v>2.313647412253273e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.99198757860961e-05</v>
+        <v>5.991987578609595e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>9.455327574655274e-05</v>
+        <v>9.455327574669429e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001016240919801444</v>
+        <v>0.0001016240919801443</v>
       </c>
       <c r="E6" t="n">
-        <v>8.456207647664606e-05</v>
+        <v>8.456207647664612e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>6.052422431836452e-05</v>
+        <v>6.052422431836457e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>9.437413263251768e-05</v>
+        <v>9.437413263251782e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>9.446163349968251e-05</v>
+        <v>9.446163349968259e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>9.389760265842578e-05</v>
+        <v>9.389760265842581e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>9.446842194500096e-05</v>
+        <v>9.446842194500074e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.927824490277949e-05</v>
+        <v>5.927824490277946e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000130543387766628</v>
+        <v>0.0001305433877666282</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.737987708167036e-05</v>
+        <v>6.737987708167044e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>8.444203159510621e-05</v>
+        <v>8.444203159510636e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>8.447740123165096e-05</v>
+        <v>8.447740123165102e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001036435429506323</v>
+        <v>0.0001036435429506324</v>
       </c>
       <c r="F7" t="n">
-        <v>8.391336416411829e-05</v>
+        <v>8.39133641641184e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>8.438989823246042e-05</v>
+        <v>8.438989823246049e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>8.447739909955124e-05</v>
+        <v>8.447739909955119e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.391336825836854e-05</v>
+        <v>8.391336825836859e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>8.447739909955124e-05</v>
+        <v>8.447739909955119e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>7.416911454038399e-05</v>
+        <v>7.457102859202718e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>8.447739909955124e-05</v>
+        <v>8.447739909955119e-05</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.454334262968722e-06</v>
+        <v>8.45433426296871e-06</v>
       </c>
       <c r="C8" t="n">
-        <v>8.413286332023254e-06</v>
+        <v>8.413286332023273e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>1.016656403068618e-05</v>
+        <v>1.016656403068619e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.121422514896351e-05</v>
+        <v>1.121422514896354e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.121422514896351e-05</v>
+        <v>1.121422514896354e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>9.272532349194825e-06</v>
+        <v>9.272532349194788e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>1.008135087582718e-05</v>
+        <v>1.008135087582716e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.121422514896351e-05</v>
+        <v>1.121422514896354e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.333351312220007e-05</v>
+        <v>1.33335131222001e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.108120669521147e-05</v>
+        <v>1.108120669521146e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>9.522001445174514e-06</v>
+        <v>9.52200144517456e-06</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.830560679853696e-06</v>
+        <v>8.830560679853711e-06</v>
       </c>
       <c r="C9" t="n">
-        <v>8.889379638252896e-06</v>
+        <v>8.889379638252911e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>1.077917709054967e-05</v>
+        <v>1.077917709054974e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.167994529404962e-05</v>
+        <v>1.167994529404965e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.167994529404962e-05</v>
+        <v>1.167994529404965e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>9.815363788981071e-06</v>
+        <v>9.815363788981036e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>1.074564087201838e-05</v>
+        <v>1.07456408720183e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.167994529404962e-05</v>
+        <v>1.167994529404965e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>1.392338544916648e-05</v>
+        <v>1.392338544916651e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.143202489780499e-05</v>
+        <v>1.143202489780492e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.0017717224332e-05</v>
+        <v>1.001771722433195e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.206577201481813e-05</v>
+        <v>4.206577201481754e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>6.249337621558359e-05</v>
+        <v>6.249337621558352e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001209003134259545</v>
+        <v>0.0001209003134259541</v>
       </c>
       <c r="E2" t="n">
-        <v>7.646237682789606e-05</v>
+        <v>7.646237682789581e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>7.646237682789606e-05</v>
+        <v>7.646237682789581e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.000286839491255016</v>
+        <v>0.0002868394912550191</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001641971716401323</v>
+        <v>0.001641971716401324</v>
       </c>
       <c r="I2" t="n">
-        <v>7.646237682789606e-05</v>
+        <v>7.646237682789581e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>7.273090013936939e-05</v>
+        <v>7.273090013936913e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>6.173354071636963e-05</v>
+        <v>6.173354071636951e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000895127414584071</v>
+        <v>0.0008951274145840708</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.758641130132877e-06</v>
+        <v>8.758641130132314e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>8.452798056970307e-06</v>
+        <v>8.452798056970317e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.758641130132877e-06</v>
+        <v>8.758641130132314e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>8.357090327189433e-06</v>
+        <v>8.357090327189364e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>8.357090327189435e-06</v>
+        <v>8.357090327189372e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.663944417741398e-06</v>
+        <v>8.663944417741929e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>8.758641130132877e-06</v>
+        <v>8.758641130132314e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>8.148391219056495e-06</v>
+        <v>8.148391219056512e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>8.758641130132877e-06</v>
+        <v>8.758641130132314e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>8.758641130132877e-06</v>
+        <v>8.758641130132314e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>8.758641130132877e-06</v>
+        <v>8.758641130132314e-06</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.123684487920267e-05</v>
+        <v>1.123684487920104e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.079152798402918e-05</v>
+        <v>1.079152798402913e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.111206838568608e-05</v>
+        <v>1.111206838568605e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.018629367405906e-05</v>
+        <v>1.018629367405896e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.063122640564941e-05</v>
+        <v>1.063122640564931e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>2.199722928041894e-05</v>
+        <v>1.114214816681067e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.385781247096668e-05</v>
+        <v>2.385781247096673e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>2.148167608173431e-05</v>
+        <v>1.062659496812556e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.277631423414185e-05</v>
+        <v>1.152437620571393e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.101157146511388e-05</v>
+        <v>1.101157146511353e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.14928787490767e-05</v>
+        <v>1.149287874907688e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.530065490494581e-05</v>
+        <v>2.530065490494614e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.52563578185384e-05</v>
+        <v>2.525635781853837e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.529213318252393e-05</v>
+        <v>2.529213318252287e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.481233750126748e-05</v>
+        <v>2.481233750126744e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.481233750126748e-05</v>
+        <v>2.481233750126744e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.520595819255506e-05</v>
+        <v>2.520595819255454e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.530065490494581e-05</v>
+        <v>2.530065490494614e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.469040499387004e-05</v>
+        <v>2.469040499387009e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.530065490494581e-05</v>
+        <v>2.530065490494614e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.530065490494581e-05</v>
+        <v>2.530065490494614e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.530065490494581e-05</v>
+        <v>2.530065490494614e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.497733669490683e-05</v>
+        <v>6.497733669490692e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001028264007099777</v>
+        <v>0.0001028264007098941</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001105654946712359</v>
+        <v>0.0001105654946712364</v>
       </c>
       <c r="E6" t="n">
-        <v>9.191724101985907e-05</v>
+        <v>9.191724101985901e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>6.564180012034866e-05</v>
+        <v>6.564180012034857e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001026412948890563</v>
+        <v>0.0001026412948890555</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001027359916014572</v>
+        <v>0.0001027359916014571</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001021257416903714</v>
+        <v>0.0001021257416903712</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001027434122607912</v>
+        <v>0.000102743412260791</v>
       </c>
       <c r="K6" t="n">
-        <v>6.427595029460573e-05</v>
+        <v>6.427595029460554e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001421780639802962</v>
+        <v>0.0001421780639802952</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.485050932649239e-05</v>
+        <v>8.485050932649186e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001067368392955384</v>
+        <v>0.0001067368392955383</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001067811249744176</v>
+        <v>0.0001067811249744169</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000131478323926355</v>
+        <v>0.0001314783239263548</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000106170861790839</v>
+        <v>0.0001061708617908389</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001066864396695552</v>
+        <v>0.0001066864396695544</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001067811363819462</v>
+        <v>0.0001067811363819463</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001061708864708704</v>
+        <v>0.0001061708864708699</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001067811363819462</v>
+        <v>0.0001067811363819463</v>
       </c>
       <c r="K7" t="n">
-        <v>9.407444013987104e-05</v>
+        <v>9.407444013987044e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001067811363819462</v>
+        <v>0.0001067811363819463</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.489426980237547e-06</v>
+        <v>8.489426980237255e-06</v>
       </c>
       <c r="C8" t="n">
-        <v>9.08230895752746e-06</v>
+        <v>9.082308957527441e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>9.876147962468436e-06</v>
+        <v>9.876147962468649e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>1.160351971524696e-05</v>
+        <v>1.160351971524694e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.160351971524696e-05</v>
+        <v>1.160351971524694e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>5.28719646686423e-06</v>
+        <v>5.287196466863811e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.084060329792335e-05</v>
+        <v>-2.084060329792328e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.160351971524696e-05</v>
+        <v>1.160351971524694e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.447509925473382e-05</v>
+        <v>1.447509925473387e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.177614177881263e-05</v>
+        <v>1.177614177881232e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.91556308733517e-06</v>
+        <v>-5.915563087335285e-06</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.845475791232939e-06</v>
+        <v>8.845475791232667e-06</v>
       </c>
       <c r="C9" t="n">
-        <v>9.463900065925746e-06</v>
+        <v>9.463900065925753e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>1.104208810115461e-05</v>
+        <v>1.104208810115447e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.214737595037491e-05</v>
+        <v>1.21473759503749e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.214737595037491e-05</v>
+        <v>1.21473759503749e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>8.637659412456956e-06</v>
+        <v>8.637659412457017e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.438105086129491e-06</v>
+        <v>-1.438105086129606e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>1.214737595037491e-05</v>
+        <v>1.21473759503749e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>1.488924159382163e-05</v>
+        <v>1.488924159382167e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.212076032437475e-05</v>
+        <v>1.212076032437425e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.247354906380177e-06</v>
+        <v>4.247354906380113e-06</v>
       </c>
     </row>
   </sheetData>
@@ -4079,34 +4079,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.275446545046725e-05</v>
+        <v>4.275446545046721e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>6.478184777399779e-05</v>
+        <v>6.478184777399776e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>7.633969726299379e-05</v>
+        <v>7.633969726299363e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>7.263516237281815e-05</v>
+        <v>7.263516237281823e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>7.263516237281815e-05</v>
+        <v>7.263516237281823e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>7.150708273395939e-05</v>
+        <v>7.150708273395795e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>8.967227876163967e-05</v>
+        <v>8.967227876163955e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>7.263516237281815e-05</v>
+        <v>7.263516237281823e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>8.23124082050743e-05</v>
+        <v>8.231240820507423e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>6.091754624970526e-05</v>
+        <v>6.09175462497052e-05</v>
       </c>
       <c r="L2" t="n">
         <v>7.285576828711251e-05</v>
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.219336646490663e-06</v>
+        <v>8.219336646490697e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>8.10823115666213e-06</v>
+        <v>8.108231156662111e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.219336646490663e-06</v>
+        <v>8.219336646490697e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>8.147208670730103e-06</v>
+        <v>8.147208670730131e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>8.147208670730104e-06</v>
+        <v>8.147208670730131e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.132456939982428e-06</v>
+        <v>8.132456939982442e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>8.219336646490663e-06</v>
+        <v>8.219336646490697e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.659014803274077e-06</v>
+        <v>7.659014803274133e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>8.219336646490663e-06</v>
+        <v>8.219336646490697e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>8.219336646490663e-06</v>
+        <v>8.219336646490697e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>8.219336646490663e-06</v>
+        <v>8.219336646490697e-06</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.038255428845853e-05</v>
+        <v>1.950091279287834e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.025884062545075e-05</v>
+        <v>1.025884062545063e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.042266885391731e-05</v>
+        <v>1.04226810312584e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>9.705273735329579e-06</v>
+        <v>9.705273735329606e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>9.865986649219224e-06</v>
+        <v>9.865986649219194e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.02956745819503e-05</v>
+        <v>1.029567458195023e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.095699622042962e-05</v>
+        <v>2.095699622042968e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.894059094966182e-05</v>
+        <v>1.894059094966178e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.009027210122338e-05</v>
+        <v>1.063198181937486e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.042196394172248e-05</v>
+        <v>1.042196394172243e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.039035630542605e-05</v>
+        <v>1.039035630542607e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.270303745590701e-05</v>
+        <v>2.2703037455907e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.266837405259821e-05</v>
+        <v>2.266837405259814e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.269496678122513e-05</v>
+        <v>2.269496678122508e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.231142153777009e-05</v>
+        <v>2.231142153777007e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.231142153777009e-05</v>
+        <v>2.231142153777007e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.26161577493988e-05</v>
+        <v>2.261615774939872e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.270303745590701e-05</v>
+        <v>2.2703037455907e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.214271561269042e-05</v>
+        <v>2.214271561269041e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.270303745590701e-05</v>
+        <v>2.2703037455907e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.270303745590701e-05</v>
+        <v>2.2703037455907e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.270303745590701e-05</v>
+        <v>2.2703037455907e-05</v>
       </c>
     </row>
     <row r="6">
@@ -4242,34 +4242,34 @@
         <v>5.913340439749087e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>9.336546796566874e-05</v>
+        <v>9.33654679656686e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001002904671242644</v>
+        <v>0.0001002904671242642</v>
       </c>
       <c r="E6" t="n">
-        <v>8.349584005451805e-05</v>
+        <v>8.349584005451789e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>5.975909355775101e-05</v>
+        <v>5.975909355775106e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>9.313509938787646e-05</v>
+        <v>9.313509938787667e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>9.322197909442398e-05</v>
+        <v>9.322197909442382e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>9.266165725116846e-05</v>
+        <v>9.266165725116832e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>9.322867847686677e-05</v>
+        <v>9.322867847686655e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.850019162136394e-05</v>
+        <v>5.850019162136398e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001288303458063734</v>
+        <v>0.0001288303458063733</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.0774747394638e-05</v>
+        <v>7.077474739463785e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>8.87967279160831e-05</v>
+        <v>8.879672791608297e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>8.88313932996455e-05</v>
+        <v>8.883139329964534e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001091080507129411</v>
+        <v>0.000109108050712941</v>
       </c>
       <c r="F7" t="n">
-        <v>8.827106565224995e-05</v>
+        <v>8.827106565224989e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>8.87445116128836e-05</v>
+        <v>8.87445116128835e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>8.883139131939184e-05</v>
+        <v>8.88313913193917e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.827106947617517e-05</v>
+        <v>8.827106947617512e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>8.883139131939184e-05</v>
+        <v>8.88313913193917e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>7.836930174839685e-05</v>
+        <v>6.609485300538803e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>8.883139131939184e-05</v>
+        <v>8.88313913193917e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.021045601403529e-05</v>
+        <v>1.021045601403524e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.475244155910028e-06</v>
+        <v>8.475244155910026e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>9.983262884756856e-06</v>
+        <v>9.983262884756833e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>1.099118639784656e-05</v>
+        <v>1.099118639784653e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.099118639784656e-05</v>
+        <v>1.099118639784653e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>9.396303646650139e-06</v>
+        <v>9.396303646650133e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>9.870447061872597e-06</v>
+        <v>9.87044706187257e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>1.099118639784656e-05</v>
+        <v>1.099118639784653e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.305718758011002e-05</v>
+        <v>1.305718758011e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.120462770066053e-05</v>
+        <v>1.120462770066043e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>9.444062009579371e-06</v>
+        <v>9.444062009579363e-06</v>
       </c>
     </row>
     <row r="9">
@@ -4362,34 +4362,34 @@
         <v>1.057458301984703e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>8.939420908046034e-06</v>
+        <v>8.939420908046026e-06</v>
       </c>
       <c r="D9" t="n">
         <v>1.060684046011682e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.154583738684084e-05</v>
+        <v>1.154583738684082e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.154583738684084e-05</v>
+        <v>1.154583738684082e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>9.943049199424345e-06</v>
+        <v>9.943049199424319e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>1.056209968145312e-05</v>
+        <v>1.05620996814531e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.154583738684084e-05</v>
+        <v>1.154583738684082e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>1.366994813148861e-05</v>
+        <v>1.366994813148856e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.158929780206399e-05</v>
+        <v>1.158929780206394e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>9.918051158321869e-06</v>
+        <v>9.918051158321854e-06</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.124780401014429e-05</v>
+        <v>4.124780401014417e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>6.505364350951311e-05</v>
+        <v>6.505364350951293e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>7.386615508702616e-05</v>
+        <v>7.3866155087026e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>6.743636250185749e-05</v>
+        <v>6.743636250185748e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>6.743636250185749e-05</v>
+        <v>6.743636250185748e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>7.045924925553156e-05</v>
+        <v>7.045924925553141e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>8.806745098806643e-05</v>
+        <v>8.806745098806616e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>6.743636250185749e-05</v>
+        <v>6.743636250185748e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>8.289557606563393e-05</v>
+        <v>8.28955760656337e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>5.933441718158613e-05</v>
+        <v>5.93344171815861e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>7.35632238321238e-05</v>
+        <v>7.356322383212379e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.348576811218501e-06</v>
+        <v>8.348576811218459e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>8.282875548254064e-06</v>
+        <v>8.282875548254054e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.348576811218501e-06</v>
+        <v>8.348576811218459e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>8.132768829225821e-06</v>
+        <v>8.132768829225874e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>8.132768829225821e-06</v>
+        <v>8.132768829225876e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.261063131443415e-06</v>
+        <v>8.261063131443364e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>8.348576811218501e-06</v>
+        <v>8.348576811218459e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.784426986966718e-06</v>
+        <v>7.784426986966763e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>8.348576811218503e-06</v>
+        <v>8.348576811218459e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>8.348576811218501e-06</v>
+        <v>8.348576811218459e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>8.348576811218501e-06</v>
+        <v>8.348576811218459e-06</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.056217446711286e-05</v>
+        <v>1.97748412846158e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.044884985329109e-05</v>
+        <v>1.044884985329107e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.060278824804411e-05</v>
+        <v>1.060277468786758e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>9.84619256729853e-06</v>
+        <v>9.846192567298648e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>1.00325723583843e-05</v>
+        <v>1.003257235838465e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.968732760484073e-05</v>
+        <v>1.047466078733772e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.137201614508208e-05</v>
+        <v>2.137201614508207e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.921069146036403e-05</v>
+        <v>9.998024642861138e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.081666058731321e-05</v>
+        <v>2.039043499273463e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.060271776147425e-05</v>
+        <v>1.06027177614742e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.057251079618566e-05</v>
+        <v>1.05725107961873e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.261385007300737e-05</v>
+        <v>2.261385007300729e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.257851165847219e-05</v>
+        <v>2.257851165847207e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.260577611710754e-05</v>
+        <v>2.260577611710755e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.218521310677634e-05</v>
+        <v>2.218521310677641e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.218521310677634e-05</v>
+        <v>2.218521310677641e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.252633639323228e-05</v>
+        <v>2.252633639323227e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.261385007300737e-05</v>
+        <v>2.261385007300729e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.204970024875596e-05</v>
+        <v>2.204970024875564e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.261385007300737e-05</v>
+        <v>2.261385007300729e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.261385007300737e-05</v>
+        <v>2.261385007300729e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.261385007300737e-05</v>
+        <v>2.261385007300729e-05</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.889182917449839e-05</v>
+        <v>5.889182917449825e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>9.287545853542765e-05</v>
+        <v>9.287545853527773e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>9.978805890121382e-05</v>
+        <v>9.978805890121366e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>8.306507662094528e-05</v>
+        <v>8.306507662094489e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>5.94870430146218e-05</v>
+        <v>5.948704301462155e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>9.26768537542794e-05</v>
+        <v>9.267685375427944e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>9.276436743412198e-05</v>
+        <v>9.276436743412174e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>9.220021760980311e-05</v>
+        <v>9.220021760980275e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>9.277102435801865e-05</v>
+        <v>9.277102435801834e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.826262938618041e-05</v>
+        <v>5.826262938618028e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001281470660215938</v>
+        <v>0.0001281470660215936</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.690048423342942e-05</v>
+        <v>6.69004842334293e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>8.382312083306695e-05</v>
+        <v>8.38231208330669e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>8.385846121902868e-05</v>
+        <v>8.385846121902866e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001028634501466552</v>
+        <v>0.0001028634501466549</v>
       </c>
       <c r="F7" t="n">
-        <v>8.329430569685278e-05</v>
+        <v>8.329430569685291e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>8.37709455678271e-05</v>
+        <v>8.377094556782706e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>8.385845924760224e-05</v>
+        <v>8.385845924760216e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.329430942335054e-05</v>
+        <v>8.329430942335038e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>8.385845924760224e-05</v>
+        <v>8.385845924760216e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>7.363430905886561e-05</v>
+        <v>7.363430905886556e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>8.385845924760224e-05</v>
+        <v>8.385845924760216e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.652001801295638e-05</v>
+        <v>1.652001801295642e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.418020134321807e-06</v>
+        <v>8.418020134321801e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>9.866364562813623e-06</v>
+        <v>9.866364562813635e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>1.08976044177624e-05</v>
+        <v>1.089760441776235e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.08976044177624e-05</v>
+        <v>1.089760441776235e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>9.847035344292333e-06</v>
+        <v>9.847035344292264e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>9.727528148513252e-06</v>
+        <v>9.727528148513288e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>1.08976044177624e-05</v>
+        <v>1.089760441776235e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.284269620227356e-05</v>
+        <v>1.284269620227358e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.091110552719484e-05</v>
+        <v>1.091110552719441e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>9.253386596663507e-06</v>
+        <v>9.253386596663476e-06</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.676452021851618e-05</v>
+        <v>1.676452021851621e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>8.885652528728929e-06</v>
+        <v>8.88565252872893e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>1.045592654977794e-05</v>
+        <v>1.045592654977795e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.138021696879519e-05</v>
+        <v>1.138021696879515e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.138021696879519e-05</v>
+        <v>1.138021696879515e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>1.037140564315364e-05</v>
+        <v>1.037140564315362e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04005562845454e-05</v>
+        <v>1.040055628454539e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.138021696879519e-05</v>
+        <v>1.138021696879515e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>1.346564639927498e-05</v>
+        <v>1.3465646399275e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.12771588090066e-05</v>
+        <v>1.127715880900615e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>9.738100204243382e-06</v>
+        <v>9.738100204243416e-06</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.006194423608248001</v>
+        <v>0.006194423608248024</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0009544972708599526</v>
+        <v>0.0009544972708599498</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001175349319702009</v>
+        <v>0.001175349319702007</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0009544972708599526</v>
+        <v>0.0009544972708599498</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0009544972708599526</v>
+        <v>0.0009544972708599498</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002528567394018125</v>
+        <v>0.002528567394018132</v>
       </c>
       <c r="H2" t="n">
-        <v>0.005056133404127914</v>
+        <v>0.005056133404127899</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0009544972708599526</v>
+        <v>0.0009544972708599498</v>
       </c>
       <c r="J2" t="n">
         <v>0.001450248346737335</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002802366654982233</v>
+        <v>0.002802366654982236</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001026263837836188</v>
+        <v>0.001026263837836189</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.559090208655884e-05</v>
+        <v>1.559090208655869e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.33357311688237e-05</v>
+        <v>1.333573116882373e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.559090208655884e-05</v>
+        <v>1.559090208655869e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.353025544688371e-05</v>
+        <v>1.353025544688376e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.353025544688371e-05</v>
+        <v>1.353025544688377e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.544846136615303e-05</v>
+        <v>1.544846136615299e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.559090208655884e-05</v>
+        <v>1.559090208655869e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.467722758855828e-05</v>
+        <v>1.467722758855832e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.559090208655884e-05</v>
+        <v>1.559090208655869e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.559090208655884e-05</v>
+        <v>1.559090208655869e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.559090208655884e-05</v>
+        <v>1.559090208655869e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.922336112399373e-05</v>
+        <v>2.523969511920195e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>2.161559410584772e-05</v>
+        <v>2.16155941058478e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>2.336999516871617e-05</v>
+        <v>2.336986776820316e-05</v>
       </c>
       <c r="E4" t="n">
         <v>2.117680543101061e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>2.386646249800763e-05</v>
+        <v>2.386646249800768e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>4.908092040358791e-05</v>
+        <v>2.509725439879628e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>5.067642970303349e-05</v>
+        <v>5.067642970303332e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>4.830968662599325e-05</v>
+        <v>4.830968662599342e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>4.954659261899382e-05</v>
+        <v>2.590417281823846e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>2.661310441011245e-05</v>
+        <v>2.661310441011126e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>2.640658967834728e-05</v>
+        <v>2.640658967834734e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.10847125831094e-05</v>
+        <v>4.108471258310927e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.017103808510886e-05</v>
+        <v>4.017103808510892e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.107594197629013e-05</v>
+        <v>4.107594197629018e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.010987406325705e-05</v>
+        <v>4.010987406325708e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.010987406325705e-05</v>
+        <v>4.010987406325708e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.09422718627036e-05</v>
+        <v>4.094227186270351e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.10847125831094e-05</v>
+        <v>4.108471258310927e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.017103808510886e-05</v>
+        <v>4.017103808510892e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.10847125831094e-05</v>
+        <v>4.108471258310927e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.10847125831094e-05</v>
+        <v>4.108471258310927e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.10847125831094e-05</v>
+        <v>4.108471258310927e-05</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.910466119877669e-05</v>
+        <v>8.910466119877648e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001386193694382791</v>
+        <v>0.0001386193694383864</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001500350131706851</v>
+        <v>0.000150035013170685</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001248190220488582</v>
+        <v>0.0001248190220488583</v>
       </c>
       <c r="F6" t="n">
-        <v>8.975942308716816e-05</v>
+        <v>8.97594230871682e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001394281360928572</v>
+        <v>0.0001394281360928571</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001395705768132604</v>
+        <v>0.0001395705768132601</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001386569023152623</v>
+        <v>0.0001386569023152622</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001395804948099821</v>
+        <v>0.0001395804948099819</v>
       </c>
       <c r="K6" t="n">
-        <v>8.816723090726024e-05</v>
+        <v>8.816723090725999e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001922864455620163</v>
+        <v>0.0001922864455620159</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001502318306838188</v>
+        <v>0.0001502318306838185</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001881886422634703</v>
+        <v>0.0001881886422634709</v>
       </c>
       <c r="D7" t="n">
         <v>0.0001891023290225818</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002330442912571235</v>
+        <v>0.0002330442912571238</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001881885791943402</v>
+        <v>0.0001881885791943404</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001889598760410659</v>
+        <v>0.0001889598760410653</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001891023167614712</v>
+        <v>0.000189102316761471</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001881886422634703</v>
+        <v>0.0001881886422634709</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001891023167614712</v>
+        <v>0.000189102316761471</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001665806096289135</v>
+        <v>0.0001665806096289137</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001891023167614712</v>
+        <v>0.000189102316761471</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.0001241207734610627</v>
+        <v>-0.0001241207734610628</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.789016859150711e-07</v>
+        <v>-4.789016859150703e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.854530001678296e-06</v>
+        <v>-3.854530001678229e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.789016859150711e-07</v>
+        <v>-4.789016859150703e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.789016859150711e-07</v>
+        <v>-4.789016859150703e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.408940717584041e-05</v>
+        <v>-3.408940717584058e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>-8.001853105691663e-05</v>
+        <v>-8.001853105691636e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.789016859150711e-07</v>
+        <v>-4.789016859150703e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>-8.21392324093447e-06</v>
+        <v>-8.213923240934514e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.14428492554261e-05</v>
+        <v>-4.144284925542624e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.082552201313255e-06</v>
+        <v>2.082552201313317e-06</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-3.747140597202306e-05</v>
+        <v>-3.74714059720231e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.235855414738431e-05</v>
+        <v>1.235855414738434e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>1.151296878589578e-05</v>
+        <v>1.151296878589581e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.235855414738431e-05</v>
+        <v>1.235855414738434e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.235855414738431e-05</v>
+        <v>1.235855414738434e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>-9.469839207503256e-07</v>
+        <v>-9.469839207503294e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.941345121338119e-05</v>
+        <v>-1.941345121338113e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.235855414738431e-05</v>
+        <v>1.235855414738434e-05</v>
       </c>
       <c r="J9" t="n">
         <v>9.748413739871772e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.793832615442294e-06</v>
+        <v>-3.79383261544232e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>1.394560336206025e-05</v>
+        <v>-2.360804517985084e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5267,34 +5267,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004798763319961984</v>
+        <v>0.004798763319961986</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001367762792828118</v>
+        <v>0.001367762792828116</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001079454390991902</v>
+        <v>0.001079454390991908</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001367762792828118</v>
+        <v>0.001367762792828116</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001367762792828118</v>
+        <v>0.001367762792828116</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002349697532139539</v>
+        <v>0.002349697532139547</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004276609023968245</v>
+        <v>0.00427660902396823</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001367762792828118</v>
+        <v>0.001367762792828116</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001232297110567382</v>
+        <v>0.001232297110567384</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002519212619587677</v>
+        <v>0.002519212619587678</v>
       </c>
       <c r="L2" t="n">
         <v>0.001335846319911896</v>
@@ -5307,13 +5307,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.745227404168354e-05</v>
+        <v>1.745227404168349e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.589391528115497e-05</v>
+        <v>1.589391528115498e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.745227404168355e-05</v>
+        <v>1.745227404168346e-05</v>
       </c>
       <c r="E3" t="n">
         <v>1.606890039462939e-05</v>
@@ -5322,22 +5322,22 @@
         <v>1.606890039462939e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.732900467438981e-05</v>
+        <v>1.732900467438992e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.745227404168355e-05</v>
+        <v>1.745227404168346e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.666111390466095e-05</v>
+        <v>1.666111390466094e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.745227404168355e-05</v>
+        <v>1.745227404168346e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.745227404168355e-05</v>
+        <v>1.745227404168346e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.745227404168355e-05</v>
+        <v>1.745227404168346e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.011192633619093e-05</v>
+        <v>2.739174412530628e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>2.515554676654524e-05</v>
+        <v>2.515554676654539e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>2.555484986407233e-05</v>
+        <v>2.555484986407377e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>2.466877030787454e-05</v>
+        <v>2.466877030787457e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>2.654480873899886e-05</v>
+        <v>2.654480873899901e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>4.99886569688972e-05</v>
+        <v>2.726847475801249e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>5.14300289921261e-05</v>
+        <v>5.143002899212616e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>4.932076619916849e-05</v>
+        <v>4.932076619916844e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>5.042251108729147e-05</v>
+        <v>2.813525288045174e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>2.87236196898569e-05</v>
+        <v>2.87236196898571e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>2.85104212113493e-05</v>
+        <v>2.851042121134921e-05</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.154134131544751e-05</v>
+        <v>4.154134131544784e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.075018117842492e-05</v>
+        <v>4.07501811784249e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.153309238102979e-05</v>
+        <v>4.153309238102983e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.073512470760105e-05</v>
+        <v>4.073512470760109e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.073512470760105e-05</v>
+        <v>4.073512470760109e-05</v>
       </c>
       <c r="G5" t="n">
         <v>4.141807194815376e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.154134131544752e-05</v>
+        <v>4.154134131544786e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.075018117842492e-05</v>
+        <v>4.07501811784249e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.154134131544752e-05</v>
+        <v>4.154134131544786e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.154134131544752e-05</v>
+        <v>4.154134131544786e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.154134131544752e-05</v>
+        <v>4.154134131544786e-05</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.617887070495924e-05</v>
+        <v>8.617887070495941e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001326719802360631</v>
+        <v>0.0001326719802360634</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001432614680352886</v>
+        <v>0.0001432614680352887</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001197388212617744</v>
+        <v>0.0001197388212617746</v>
       </c>
       <c r="F6" t="n">
-        <v>8.688232054367655e-05</v>
+        <v>8.68823205436767e-05</v>
       </c>
       <c r="G6" t="n">
         <v>0.0001333345919672364</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001334578613345248</v>
+        <v>0.0001334578613345249</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001326667011975077</v>
+        <v>0.0001326667011975078</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001334671530071563</v>
+        <v>0.0001334671530071568</v>
       </c>
       <c r="K6" t="n">
-        <v>8.53006391813268e-05</v>
+        <v>8.530063918132693e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001828447204484153</v>
+        <v>0.0001828447204484156</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.000135667214174051</v>
+        <v>0.0001356672141740513</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00016914064108405</v>
+        <v>0.0001691406410840505</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001699318156544137</v>
+        <v>0.0001699318156544139</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002086811991450562</v>
+        <v>0.0002086811991450565</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001691405915542978</v>
+        <v>0.0001691405915542981</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001698085318537791</v>
+        <v>0.0001698085318537793</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001699318012210726</v>
+        <v>0.000169931801221073</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00016914064108405</v>
+        <v>0.0001691406410840505</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001699318012210726</v>
+        <v>0.000169931801221073</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001267865661809448</v>
+        <v>0.0001500787709892537</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001699318012210726</v>
+        <v>0.000169931801221073</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-9.606308793512133e-05</v>
+        <v>-9.606308793512144e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.120156336257545e-05</v>
+        <v>-1.120156336257541e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.856017863679775e-06</v>
+        <v>-2.85601786368015e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.120156336257545e-05</v>
+        <v>-1.120156336257541e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.120156336257545e-05</v>
+        <v>-1.120156336257541e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.360240596678845e-05</v>
+        <v>-3.360240596678858e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>-6.935469907145471e-05</v>
+        <v>-6.935469907145451e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.120156336257545e-05</v>
+        <v>-1.120156336257541e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.466500574403272e-06</v>
+        <v>-4.466500574403283e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.226867607152813e-05</v>
+        <v>-4.226867607152795e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.585959638166942e-06</v>
+        <v>-5.585959638166958e-06</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-2.551677267356136e-05</v>
+        <v>-2.551677267356139e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>9.282398132282894e-06</v>
+        <v>9.282398132282922e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>1.244657019165664e-05</v>
+        <v>1.244657019165651e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>9.282398132282894e-06</v>
+        <v>9.282398132282922e-06</v>
       </c>
       <c r="F9" t="n">
-        <v>9.282398132282894e-06</v>
+        <v>9.282398132282922e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.671920110117829e-07</v>
+        <v>-1.671920110118129e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.455231044135074e-05</v>
+        <v>-1.45523104413507e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>9.282398132282894e-06</v>
+        <v>9.282398132282922e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>1.180054657945696e-05</v>
+        <v>1.180054657945697e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.603178843386741e-06</v>
+        <v>-3.603178843386647e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>1.135558218840481e-05</v>
+        <v>-2.067934707199898e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5663,13 +5663,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00395892277892593</v>
+        <v>0.003958922778925942</v>
       </c>
       <c r="C2" t="n">
         <v>0.002420548167498273</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00101066729335924</v>
+        <v>0.001010667293359241</v>
       </c>
       <c r="E2" t="n">
         <v>0.002420548167498273</v>
@@ -5678,22 +5678,22 @@
         <v>0.002420548167498273</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002149365152324204</v>
+        <v>0.00214936515232421</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003605045249973458</v>
+        <v>0.003605045249973451</v>
       </c>
       <c r="I2" t="n">
         <v>0.002420548167498273</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001373248913517361</v>
+        <v>0.001373248913517363</v>
       </c>
       <c r="K2" t="n">
         <v>0.002317845473557131</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004819047504247927</v>
+        <v>0.001185982315958654</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.186872921843167e-05</v>
+        <v>2.186872921843181e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>2.191271635567945e-05</v>
+        <v>2.191271635567948e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>2.186872921843167e-05</v>
+        <v>2.186872921843181e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>2.203793145559557e-05</v>
+        <v>2.203793145559554e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.203793145559556e-05</v>
+        <v>2.203793145559553e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>2.179494914667283e-05</v>
+        <v>2.179494914667287e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>2.186872921843167e-05</v>
+        <v>2.186872921843181e-05</v>
       </c>
       <c r="I3" t="n">
         <v>2.139347464051572e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.186872921843167e-05</v>
+        <v>2.186872921843181e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.186872921843167e-05</v>
+        <v>2.186872921843181e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.186872921843167e-05</v>
+        <v>2.186872921843181e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.372689893949754e-05</v>
+        <v>3.372689893949763e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>3.438511640858974e-05</v>
+        <v>3.438511640858989e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>5.615353886618951e-05</v>
+        <v>3.175436981812786e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>3.373143564014454e-05</v>
+        <v>3.37314356401446e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>3.392408032292913e-05</v>
+        <v>3.392408032292909e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.365311886773874e-05</v>
+        <v>5.605538090582093e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>5.737557483277972e-05</v>
+        <v>5.737557483277999e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>5.565390639966362e-05</v>
+        <v>3.325164436158164e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.472579901643815e-05</v>
+        <v>5.638968635126292e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.486087266466959e-05</v>
+        <v>3.486087266466964e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>3.486528069432251e-05</v>
+        <v>3.486528069432253e-05</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.653538181150105e-05</v>
+        <v>4.653538181150119e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.606012723358505e-05</v>
+        <v>4.606012723358508e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.652696503126034e-05</v>
+        <v>4.652696503126036e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.615676524360243e-05</v>
+        <v>4.615676524360244e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.615676524360243e-05</v>
+        <v>4.615676524360244e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.646160173974218e-05</v>
+        <v>4.646160173974225e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.653538181150102e-05</v>
+        <v>4.653538181150116e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.606012723358505e-05</v>
+        <v>4.606012723358508e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.653538181150102e-05</v>
+        <v>4.653538181150116e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.653538181150102e-05</v>
+        <v>4.653538181150116e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.653538181150102e-05</v>
+        <v>4.653538181150116e-05</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.055218609867419e-05</v>
+        <v>9.05521860986743e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001374890219296866</v>
+        <v>0.0001374890219296868</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001476598878193914</v>
+        <v>0.0001476598878193917</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001245387692162508</v>
+        <v>0.000124538769216251</v>
       </c>
       <c r="F6" t="n">
-        <v>9.163893190642614e-05</v>
+        <v>9.163893190642626e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001377781895127952</v>
+        <v>0.0001377781895127955</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001378519695845534</v>
+        <v>0.0001378519695845538</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001373767150066382</v>
+        <v>0.0001373767150066384</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001378612653419534</v>
+        <v>0.0001378612653419537</v>
       </c>
       <c r="K6" t="n">
-        <v>8.967356833719663e-05</v>
+        <v>8.967356833719691e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001872605485740239</v>
+        <v>0.0001872605485740243</v>
       </c>
     </row>
     <row r="7">
@@ -5863,28 +5863,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001350052143024038</v>
+        <v>0.0001350052143024039</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001674110614994612</v>
+        <v>0.0001674110614994613</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001678863239477569</v>
+        <v>0.000167886323947757</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002053551175414265</v>
+        <v>0.0002053551175414264</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000167411025236152</v>
+        <v>0.0001674110252361523</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001678125360056187</v>
+        <v>0.0001678125360056185</v>
       </c>
       <c r="H7" t="n">
         <v>0.0001678863160773772</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001674110614994612</v>
+        <v>0.0001674110614994613</v>
       </c>
       <c r="J7" t="n">
         <v>0.0001678863160773772</v>
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-7.692330573557143e-05</v>
+        <v>-7.692330573557161e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>-3.503505474845091e-05</v>
+        <v>-3.503505474845094e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.782283342474218e-07</v>
+        <v>-3.782283342473498e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.503505474845091e-05</v>
+        <v>-3.503505474845094e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.503505474845091e-05</v>
+        <v>-3.503505474845094e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.82573793637648e-05</v>
+        <v>-2.825737936376468e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>-5.667127404785102e-05</v>
+        <v>-5.667127404785098e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.503505474845091e-05</v>
+        <v>-3.503505474845094e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>-6.247846772104481e-06</v>
+        <v>-6.247846772104464e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.898366279952334e-05</v>
+        <v>-3.898366279952339e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>-7.701486676359455e-05</v>
+        <v>-7.70148667635947e-05</v>
       </c>
     </row>
     <row r="9">
@@ -5943,31 +5943,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.693430530680434e-05</v>
+        <v>-1.693430530680444e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.316738283069429e-06</v>
+        <v>2.316738283069485e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>1.424268392594112e-05</v>
+        <v>1.424268392594116e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.316738283069429e-06</v>
+        <v>2.316738283069485e-06</v>
       </c>
       <c r="F9" t="n">
-        <v>2.316738283069429e-06</v>
+        <v>2.316738283069485e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>2.937567065407169e-06</v>
+        <v>2.937567065407243e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>-8.610026505162777e-06</v>
+        <v>-8.61002650516273e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>2.316738283069429e-06</v>
+        <v>2.316738283069485e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>1.18631665548354e-05</v>
+        <v>1.186316655483543e-05</v>
       </c>
       <c r="K9" t="n">
         <v>-1.478360420660658e-06</v>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0006056877093879689</v>
+        <v>0.0006056877093879701</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002407477064330083</v>
+        <v>0.0002407477064330082</v>
       </c>
       <c r="D2" t="n">
         <v>0.0004183231040152456</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002407477064330083</v>
+        <v>0.0002407477064330082</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002407477064330083</v>
+        <v>0.0002407477064330082</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0006653874257805857</v>
+        <v>0.0006653874257805852</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001454432271098964</v>
+        <v>0.001454432271098965</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002407477064330083</v>
+        <v>0.0002407477064330082</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008080067291811149</v>
+        <v>0.0008080067291811156</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0005121877297782627</v>
+        <v>0.0005121877297782637</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001788191881699813</v>
+        <v>0.001788191881699816</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.167070376293997e-06</v>
+        <v>9.167070376294052e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>8.096971182418963e-06</v>
+        <v>8.096971182418911e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>9.167070376293997e-06</v>
+        <v>9.167070376294052e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>8.1757830053266e-06</v>
+        <v>8.17578300532654e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>8.175783005326596e-06</v>
+        <v>8.175783005326549e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>9.064377007194032e-06</v>
+        <v>9.064377007194035e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>9.167070376293997e-06</v>
+        <v>9.167070376294052e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>8.506288680405104e-06</v>
+        <v>8.506288680405123e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>9.167070376293997e-06</v>
+        <v>9.167070376294052e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>9.167070376293997e-06</v>
+        <v>9.167070376294052e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>9.167070376293997e-06</v>
+        <v>9.167070376294052e-06</v>
       </c>
     </row>
     <row r="4">
@@ -6139,34 +6139,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.337164248224768e-05</v>
+        <v>2.675789730852742e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.196376537109e-05</v>
+        <v>1.196376537108994e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>2.691031765637149e-05</v>
+        <v>2.691031765637142e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.173839165488899e-05</v>
+        <v>1.173839165488898e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.265696782998466e-05</v>
+        <v>1.265696782998461e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.326894911314767e-05</v>
+        <v>2.665520393942747e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.76400698495969e-05</v>
+        <v>1.379994318345036e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.27108607863588e-05</v>
+        <v>2.60971156126385e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.688878904168833e-05</v>
+        <v>2.688878904168829e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.341816816433394e-05</v>
+        <v>1.341816816433392e-05</v>
       </c>
       <c r="L4" t="n">
         <v>1.386122336083323e-05</v>
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.630514631111025e-05</v>
+        <v>2.630514631111023e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.564436461522145e-05</v>
+        <v>2.56443646152213e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.629643806049826e-05</v>
+        <v>2.629643806049815e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.56473676817592e-05</v>
+        <v>2.564736768175908e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.56473676817592e-05</v>
+        <v>2.564736768175908e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.620245294201033e-05</v>
+        <v>2.620245294201026e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.630514631111025e-05</v>
+        <v>2.630514631111023e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.564436461522145e-05</v>
+        <v>2.56443646152213e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.630514631111025e-05</v>
+        <v>2.630514631111023e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.630514631111025e-05</v>
+        <v>2.630514631111023e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.630514631111025e-05</v>
+        <v>2.630514631111023e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.67506759227989e-05</v>
+        <v>6.675067592279887e-05</v>
       </c>
       <c r="C6" t="n">
         <v>0.0001048259511993007</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001134929929893224</v>
+        <v>0.0001134929929893225</v>
       </c>
       <c r="E6" t="n">
-        <v>9.423321636443359e-05</v>
+        <v>9.423321636443356e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>6.732407344088198e-05</v>
+        <v>6.732407344088187e-05</v>
       </c>
       <c r="G6" t="n">
         <v>0.0001053625763867455</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001054652697558446</v>
+        <v>0.0001054652697558445</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001048044880599565</v>
+        <v>0.0001048044880599566</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001054728782836746</v>
+        <v>0.0001054728782836744</v>
       </c>
       <c r="K6" t="n">
-        <v>6.603153246628889e-05</v>
+        <v>6.603153246628883e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000145905900276732</v>
+        <v>0.0001459059002767319</v>
       </c>
     </row>
     <row r="7">
@@ -6259,16 +6259,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.640417345904198e-05</v>
+        <v>9.640417345904202e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001207948806286025</v>
+        <v>0.0001207948806286026</v>
       </c>
       <c r="D7" t="n">
         <v>0.0001214556634295073</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001497037403216832</v>
+        <v>0.0001497037403216831</v>
       </c>
       <c r="F7" t="n">
         <v>0.0001207948580051659</v>
@@ -6280,7 +6280,7 @@
         <v>0.0001214556623244916</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001207948806286025</v>
+        <v>0.0001207948806286026</v>
       </c>
       <c r="J7" t="n">
         <v>0.0001214556623244916</v>
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-3.197427714136883e-07</v>
+        <v>-3.197427714137027e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>9.486442805966345e-06</v>
+        <v>9.486442805966318e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>3.963968348671868e-06</v>
+        <v>3.963968348671871e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>9.486442805966345e-06</v>
+        <v>9.486442805966318e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>9.486442805966345e-06</v>
+        <v>9.486442805966318e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.709443088349337e-06</v>
+        <v>-1.709443088349331e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.861838591977246e-05</v>
+        <v>-1.861838591977245e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>9.486442805966345e-06</v>
+        <v>9.486442805966318e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.477269338977749e-06</v>
+        <v>-3.477269338977736e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>1.70919775698695e-06</v>
+        <v>1.70919775698691e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>1.148204585277309e-05</v>
+        <v>-2.247555332760935e-05</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.691196262515051e-06</v>
+        <v>7.691196262515057e-06</v>
       </c>
       <c r="C9" t="n">
-        <v>1.221041437879543e-05</v>
+        <v>1.221041437879542e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>9.436175128011758e-06</v>
+        <v>9.436175128011762e-06</v>
       </c>
       <c r="E9" t="n">
-        <v>1.221041437879544e-05</v>
+        <v>1.221041437879542e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.221041437879544e-05</v>
+        <v>1.221041437879542e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>7.07740289318593e-06</v>
+        <v>7.077402893185948e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>2.68084436456189e-07</v>
+        <v>2.680844364561686e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>1.221041437879544e-05</v>
+        <v>1.221041437879542e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>6.411594800135762e-06</v>
+        <v>6.41159480013575e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>8.518189495398147e-06</v>
+        <v>8.518189495398128e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.30555012861877e-06</v>
+        <v>-1.305550128618804e-06</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.48025488141651e-05</v>
+        <v>7.480254881416515e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001371580050817831</v>
+        <v>0.000137158005081783</v>
       </c>
       <c r="D2" t="n">
         <v>0.0001423610220240773</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001371580050817831</v>
+        <v>0.000137158005081783</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001371580050817831</v>
+        <v>0.000137158005081783</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001699555984351115</v>
+        <v>0.0001699555984351171</v>
       </c>
       <c r="H2" t="n">
         <v>0.0001642166508622436</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001371580050817831</v>
+        <v>0.000137158005081783</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002496475261902105</v>
+        <v>0.0002496475261902112</v>
       </c>
       <c r="K2" t="n">
         <v>0.0001141664179590864</v>
       </c>
       <c r="L2" t="n">
-        <v>6.828165478231897e-05</v>
+        <v>6.828165478231911e-05</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.661044615340675e-06</v>
+        <v>7.661044615340653e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.009158382974494e-06</v>
+        <v>7.009158382974487e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.661044615340675e-06</v>
+        <v>7.661044615340653e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.058895386165313e-06</v>
+        <v>7.058895386165307e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.058895386165326e-06</v>
+        <v>7.058895386165323e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.572989604558646e-06</v>
+        <v>7.572989604558701e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.661044615340675e-06</v>
+        <v>7.661044615340653e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.093505962847453e-06</v>
+        <v>7.093505962847452e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.661044615340675e-06</v>
+        <v>7.661044615340653e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.661044615340675e-06</v>
+        <v>7.661044615340653e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.661044615340675e-06</v>
+        <v>7.661044615340653e-06</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.012651801282909e-05</v>
+        <v>2.012651801282918e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>9.669266837254793e-06</v>
+        <v>9.669266837254812e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.036042243419489e-05</v>
+        <v>1.03604240684082e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>9.510268585125168e-06</v>
+        <v>9.51026858512517e-06</v>
       </c>
       <c r="F4" t="n">
         <v>9.789672149331462e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.025250283312086e-05</v>
+        <v>2.003846300204719e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.036380990058047e-05</v>
+        <v>2.069193157887842e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>9.773019191409607e-06</v>
+        <v>1.955897936033594e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.014799286193982e-05</v>
+        <v>1.065202638829645e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.030974712624933e-05</v>
+        <v>1.030974712624936e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.035863180247004e-05</v>
+        <v>1.035863180247005e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.148054516808567e-05</v>
+        <v>2.148054516808568e-05</v>
       </c>
       <c r="C5" t="n">
         <v>2.09130065155925e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.147244654831115e-05</v>
+        <v>2.147244654831118e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.093090459511334e-05</v>
+        <v>2.093090459511335e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.093090459511334e-05</v>
+        <v>2.093090459511335e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.139249015730374e-05</v>
+        <v>2.139249015730375e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.148054516808567e-05</v>
+        <v>2.148054516808568e-05</v>
       </c>
       <c r="I5" t="n">
         <v>2.09130065155925e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.148054516808567e-05</v>
+        <v>2.148054516808568e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.148054516808567e-05</v>
+        <v>2.148054516808568e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.148054516808567e-05</v>
+        <v>2.148054516808568e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.712661590851922e-05</v>
+        <v>5.712661590851929e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>8.963094714202192e-05</v>
+        <v>8.963094714202175e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>9.701530984760773e-05</v>
+        <v>9.701530984760781e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>8.058954478147121e-05</v>
+        <v>8.058954478147115e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>5.762184043205784e-05</v>
+        <v>5.762184043205788e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>9.007660182722985e-05</v>
+        <v>9.007660182722974e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>9.016465683801216e-05</v>
+        <v>9.016465683801222e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>8.959711818551863e-05</v>
+        <v>8.959711818551852e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>9.017114976035847e-05</v>
+        <v>9.017114976035851e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.651291733652928e-05</v>
+        <v>5.651291733652937e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001246756531853626</v>
+        <v>0.0001246756531853627</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.22631188689196e-05</v>
+        <v>7.226311886891971e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>9.02615780186511e-05</v>
+        <v>9.026157801865109e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>9.082912044637203e-05</v>
+        <v>9.082912044637223e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001116863450272442</v>
+        <v>0.0001116863450272444</v>
       </c>
       <c r="F7" t="n">
-        <v>9.026157465444921e-05</v>
+        <v>9.02615746544492e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>9.074106166036238e-05</v>
+        <v>9.074106166036246e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>9.082911667114413e-05</v>
+        <v>9.082911667114434e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>9.02615780186511e-05</v>
+        <v>9.026157801865109e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>9.082911667114413e-05</v>
+        <v>9.082911667114434e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>7.963547244844714e-05</v>
+        <v>8.007190621811493e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>9.082911667114413e-05</v>
+        <v>9.082911667114434e-05</v>
       </c>
     </row>
     <row r="8">
@@ -6695,13 +6695,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.000234094472938e-05</v>
+        <v>1.000234094472941e-05</v>
       </c>
       <c r="C8" t="n">
         <v>1.00056689810156e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.495165314728323e-06</v>
+        <v>8.495165314728324e-06</v>
       </c>
       <c r="E8" t="n">
         <v>1.00056689810156e-05</v>
@@ -6710,7 +6710,7 @@
         <v>1.00056689810156e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.692404080009301e-06</v>
+        <v>7.692404080009298e-06</v>
       </c>
       <c r="H8" t="n">
         <v>8.321869643322192e-06</v>
@@ -6719,13 +6719,13 @@
         <v>1.00056689810156e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>5.836114528818349e-06</v>
+        <v>5.836114528818363e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>9.055294967628931e-06</v>
+        <v>9.055294967628933e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>8.768898789065659e-06</v>
+        <v>1.046382220098201e-05</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.057050409697327e-05</v>
+        <v>1.057050409697331e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.140365527189754e-05</v>
+        <v>1.140365527189755e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>9.956710927005012e-06</v>
+        <v>9.956710927005056e-06</v>
       </c>
       <c r="E9" t="n">
-        <v>1.140365527189754e-05</v>
+        <v>1.140365527189755e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.140365527189754e-05</v>
+        <v>1.140365527189755e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>9.620271551608158e-06</v>
+        <v>9.620271551608147e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>9.888666905446826e-06</v>
+        <v>9.888666905446848e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>1.140365527189754e-05</v>
+        <v>1.140365527189755e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>8.875643624068847e-06</v>
+        <v>8.875643624068869e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>1.018488781107695e-05</v>
+        <v>1.018488781107696e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.006991324968875e-05</v>
+        <v>1.075895469201307e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.997170021913441e-05</v>
+        <v>8.997170021913438e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001790933508991229</v>
+        <v>0.0001790933508991232</v>
       </c>
       <c r="D2" t="n">
-        <v>9.129510400319986e-05</v>
+        <v>9.129510400319976e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001790933508991229</v>
+        <v>0.0001790933508991232</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001790933508991229</v>
+        <v>0.0001790933508991232</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001445241779878967</v>
+        <v>0.0001445241779878957</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000157933523164056</v>
+        <v>0.0001579335231640556</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001790933508991229</v>
+        <v>0.0001790933508991232</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001100678600251333</v>
+        <v>0.0001100678600251331</v>
       </c>
       <c r="K2" t="n">
-        <v>9.239215959291085e-05</v>
+        <v>9.239215959291064e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002858860778776771</v>
+        <v>0.0001323052397383749</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.85917017385136e-06</v>
+        <v>7.85917017385138e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.281813580110761e-06</v>
+        <v>7.281813580110724e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.859170173851361e-06</v>
+        <v>7.85917017385138e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.332353398679785e-06</v>
+        <v>7.332353398679767e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.332353398679742e-06</v>
+        <v>7.332353398679769e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.773819652881675e-06</v>
+        <v>7.773819652881697e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.85917017385136e-06</v>
+        <v>7.85917017385138e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.308895517925536e-06</v>
+        <v>7.308895517925488e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.85917017385136e-06</v>
+        <v>7.85917017385138e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>7.85917017385136e-06</v>
+        <v>7.85917017385138e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.85917017385136e-06</v>
+        <v>7.85917017385138e-06</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.051132828344737e-05</v>
+        <v>1.051132828344738e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>9.98547168501193e-06</v>
+        <v>9.985471685011823e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.044402543999666e-05</v>
+        <v>1.044402543999657e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>9.825699142338358e-06</v>
+        <v>9.825699142338368e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>1.000917176848498e-05</v>
+        <v>1.00091717684849e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>2.035404609548427e-05</v>
+        <v>1.042597776247772e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.093061471619375e-05</v>
+        <v>2.093061471619384e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>9.961053627521559e-06</v>
+        <v>9.961053627521528e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>2.03549504946715e-05</v>
+        <v>1.077726316669546e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.045027022611345e-05</v>
+        <v>1.04502702261135e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.05776824186641e-05</v>
+        <v>1.057768241866412e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.15943033423122e-05</v>
+        <v>2.159430334231226e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.104402868638633e-05</v>
+        <v>2.104402868638631e-05</v>
       </c>
       <c r="D5" t="n">
         <v>2.158620141350617e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.10656974605103e-05</v>
+        <v>2.106569746051026e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.10656974605103e-05</v>
+        <v>2.106569746051026e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.150895282134256e-05</v>
+        <v>2.150895282134251e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.15943033423122e-05</v>
+        <v>2.159430334231226e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.104402868638633e-05</v>
+        <v>2.104402868638631e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.15943033423122e-05</v>
+        <v>2.159430334231226e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.15943033423122e-05</v>
+        <v>2.159430334231226e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.15943033423122e-05</v>
+        <v>2.159430334231226e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.706268176195726e-05</v>
+        <v>5.706268176195731e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>8.943624908614943e-05</v>
+        <v>8.943624908614931e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>9.676832954575156e-05</v>
+        <v>9.676832954575153e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>8.043592855681507e-05</v>
+        <v>8.043592855681511e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>5.75726158863886e-05</v>
+        <v>5.757261588638867e-05</v>
       </c>
       <c r="G6" t="n">
         <v>8.986376313613607e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>8.994911365711049e-05</v>
+        <v>8.994911365711057e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>8.939883900117985e-05</v>
+        <v>8.93988390011798e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>8.995557678348523e-05</v>
+        <v>8.99555767834851e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.645179940565223e-05</v>
+        <v>5.645179940565221e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001243017416903325</v>
+        <v>0.0001243017416903324</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.850683217484025e-05</v>
+        <v>6.850683217484016e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>8.54354295743902e-05</v>
+        <v>8.54354295743901e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>8.59857065386767e-05</v>
+        <v>8.598570653867664e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001056056755655251</v>
+        <v>0.000105605675565525</v>
       </c>
       <c r="F7" t="n">
-        <v>8.543542650580219e-05</v>
+        <v>8.543542650580204e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>8.590035370934632e-05</v>
+        <v>8.590035370934628e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>8.598570423031616e-05</v>
+        <v>8.598570423031603e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.54354295743902e-05</v>
+        <v>8.54354295743901e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>8.598570423031616e-05</v>
+        <v>8.598570423031603e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>7.544749957943861e-05</v>
+        <v>7.544749957943859e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>8.598570423031616e-05</v>
+        <v>8.598570423031603e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.583237595257162e-06</v>
+        <v>9.583237595257177e-06</v>
       </c>
       <c r="C8" t="n">
-        <v>8.968055095708023e-06</v>
+        <v>8.968055095708011e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>9.733834903348757e-06</v>
+        <v>9.733834903348742e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>8.968055095708023e-06</v>
+        <v>8.968055095708011e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>8.968055095708023e-06</v>
+        <v>8.968055095708011e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>8.310415039525205e-06</v>
+        <v>8.310415039525202e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>8.341134065620625e-06</v>
+        <v>8.341134065620635e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>8.968055095708023e-06</v>
+        <v>8.968055095708011e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>9.221871709309095e-06</v>
+        <v>9.221871709309098e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>9.616838159804952e-06</v>
+        <v>9.616838159804918e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>8.832377272309059e-06</v>
+        <v>5.530067441315109e-06</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.037147387539898e-05</v>
+        <v>1.037147387539896e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.104590039574642e-05</v>
+        <v>1.10459003957464e-05</v>
       </c>
       <c r="D9" t="n">
         <v>1.043284691421163e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>1.104590039574642e-05</v>
+        <v>1.10459003957464e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.104590039574642e-05</v>
+        <v>1.10459003957464e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>9.851347289435546e-06</v>
+        <v>9.851347289435532e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>9.868117362100223e-06</v>
+        <v>9.868117362100203e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>1.104590039574642e-05</v>
+        <v>1.10459003957464e-05</v>
       </c>
       <c r="J9" t="n">
         <v>1.022499837035616e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.03852363817725e-05</v>
+        <v>1.038523638177249e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>8.724841888205828e-06</v>
+        <v>8.724841888205833e-06</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003260648478018178</v>
+        <v>0.003260648478018179</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0006958978737353113</v>
+        <v>0.000695897873735311</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001071225790579777</v>
+        <v>0.001071225790579775</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0006958978737353113</v>
+        <v>0.000695897873735311</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0006958978737353113</v>
+        <v>0.000695897873735311</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002004128555050532</v>
+        <v>0.002004128555050526</v>
       </c>
       <c r="H2" t="n">
         <v>0.004415548160127147</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0006958978737353113</v>
+        <v>0.000695897873735311</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001308060791377404</v>
+        <v>0.001308060791377402</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00185821712287023</v>
+        <v>0.001858217122870226</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004982132875205759</v>
+        <v>0.0004294201613404338</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.349728075125444e-05</v>
+        <v>1.349728075125433e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.149815865097796e-05</v>
+        <v>1.149815865097791e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.349728075125444e-05</v>
+        <v>1.349728075125432e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1660934783684e-05</v>
+        <v>1.166093478368386e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.166093478368399e-05</v>
+        <v>1.166093478368381e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.336239861793568e-05</v>
+        <v>1.336239861793561e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.349728075125444e-05</v>
+        <v>1.349728075125433e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.263157778304378e-05</v>
+        <v>1.263157778304369e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.349728075125444e-05</v>
+        <v>1.349728075125432e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.349728075125444e-05</v>
+        <v>1.349728075125432e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.349728075125444e-05</v>
+        <v>1.349728075125432e-05</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.159510140242318e-05</v>
+        <v>2.159510140242312e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.845565206804017e-05</v>
+        <v>1.845565206804008e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>2.052540887716744e-05</v>
+        <v>2.052540887716883e-05</v>
       </c>
       <c r="E4" t="n">
         <v>1.808319347409865e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0377370633477e-05</v>
+        <v>2.037737063347694e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>4.254362408354524e-05</v>
+        <v>4.254362408354519e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>4.43036094211727e-05</v>
+        <v>4.430360942117252e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>4.181280324865321e-05</v>
+        <v>4.18128032486533e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>4.310005306790732e-05</v>
+        <v>4.310005306790734e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2086721009191e-05</v>
+        <v>2.208672100919151e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>2.269675685280442e-05</v>
+        <v>2.269675685280432e-05</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.622871804164975e-05</v>
+        <v>3.622871804164963e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>3.536301507343905e-05</v>
+        <v>3.536301507343894e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>3.621997039729036e-05</v>
+        <v>3.621997039729022e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>3.532398444179309e-05</v>
+        <v>3.53239844417929e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>3.532398444179309e-05</v>
+        <v>3.53239844417929e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>3.609383590833097e-05</v>
+        <v>3.60938359083307e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>3.622871804164975e-05</v>
+        <v>3.622871804164963e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.536301507343905e-05</v>
+        <v>3.536301507343894e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>3.622871804164975e-05</v>
+        <v>3.622871804164963e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>3.622871804164975e-05</v>
+        <v>3.622871804164963e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>3.622871804164975e-05</v>
+        <v>3.622871804164963e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.184532858545362e-05</v>
+        <v>8.184532858545329e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001276246494952798</v>
+        <v>0.0001276246494951749</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001381831916986594</v>
+        <v>0.0001381831916986584</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001148624287180254</v>
+        <v>0.000114862428718025</v>
       </c>
       <c r="F6" t="n">
-        <v>8.244067877391082e-05</v>
+        <v>8.24406787739104e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001283726066687755</v>
+        <v>0.0001283726066687752</v>
       </c>
       <c r="H6" t="n">
-        <v>0.000128507488802101</v>
+        <v>0.0001285074888021004</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001276417858338834</v>
+        <v>0.0001276417858338827</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001285166592525231</v>
+        <v>0.000128516659252523</v>
       </c>
       <c r="K6" t="n">
-        <v>8.097855500325666e-05</v>
+        <v>8.097855500325635e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001772500169735366</v>
+        <v>0.0001772500169735356</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001351155692758185</v>
+        <v>0.0001351155692758178</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001692918919730498</v>
+        <v>0.0001692918919730505</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001701575960011184</v>
+        <v>0.0001701575960011178</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002097295705020998</v>
+        <v>0.0002097295705020988</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001692918303441687</v>
+        <v>0.0001692918303441669</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001700227128079414</v>
+        <v>0.0001700227128079413</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001701575949412604</v>
+        <v>0.0001701575949412628</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001692918919730498</v>
+        <v>0.0001692918919730505</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001701575949412604</v>
+        <v>0.0001701575949412628</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001498541080958588</v>
+        <v>0.0001498541080958583</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001701575949412604</v>
+        <v>0.0001701575949412628</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-5.78426853840877e-05</v>
+        <v>-5.784268538408771e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>3.170933983038455e-06</v>
+        <v>3.170933983038281e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.453295310756607e-06</v>
+        <v>-5.453295310756729e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>3.170933983038455e-06</v>
+        <v>3.170933983038281e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>3.170933983038455e-06</v>
+        <v>3.170933983038281e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.657814408780584e-05</v>
+        <v>-2.657814408780577e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>-7.793051511974881e-05</v>
+        <v>-7.793051511974869e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>3.170933983038455e-06</v>
+        <v>3.170933983038281e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>-8.209273163124714e-06</v>
+        <v>-8.20927316312478e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.376205870275949e-05</v>
+        <v>-2.376205870275958e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>-7.802789830342144e-05</v>
+        <v>-7.802789830342124e-05</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.223392209878833e-05</v>
+        <v>-1.223392209878844e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.236394435118685e-05</v>
+        <v>1.236394435118674e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>9.104603741456065e-06</v>
+        <v>9.104603741455904e-06</v>
       </c>
       <c r="E9" t="n">
-        <v>1.236394435118685e-05</v>
+        <v>1.236394435118674e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.236394435118685e-05</v>
+        <v>1.236394435118674e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>3.720417607154577e-07</v>
+        <v>3.720417607153709e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.032493532392737e-05</v>
+        <v>-2.032493532392751e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.236394435118685e-05</v>
+        <v>1.236394435118674e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>7.991991837777892e-06</v>
+        <v>7.991991837777814e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>1.649185298185327e-06</v>
+        <v>1.649185298185261e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.038141716907824e-05</v>
+        <v>1.59313856219942e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7643,7 +7643,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.118346846942067e-05</v>
+        <v>7.118346846942058e-05</v>
       </c>
       <c r="C2" t="n">
         <v>0.0001475172459251992</v>
@@ -7658,10 +7658,10 @@
         <v>0.0001475172459251992</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0009309615243772303</v>
+        <v>0.0009309615243772281</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0006026361400259348</v>
+        <v>0.0006026361400259362</v>
       </c>
       <c r="I2" t="n">
         <v>0.0001475172459251992</v>
@@ -7670,10 +7670,10 @@
         <v>0.0003540400575296459</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002443275290516772</v>
+        <v>0.0002443275290516773</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001991011344772465</v>
+        <v>0.002867978356284166</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.364979948887058e-06</v>
+        <v>9.364979948887113e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.883621542086847e-06</v>
+        <v>7.883621542086889e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>9.364979948887058e-06</v>
+        <v>9.364979948887113e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.989807464667154e-06</v>
+        <v>7.989807464667249e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.989807464667147e-06</v>
+        <v>7.989807464667245e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>9.247279459614134e-06</v>
+        <v>9.247279459614131e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>9.364979948887058e-06</v>
+        <v>9.364979948887113e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>8.6087247998741e-06</v>
+        <v>8.608724799874115e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>9.364979948887058e-06</v>
+        <v>9.364979948887113e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>9.364979948887058e-06</v>
+        <v>9.364979948887113e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>9.364979948887058e-06</v>
+        <v>9.364979948887113e-06</v>
       </c>
     </row>
     <row r="4">
@@ -7726,34 +7726,34 @@
         <v>2.795428521077512e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.135176573208348e-05</v>
+        <v>1.135176573208343e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.366754843924363e-05</v>
+        <v>1.366751387415522e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.115677026604992e-05</v>
+        <v>1.115677026604989e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.250016399041009e-05</v>
+        <v>1.250016399041011e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.325791083580579e-05</v>
+        <v>2.783658472150215e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.876178297160522e-05</v>
+        <v>2.876178297160509e-05</v>
       </c>
       <c r="I4" t="n">
         <v>2.719803006176216e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.382621913695215e-05</v>
+        <v>1.382621913695217e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.258879756569572e-05</v>
+        <v>1.258879756569562e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.421807797211517e-05</v>
+        <v>1.421807797211514e-05</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.63782697286569e-05</v>
+        <v>2.637826972865687e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.562201457964401e-05</v>
+        <v>2.562201457964392e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.637016801965547e-05</v>
+        <v>2.637016801965546e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.560824172149306e-05</v>
+        <v>2.560824172149302e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.560824172149306e-05</v>
+        <v>2.560824172149302e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.626056923938398e-05</v>
+        <v>2.626056923938388e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.63782697286569e-05</v>
+        <v>2.637826972865687e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.562201457964401e-05</v>
+        <v>2.562201457964392e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.63782697286569e-05</v>
+        <v>2.637826972865687e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.63782697286569e-05</v>
+        <v>2.637826972865687e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.63782697286569e-05</v>
+        <v>2.637826972865687e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.528739750160779e-05</v>
+        <v>6.528739750160773e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001023427843184464</v>
+        <v>0.0001023427843184463</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001109341231467674</v>
+        <v>0.0001109341231467676</v>
       </c>
       <c r="E6" t="n">
-        <v>9.200019074956163e-05</v>
+        <v>9.200019074956145e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>6.572618795511297e-05</v>
+        <v>6.572618795511299e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001029768609286816</v>
+        <v>0.0001029768609286813</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001030945614179471</v>
+        <v>0.000103094561417947</v>
       </c>
       <c r="I6" t="n">
         <v>0.0001023383062689414</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001031019916087447</v>
+        <v>0.0001031019916087445</v>
       </c>
       <c r="K6" t="n">
-        <v>6.458511002175866e-05</v>
+        <v>6.458511002175857e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000142587305511851</v>
+        <v>0.0001425873055118507</v>
       </c>
     </row>
     <row r="7">
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.090457832905029e-05</v>
+        <v>9.090457832905031e-05</v>
       </c>
       <c r="C7" t="n">
         <v>0.0001136885638832049</v>
@@ -7852,7 +7852,7 @@
         <v>0.0001144448423231215</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001408535102881281</v>
+        <v>0.000140853510288128</v>
       </c>
       <c r="F7" t="n">
         <v>0.0001136885532532981</v>
@@ -7870,7 +7870,7 @@
         <v>0.0001144448190322178</v>
       </c>
       <c r="K7" t="n">
-        <v>8.480344803236531e-05</v>
+        <v>0.00010080552091524</v>
       </c>
       <c r="L7" t="n">
         <v>0.0001144448190322178</v>
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.309353056322616e-05</v>
+        <v>1.309353056322615e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.178248953820097e-05</v>
+        <v>1.178248953820095e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.310603159872563e-06</v>
+        <v>-4.310603159872597e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>1.178248953820097e-05</v>
+        <v>1.178248953820095e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.178248953820097e-05</v>
+        <v>1.178248953820095e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>-9.13894079487211e-06</v>
+        <v>-9.138940794872163e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>5.563139019857621e-07</v>
+        <v>5.563139019857371e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.178248953820097e-05</v>
+        <v>1.178248953820095e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>6.494101643935418e-06</v>
+        <v>6.494101643935426e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>8.579614817102201e-06</v>
+        <v>8.579614817102157e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.738903654398917e-05</v>
+        <v>-4.738903654398923e-05</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.354551281778188e-05</v>
+        <v>1.354551281778185e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.327455710742139e-05</v>
+        <v>1.327455710742135e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>6.457407544474671e-06</v>
+        <v>6.45740754447466e-06</v>
       </c>
       <c r="E9" t="n">
-        <v>1.327455710742139e-05</v>
+        <v>1.327455710742135e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.327455710742139e-05</v>
+        <v>1.327455710742135e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.400113873609817e-06</v>
+        <v>4.400113873609799e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>8.451761878799386e-06</v>
+        <v>8.451761878799382e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>1.327455710742139e-05</v>
+        <v>1.327455710742135e-05</v>
       </c>
       <c r="J9" t="n">
         <v>1.08604961842992e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.17073140143118e-05</v>
+        <v>1.170731401431179e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.104210132563641e-05</v>
+        <v>-1.104210132563642e-05</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Hydrogen/hydrogen eutrophication freshwater results.xlsx
+++ b/Results/Hydrogen/hydrogen eutrophication freshwater results.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,321 +511,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007886762567972362</v>
+        <v>3.214433373975667e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001723738605140722</v>
+        <v>2.592546227669423e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001284908587117469</v>
+        <v>2.513661222332482e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001723738605140722</v>
+        <v>2.592546227669423e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001723738605140722</v>
+        <v>2.592546227669423e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002719256064629243</v>
+        <v>2.639596257791443e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.005750835857818341</v>
+        <v>2.913969902978026e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001723738605140722</v>
+        <v>2.592546227669423e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00224966363809297</v>
+        <v>2.601952353933119e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003646867655377436</v>
+        <v>2.755751969111493e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00635206259964423</v>
+        <v>2.432254068728459e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.834195374324882e-05</v>
+        <v>2.407784099732849e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.669533465412943e-05</v>
+        <v>2.439653165672698e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.834195374324882e-05</v>
+        <v>2.407784099732849e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.688156968271491e-05</v>
+        <v>2.439653165672698e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.688156968271491e-05</v>
+        <v>2.439653165672698e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.822170357809674e-05</v>
+        <v>2.392081257568334e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.834195374324882e-05</v>
+        <v>2.407784099732849e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.756986977313902e-05</v>
+        <v>2.439653165672698e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.834195374324882e-05</v>
+        <v>2.407784099732849e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.834195374324882e-05</v>
+        <v>2.407784099732849e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.834195374324882e-05</v>
+        <v>2.407784099732849e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.042947522643242e-05</v>
+        <v>0.007886762567972369</v>
       </c>
       <c r="C4" t="n">
-        <v>2.788284662730234e-05</v>
+        <v>0.001723738605140727</v>
       </c>
       <c r="D4" t="n">
-        <v>2.804921789430064e-05</v>
+        <v>0.00128490858711747</v>
       </c>
       <c r="E4" t="n">
-        <v>2.729562415002185e-05</v>
+        <v>0.001723738605140727</v>
       </c>
       <c r="F4" t="n">
-        <v>2.939774277767257e-05</v>
+        <v>0.001723738605140727</v>
       </c>
       <c r="G4" t="n">
-        <v>5.596718484601377e-05</v>
+        <v>0.00271925606462924</v>
       </c>
       <c r="H4" t="n">
-        <v>5.749208406109814e-05</v>
+        <v>0.005750835857818337</v>
       </c>
       <c r="I4" t="n">
-        <v>5.531535104105604e-05</v>
+        <v>0.001723738605140727</v>
       </c>
       <c r="J4" t="n">
-        <v>5.625238569815289e-05</v>
+        <v>0.002249663638092968</v>
       </c>
       <c r="K4" t="n">
-        <v>3.277942513546286e-05</v>
+        <v>0.003646867655377437</v>
       </c>
       <c r="L4" t="n">
-        <v>3.16178827009664e-05</v>
+        <v>0.006352062599644246</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.659485276609266e-05</v>
+        <v>1.834195374324878e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.582276879598284e-05</v>
+        <v>1.669533465412943e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.658543075554202e-05</v>
+        <v>1.834195374324878e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.578283071980747e-05</v>
+        <v>1.688156968271491e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.578283071980747e-05</v>
+        <v>1.68815696827149e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.647460260094063e-05</v>
+        <v>1.822170357809672e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.659485276609266e-05</v>
+        <v>1.834195374324878e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.582276879598284e-05</v>
+        <v>1.756986977313897e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.659485276609266e-05</v>
+        <v>1.834195374324878e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.659485276609266e-05</v>
+        <v>1.834195374324878e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.659485276609266e-05</v>
+        <v>1.834195374324878e-05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.81859996230002e-05</v>
+        <v>3.042947522643241e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001521913743205779</v>
+        <v>2.788284662730236e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001643407242429704</v>
+        <v>2.804921789430068e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001372051017462864</v>
+        <v>2.729562415002177e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>9.913256586041866e-05</v>
+        <v>2.93977427776725e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001528587818649071</v>
+        <v>5.596718484601366e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001529790320300613</v>
+        <v>5.749208406109809e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001522069480599494</v>
+        <v>5.531535104105591e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001529898004301128</v>
+        <v>5.625238569815293e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>9.716819091547199e-05</v>
+        <v>3.277942513546076e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002102149360970526</v>
+        <v>3.161788270096633e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.000183075653809287</v>
+        <v>4.659485276609263e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0002296290933397728</v>
+        <v>4.582276879598276e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0002304011809044706</v>
+        <v>4.658543075554188e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002842416618725175</v>
+        <v>4.578283071980741e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0002296290250411342</v>
+        <v>4.578283071980741e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0002302809271447305</v>
+        <v>4.647460260094054e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0002304011773098826</v>
+        <v>4.659485276609263e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0002296290933397728</v>
+        <v>4.582276879598276e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0002304011773098826</v>
+        <v>4.659485276609263e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001708098947149724</v>
+        <v>4.659485276609263e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002304011773098826</v>
+        <v>4.659485276609263e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.0001494314001551532</v>
+        <v>9.818599962300015e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.22927277356291e-05</v>
+        <v>0.0001521913743205779</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.533546470963399e-06</v>
+        <v>0.0001643407242429705</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.22927277356291e-05</v>
+        <v>0.0001372051017462864</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.22927277356291e-05</v>
+        <v>9.913256586041857e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.211539070330453e-05</v>
+        <v>0.0001528587818649072</v>
       </c>
       <c r="H8" t="n">
-        <v>-8.433716897656401e-05</v>
+        <v>0.0001529790320300614</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.22927277356291e-05</v>
+        <v>0.0001522069480599494</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.069590189068646e-05</v>
+        <v>0.0001529898004301129</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.320524458559455e-05</v>
+        <v>9.716819091547191e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>1.466276707006489e-05</v>
+        <v>0.0002102149360970527</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.000183075653809287</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0002296290933397728</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0002304011809044706</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0002842416618725174</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0002296290250411343</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0002302809271447305</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0002304011773098827</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0002296290933397728</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0002304011773098827</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001708098947149725</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0002304011773098827</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.0001494314001551532</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-1.229272773562911e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-2.533546470963385e-06</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-1.229272773562911e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-1.229272773562911e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-3.211539070330461e-05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-8.433716897656399e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1.229272773562911e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-2.06959018906864e-05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-5.32052445855945e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.466276707006493e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>-4.680292392576571e-05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>9.231732331439953e-06</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.302834611979201e-05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>9.231732331439953e-06</v>
-      </c>
-      <c r="F9" t="n">
-        <v>9.231732331439953e-06</v>
-      </c>
-      <c r="G9" t="n">
-        <v>8.993115091907219e-07</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-2.018947600647781e-05</v>
-      </c>
-      <c r="I9" t="n">
-        <v>9.231732331439953e-06</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.647327839831935e-06</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-7.60653053569568e-06</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-2.325085276427653e-05</v>
+      <c r="B11" t="n">
+        <v>-4.680292392576579e-05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>9.231732331439956e-06</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.302834611979197e-05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9.231732331439956e-06</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9.231732331439956e-06</v>
+      </c>
+      <c r="G11" t="n">
+        <v>8.993115091907679e-07</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-2.01894760064778e-05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>9.231732331439956e-06</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.647327839831939e-06</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-7.606530535695657e-06</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-2.32508527642765e-05</v>
       </c>
     </row>
   </sheetData>
@@ -839,7 +919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,321 +987,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.717984789985841e-05</v>
+        <v>1.181202908842728e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001973528699744921</v>
+        <v>1.353645971385703e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002490610083368838</v>
+        <v>1.203635615535055e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001973528699744921</v>
+        <v>1.353645971385703e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001973528699744921</v>
+        <v>1.353645971385703e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002715907265270347</v>
+        <v>1.203358293927008e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0002767046234951623</v>
+        <v>1.203790840967014e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001973528699744921</v>
+        <v>1.353645971385703e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001777335177881013</v>
+        <v>1.193847226848457e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>9.85665657993265e-05</v>
+        <v>1.184707110127122e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000294336747306077</v>
+        <v>1.187586475443884e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.3348519408768e-06</v>
+        <v>1.185127780874014e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>7.65148712797829e-06</v>
+        <v>1.344442486064531e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>8.3348519408768e-06</v>
+        <v>1.185127780874014e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>7.709129026630355e-06</v>
+        <v>1.344442486064531e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>7.709129026630338e-06</v>
+        <v>1.344442486064531e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>8.245430085608254e-06</v>
+        <v>1.18267151116449e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>8.3348519408768e-06</v>
+        <v>1.185127780874014e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>7.75872385280574e-06</v>
+        <v>1.344442486064531e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>8.3348519408768e-06</v>
+        <v>1.185127780874014e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>8.3348519408768e-06</v>
+        <v>1.185127780874014e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>8.3348519408768e-06</v>
+        <v>1.185127780874014e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.117351024945195e-05</v>
+        <v>6.717984789985813e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.047313286490503e-05</v>
+        <v>0.0001973528699744925</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184287357290891e-05</v>
+        <v>0.0002490610083368836</v>
       </c>
       <c r="E4" t="n">
-        <v>1.030377714793364e-05</v>
+        <v>0.0001973528699744925</v>
       </c>
       <c r="F4" t="n">
-        <v>1.063265876530069e-05</v>
+        <v>0.0001973528699744925</v>
       </c>
       <c r="G4" t="n">
-        <v>2.157952476276159e-05</v>
+        <v>0.0002715907265270376</v>
       </c>
       <c r="H4" t="n">
-        <v>2.234131040119772e-05</v>
+        <v>0.0002767046234951621</v>
       </c>
       <c r="I4" t="n">
-        <v>1.059738216138089e-05</v>
+        <v>0.0001973528699744925</v>
       </c>
       <c r="J4" t="n">
-        <v>1.14847625621557e-05</v>
+        <v>0.0001777335177881006</v>
       </c>
       <c r="K4" t="n">
-        <v>1.095368000145172e-05</v>
+        <v>9.856656579932644e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.123959256166818e-05</v>
+        <v>0.0002943367473060772</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.309181731968592e-05</v>
+        <v>8.334851940876771e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>2.251568923161478e-05</v>
+        <v>7.651487127978217e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>2.308370470599683e-05</v>
+        <v>8.334851940876771e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>2.253557346899584e-05</v>
+        <v>7.709129026630294e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>2.253557346899584e-05</v>
+        <v>7.709129026630292e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>2.300239546441735e-05</v>
+        <v>8.245430085608207e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>2.309181731968592e-05</v>
+        <v>8.334851940876771e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>2.251568923161478e-05</v>
+        <v>7.758723852805641e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>2.309181731968592e-05</v>
+        <v>8.334851940876771e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>2.309181731968592e-05</v>
+        <v>8.334851940876771e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>2.309181731968592e-05</v>
+        <v>8.334851940876771e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.949979862628964e-05</v>
+        <v>1.117351024945185e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>9.327296960845963e-05</v>
+        <v>1.047313286490502e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001009281881776294</v>
+        <v>2.184287357290874e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>8.388256124743514e-05</v>
+        <v>1.03037771479336e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>6.002805073113805e-05</v>
+        <v>1.063265876530063e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>9.372367947606159e-05</v>
+        <v>2.157952476276092e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>9.381310133132512e-05</v>
+        <v>2.234131040119756e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>9.323697324325911e-05</v>
+        <v>1.059738216138084e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>9.381984487895429e-05</v>
+        <v>1.148476256215563e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.886241141211546e-05</v>
+        <v>1.095368000145163e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001296562152387085</v>
+        <v>1.123959256166807e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.205850820651292e-05</v>
+        <v>2.309181731968591e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>8.989053665748806e-05</v>
+        <v>2.251568923161483e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>9.046667016218204e-05</v>
+        <v>2.30837047059968e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001111331581097231</v>
+        <v>2.253557346899574e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>8.989053203791566e-05</v>
+        <v>2.253557346899574e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>9.037724289029062e-05</v>
+        <v>2.300239546441736e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>9.046666474555923e-05</v>
+        <v>2.309181731968591e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.989053665748806e-05</v>
+        <v>2.251568923161483e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>9.046666474555923e-05</v>
+        <v>2.309181731968591e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>7.980090883067043e-05</v>
+        <v>2.309181731968591e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>9.046666474555923e-05</v>
+        <v>2.309181731968591e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.102250446940598e-05</v>
+        <v>5.949979862628963e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>9.316363872305442e-06</v>
+        <v>9.327296960845968e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>6.323673287178183e-06</v>
+        <v>0.0001009281881776292</v>
       </c>
       <c r="E8" t="n">
-        <v>9.316363872305442e-06</v>
+        <v>8.388256124743508e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>9.316363872305442e-06</v>
+        <v>6.002805073113783e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>5.869109465543178e-06</v>
+        <v>9.372367947606128e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>6.395354181659436e-06</v>
+        <v>9.381310133132505e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>9.316363872305442e-06</v>
+        <v>9.323697324325893e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>8.40017832284675e-06</v>
+        <v>9.38198448789543e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.028980032552838e-05</v>
+        <v>5.886241141211533e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>6.23905280186274e-06</v>
+        <v>0.0001296562152387084</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7.205850820651261e-05</v>
+      </c>
+      <c r="C9" t="n">
+        <v>8.989053665748793e-05</v>
+      </c>
+      <c r="D9" t="n">
+        <v>9.046667016218208e-05</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0001111331581097227</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8.989053203791585e-05</v>
+      </c>
+      <c r="G9" t="n">
+        <v>9.037724289029034e-05</v>
+      </c>
+      <c r="H9" t="n">
+        <v>9.046666474555921e-05</v>
+      </c>
+      <c r="I9" t="n">
+        <v>8.989053665748793e-05</v>
+      </c>
+      <c r="J9" t="n">
+        <v>9.04666647455592e-05</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7.980090883067005e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9.04666647455592e-05</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.1022504469406e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9.316363872305388e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.3236732871782e-06</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9.316363872305388e-06</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9.316363872305388e-06</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5.869109465543192e-06</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6.395354181659477e-06</v>
+      </c>
+      <c r="I10" t="n">
+        <v>9.316363872305388e-06</v>
+      </c>
+      <c r="J10" t="n">
+        <v>8.400178322846719e-06</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.028980032552839e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.239052801862794e-06</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1.143493457788636e-05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.165817880881259e-05</v>
-      </c>
-      <c r="D9" t="n">
-        <v>9.521278482609442e-06</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.165817880881259e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.165817880881259e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>9.322853384531133e-06</v>
-      </c>
-      <c r="H9" t="n">
-        <v>9.555445772351475e-06</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.165817880881259e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.036821100440157e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.113659387027641e-05</v>
-      </c>
-      <c r="L9" t="n">
-        <v>9.490948286135879e-06</v>
+      <c r="B11" t="n">
+        <v>1.143493457788634e-05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.165817880881255e-05</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.521278482609452e-06</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.165817880881255e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.165817880881255e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9.322853384531138e-06</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9.555445772351495e-06</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.165817880881255e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.036821100440158e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.113659387027637e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9.490948286135904e-06</v>
       </c>
     </row>
   </sheetData>
@@ -1235,7 +1395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,321 +1463,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001493517404076352</v>
+        <v>1.615663211327207e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00292433822947138</v>
+        <v>2.409454777135702e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007844913768527618</v>
+        <v>2.141212459752053e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0009269635363640596</v>
+        <v>2.126220399474325e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0009269635363640596</v>
+        <v>2.126220399474325e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001430281033238762</v>
+        <v>1.919461561766397e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.002572305310437346</v>
+        <v>2.309919755085591e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0009269635363640596</v>
+        <v>2.126220399474325e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001996040031621128</v>
+        <v>2.475411645487074e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001556290536172602</v>
+        <v>2.472988921746749e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001202877379448047</v>
+        <v>1.795265046664765e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.693939410370625e-05</v>
+        <v>1.467178717740349e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.807068225818025e-05</v>
+        <v>2.117938422009972e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.693939410370624e-05</v>
+        <v>2.07764404117796e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.584804505979243e-05</v>
+        <v>2.047724752230123e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.584804505979243e-05</v>
+        <v>2.047724752230123e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.683516470790391e-05</v>
+        <v>1.784051216625514e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.693939410370625e-05</v>
+        <v>2.07764404117796e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.626963068875825e-05</v>
+        <v>2.047724752230123e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.693939410370625e-05</v>
+        <v>2.290933677535272e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.693939410370624e-05</v>
+        <v>2.328820930517216e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.693939410370624e-05</v>
+        <v>1.695399627462411e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.424114226252883e-05</v>
+        <v>0.001493517404076354</v>
       </c>
       <c r="C4" t="n">
-        <v>2.977405910935293e-05</v>
+        <v>0.002924338229471385</v>
       </c>
       <c r="D4" t="n">
-        <v>2.586968139110197e-05</v>
+        <v>0.0007844913768527612</v>
       </c>
       <c r="E4" t="n">
-        <v>2.462628698887852e-05</v>
+        <v>0.0009269635363640579</v>
       </c>
       <c r="F4" t="n">
-        <v>2.601089264802408e-05</v>
+        <v>0.0009269635363640579</v>
       </c>
       <c r="G4" t="n">
-        <v>2.683525637303943e-05</v>
+        <v>0.001430281033238765</v>
       </c>
       <c r="H4" t="n">
-        <v>4.636764544845738e-05</v>
+        <v>0.002572305310437349</v>
       </c>
       <c r="I4" t="n">
-        <v>2.626972235389388e-05</v>
+        <v>0.0009269635363640579</v>
       </c>
       <c r="J4" t="n">
-        <v>4.508213702881493e-05</v>
+        <v>0.001996040031621126</v>
       </c>
       <c r="K4" t="n">
-        <v>2.742344291659438e-05</v>
+        <v>0.001556290536172603</v>
       </c>
       <c r="L4" t="n">
-        <v>2.680914254104262e-05</v>
+        <v>0.001202877379448047</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.878848179971176e-05</v>
+        <v>1.693939410370621e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>3.877993895780347e-05</v>
+        <v>1.807068225818027e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>3.877979048389628e-05</v>
+        <v>1.693939410370621e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>3.81034514047673e-05</v>
+        <v>1.584804505979239e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>3.81034514047673e-05</v>
+        <v>1.58480450597924e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>3.868425240390929e-05</v>
+        <v>1.683516470790383e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>3.878848179971176e-05</v>
+        <v>1.693939410370621e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.811871838476373e-05</v>
+        <v>1.626963068875825e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>3.878848179971176e-05</v>
+        <v>1.693939410370621e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>3.878848179971176e-05</v>
+        <v>1.693939410370621e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>3.878848179971176e-05</v>
+        <v>1.693939410370621e-05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.27318637396851e-05</v>
+        <v>4.424114226252896e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001276171254509637</v>
+        <v>2.977405910935295e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001369283285378408</v>
+        <v>2.586968139110203e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001146763009428296</v>
+        <v>2.462628698887856e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>8.348107485962236e-05</v>
+        <v>2.601089264802416e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000127516169049208</v>
+        <v>2.683525637303951e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.000127620398445056</v>
+        <v>4.636764544845748e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001269506350300625</v>
+        <v>2.626972235389394e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001276292203280404</v>
+        <v>4.508213702881482e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>8.189803616176176e-05</v>
+        <v>2.742344291659438e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001745102264628059</v>
+        <v>2.680914254104267e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001251274422607804</v>
+        <v>3.878848179971177e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001563815102004416</v>
+        <v>3.877993895780349e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001563900491426297</v>
+        <v>3.877979048389635e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001917966216430443</v>
+        <v>3.810345140476734e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001557202460860391</v>
+        <v>3.810345140476734e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001562858236465473</v>
+        <v>3.868425240390931e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001563900530423498</v>
+        <v>3.878848179971177e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001557202896274018</v>
+        <v>3.811871838476374e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001563900530423498</v>
+        <v>3.878848179971177e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001382763719375912</v>
+        <v>3.878848179971177e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001563900530423498</v>
+        <v>3.878848179971177e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.831459982409869e-05</v>
+        <v>8.273186373968502e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.368584895002019e-05</v>
+        <v>0.0001276171254509638</v>
       </c>
       <c r="D8" t="n">
-        <v>3.525704919735415e-06</v>
+        <v>0.0001369283285378408</v>
       </c>
       <c r="E8" t="n">
-        <v>1.311443878736002e-07</v>
+        <v>0.0001146763009428296</v>
       </c>
       <c r="F8" t="n">
-        <v>1.311443878736002e-07</v>
+        <v>8.348107485962215e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.338834763065899e-05</v>
+        <v>0.0001275161690492079</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.083616858746192e-05</v>
+        <v>0.0001276203984450559</v>
       </c>
       <c r="I8" t="n">
-        <v>1.311443878735994e-07</v>
+        <v>0.0001269506350300624</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.003307847075898e-05</v>
+        <v>0.0001276292203280403</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.165028686478475e-05</v>
+        <v>8.189803616176172e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.270742672185873e-06</v>
+        <v>0.0001745102264628055</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001251274422607805</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001563815102004417</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0001563900491426296</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0001917966216430443</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001557202460860393</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0001562858236465473</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001563900530423497</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001557202896274019</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001563900530423497</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001382763719375911</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001563900530423497</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-1.831459982409872e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-4.368584895002023e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.525704919735422e-06</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.311443878736078e-07</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.311443878736057e-07</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-1.338834763065906e-05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-3.083616858746192e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.311443878736078e-07</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-2.003307847075894e-05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-1.165028686478499e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-6.270742672185834e-06</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1.147720906210487e-06</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-5.419340034280557e-06</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.356298497380831e-05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.200466222939514e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.200466222939514e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.985384889596764e-06</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-3.847040234246267e-07</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.200466222939514e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.2151806685323e-06</v>
-      </c>
-      <c r="K9" t="n">
-        <v>8.83276211775645e-06</v>
-      </c>
-      <c r="L9" t="n">
-        <v>7.385320232997569e-06</v>
+      <c r="B11" t="n">
+        <v>1.147720906210468e-06</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-5.419340034280555e-06</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.356298497380833e-05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.200466222939517e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.200466222939517e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.985384889596752e-06</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-3.847040234246386e-07</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.200466222939517e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.215180668532282e-06</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8.832762117756262e-06</v>
+      </c>
+      <c r="L11" t="n">
+        <v>7.385320232997574e-06</v>
       </c>
     </row>
   </sheetData>
@@ -1631,7 +1871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1699,321 +1939,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.000552666288882657</v>
+        <v>1.168658211501859e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001840147929687068</v>
+        <v>1.900162995373905e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0005339774925564358</v>
+        <v>1.746260490276083e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0004465293216036643</v>
+        <v>1.78026624735245e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0004465293216036643</v>
+        <v>1.78026624735245e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008014372858603239</v>
+        <v>1.555270786895026e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001321224625876579</v>
+        <v>1.82257132388897e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0004465293216036643</v>
+        <v>1.78026624735245e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001133756082091973</v>
+        <v>2.123945352408617e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0004807281313544849</v>
+        <v>1.759062843640609e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003798088182379137</v>
+        <v>1.494443999721308e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.363993582201214e-05</v>
+        <v>1.113480966775329e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.436077302470192e-05</v>
+        <v>1.709143340039559e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.363993582201214e-05</v>
+        <v>1.702297190212775e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.288004359369012e-05</v>
+        <v>1.747928263346016e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.288004359369012e-05</v>
+        <v>1.747928263346016e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.354043047817827e-05</v>
+        <v>1.479014234318128e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.363993582201214e-05</v>
+        <v>1.702297190212775e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.299998356961119e-05</v>
+        <v>1.747928263346016e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.363993582201214e-05</v>
+        <v>2.020720369282717e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.363993582201214e-05</v>
+        <v>1.721800132156961e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.363993582201214e-05</v>
+        <v>1.469915967765493e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.356439164358161e-05</v>
+        <v>0.0005526662888826585</v>
       </c>
       <c r="C4" t="n">
-        <v>2.212244710247976e-05</v>
+        <v>0.00184014792968707</v>
       </c>
       <c r="D4" t="n">
-        <v>3.442235125347648e-05</v>
+        <v>0.0005339774925564369</v>
       </c>
       <c r="E4" t="n">
-        <v>1.839680074477895e-05</v>
+        <v>0.0004465293216036638</v>
       </c>
       <c r="F4" t="n">
-        <v>1.93300379842162e-05</v>
+        <v>0.0004465293216036638</v>
       </c>
       <c r="G4" t="n">
-        <v>3.346488629974765e-05</v>
+        <v>0.0008014372858603187</v>
       </c>
       <c r="H4" t="n">
-        <v>3.583005497504968e-05</v>
+        <v>0.001321224625876578</v>
       </c>
       <c r="I4" t="n">
-        <v>1.940433357655722e-05</v>
+        <v>0.0004465293216036638</v>
       </c>
       <c r="J4" t="n">
-        <v>2.075986295685672e-05</v>
+        <v>0.00113375608209197</v>
       </c>
       <c r="K4" t="n">
-        <v>1.971549456273395e-05</v>
+        <v>0.000480728131354486</v>
       </c>
       <c r="L4" t="n">
-        <v>1.997260935078768e-05</v>
+        <v>0.000379808818237914</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.224287754055485e-05</v>
+        <v>1.363993582201197e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>3.222877243640855e-05</v>
+        <v>1.436077302470194e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>3.223468294858887e-05</v>
+        <v>1.363993582201197e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>3.165628914380343e-05</v>
+        <v>1.28800435936901e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>3.165628914380343e-05</v>
+        <v>1.288004359369008e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>3.214337219672089e-05</v>
+        <v>1.354043047817826e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>3.224287754055485e-05</v>
+        <v>1.363993582201197e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.160292528815384e-05</v>
+        <v>1.299998356961119e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>3.224287754055485e-05</v>
+        <v>1.363993582201197e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>3.224287754055485e-05</v>
+        <v>1.363993582201197e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>3.224287754055485e-05</v>
+        <v>1.363993582201197e-05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.225372336631914e-05</v>
+        <v>3.356439164358157e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001121673200517688</v>
+        <v>2.212244710247989e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001203770732511265</v>
+        <v>3.442235125347642e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001006309187290137</v>
+        <v>1.839680074477899e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>7.291394478995127e-05</v>
+        <v>1.933003798421621e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001120126602565219</v>
+        <v>3.346488629974761e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001121121656004848</v>
+        <v>3.583005497504944e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001114722133479547</v>
+        <v>1.940433357655725e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001121199989249076</v>
+        <v>2.075986295685678e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>7.15133323385712e-05</v>
+        <v>1.971549456273399e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001537476414213723</v>
+        <v>1.99726093507877e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.451396957580699e-05</v>
+        <v>3.224287754055478e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001180045781836054</v>
+        <v>3.222877243640861e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001180186824437628</v>
+        <v>3.223468294858884e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000144502638956179</v>
+        <v>3.165628914380341e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001173787049877748</v>
+        <v>3.165628914380341e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001179191779439176</v>
+        <v>3.214337219672087e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001180186832877518</v>
+        <v>3.224287754055478e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001173787310353508</v>
+        <v>3.160292528815381e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001180186832877518</v>
+        <v>3.224287754055478e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001043999594979729</v>
+        <v>3.224287754055478e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001180186832877518</v>
+        <v>3.224287754055478e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.541852675221837e-06</v>
+        <v>7.225372336631895e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.5773718470951e-05</v>
+        <v>0.0001121673200517686</v>
       </c>
       <c r="D8" t="n">
-        <v>4.809680670359917e-06</v>
+        <v>0.0001203770732511265</v>
       </c>
       <c r="E8" t="n">
-        <v>7.490077612115387e-06</v>
+        <v>0.0001006309187290135</v>
       </c>
       <c r="F8" t="n">
-        <v>7.490077612115387e-06</v>
+        <v>7.291394478995116e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.397826585785862e-06</v>
+        <v>0.0001120126602565216</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.065040683710808e-05</v>
+        <v>0.0001121121656004846</v>
       </c>
       <c r="I8" t="n">
-        <v>7.490077612115387e-06</v>
+        <v>0.0001114722133479547</v>
       </c>
       <c r="J8" t="n">
-        <v>-5.264866367166427e-06</v>
+        <v>0.0001121199989249076</v>
       </c>
       <c r="K8" t="n">
-        <v>6.351166640739123e-06</v>
+        <v>7.151333233857115e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>7.437807774403734e-06</v>
+        <v>0.0001537476414213722</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>9.451396957580679e-05</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001180045781836055</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0001180186824437625</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0001445026389561789</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001173787049877748</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0001179191779439175</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001180186832877515</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001173787310353508</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001180186832877515</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001043999594979727</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001180186832877515</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-1.541852675221863e-06</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-2.577371847095103e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.809680670359758e-06</v>
+      </c>
+      <c r="E10" t="n">
+        <v>7.490077612115376e-06</v>
+      </c>
+      <c r="F10" t="n">
+        <v>7.490077612115376e-06</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-3.397826585785776e-06</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-1.065040683710809e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7.490077612115376e-06</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-5.264866367166504e-06</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.351166640738901e-06</v>
+      </c>
+      <c r="L10" t="n">
+        <v>7.437807774403684e-06</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>5.918660350838962e-06</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-5.02150750857442e-07</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.190551847085668e-05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.325754235510504e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.325754235510504e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>7.277124044652434e-06</v>
-      </c>
-      <c r="H9" t="n">
-        <v>5.634237722712052e-06</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.325754235510504e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>9.649580472118271e-06</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.264618402608101e-05</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.164050174067835e-05</v>
+      <c r="B11" t="n">
+        <v>5.918660350838922e-06</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-5.021507508574441e-07</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.190551847085661e-05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.3257542355105e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.3257542355105e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>7.277124044652373e-06</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5.634237722712038e-06</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.3257542355105e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>9.649580472118144e-06</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.264618402608075e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.164050174067834e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2027,7 +2347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2095,321 +2415,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.580670305238399e-05</v>
+        <v>9.038747871962618e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0010565852803508</v>
+        <v>1.474638694687569e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0003690627234170346</v>
+        <v>1.418808284207909e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>9.056940660134501e-05</v>
+        <v>1.480385612541515e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>9.056940660134501e-05</v>
+        <v>1.480385612541515e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0004270155701620355</v>
+        <v>1.290026006529551e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007102151590743136</v>
+        <v>1.450348481936026e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>9.056940660134501e-05</v>
+        <v>1.480385612541515e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0004006841763599399</v>
+        <v>1.80391488815474e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>8.249897272421783e-05</v>
+        <v>1.397081793060819e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000141146504549235</v>
+        <v>1.294699692648459e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.109951313755928e-05</v>
+        <v>8.990475910140927e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>1.144175878185446e-05</v>
+        <v>1.368201953156996e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.109951313755927e-05</v>
+        <v>1.389936772619178e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.03870967585146e-05</v>
+        <v>1.485810189352813e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.038709675851461e-05</v>
+        <v>1.485810189352813e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.100046555273742e-05</v>
+        <v>1.253531973134985e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.109951313755927e-05</v>
+        <v>1.389936772619178e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.046231541618995e-05</v>
+        <v>1.485810189352813e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.109951313755927e-05</v>
+        <v>1.779390099720752e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.109951313755927e-05</v>
+        <v>1.401798634412166e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.109951313755927e-05</v>
+        <v>1.292620548612038e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.516717690159862e-05</v>
+        <v>8.580670305238416e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.64638874602205e-05</v>
+        <v>0.001056585280350802</v>
       </c>
       <c r="D4" t="n">
-        <v>1.534892859811808e-05</v>
+        <v>0.0003690627234170346</v>
       </c>
       <c r="E4" t="n">
-        <v>1.372523848885951e-05</v>
+        <v>9.056940660134497e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.44958852967832e-05</v>
+        <v>9.056940660134497e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>2.67220658429799e-05</v>
+        <v>0.0004270155701620344</v>
       </c>
       <c r="H4" t="n">
-        <v>2.902296984200974e-05</v>
+        <v>0.000710215159074316</v>
       </c>
       <c r="I4" t="n">
-        <v>2.618391570643232e-05</v>
+        <v>9.056940660134497e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.76377406606281e-05</v>
+        <v>0.0004006841763599401</v>
       </c>
       <c r="K4" t="n">
-        <v>1.479339639779858e-05</v>
+        <v>8.249897272421806e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.517608087292389e-05</v>
+        <v>0.0001411465045492351</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.806213287941095e-05</v>
+        <v>1.10995131375593e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.803874145676705e-05</v>
+        <v>1.14417587818545e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.805397023633576e-05</v>
+        <v>1.10995131375593e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.749719456570111e-05</v>
+        <v>1.038709675851468e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.749719456570111e-05</v>
+        <v>1.038709675851468e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.796308529458915e-05</v>
+        <v>1.10004655527375e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.806213287941095e-05</v>
+        <v>1.10995131375593e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.742493515804168e-05</v>
+        <v>1.046231541619002e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.806213287941095e-05</v>
+        <v>1.10995131375593e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.806213287941095e-05</v>
+        <v>1.10995131375593e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.806213287941095e-05</v>
+        <v>1.10995131375593e-05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.689622580389599e-05</v>
+        <v>1.516717690159874e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001047697913051804</v>
+        <v>1.646388746022054e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001125464406348486</v>
+        <v>1.534892859811679e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>9.380376688899456e-05</v>
+        <v>1.37252384888596e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>6.750552406497646e-05</v>
+        <v>1.449588529678328e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001046072320737706</v>
+        <v>2.672206584297987e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001047062796587331</v>
+        <v>2.902296984200985e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001040690819372231</v>
+        <v>2.618391570643236e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001047137104157146</v>
+        <v>2.763774066062823e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>6.61938846419731e-05</v>
+        <v>1.479339639779845e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001442020425335728</v>
+        <v>1.517608087292393e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.791924133717752e-05</v>
+        <v>2.806213287941104e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>9.740128148733318e-05</v>
+        <v>2.803874145676713e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>9.742467268450536e-05</v>
+        <v>2.805397023633587e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001192963071450988</v>
+        <v>2.749719456570126e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>9.678745735433709e-05</v>
+        <v>2.749719456570126e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>9.73256253251553e-05</v>
+        <v>2.796308529458923e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>9.74246729099772e-05</v>
+        <v>2.806213287941104e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>9.678747518860788e-05</v>
+        <v>2.742493515804177e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>9.74246729099772e-05</v>
+        <v>2.806213287941104e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>8.56646320727007e-05</v>
+        <v>2.806213287941104e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>9.74246729099772e-05</v>
+        <v>2.806213287941104e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.286895710624502e-06</v>
+        <v>6.689622580389619e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.065112580803959e-05</v>
+        <v>0.0001047697913051805</v>
       </c>
       <c r="D8" t="n">
-        <v>5.64578454841445e-06</v>
+        <v>0.0001125464406348486</v>
       </c>
       <c r="E8" t="n">
-        <v>1.340215330119991e-05</v>
+        <v>9.380376688899458e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.340215330119991e-05</v>
+        <v>6.750552406497649e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>3.152068940621349e-06</v>
+        <v>0.0001046072320737706</v>
       </c>
       <c r="H8" t="n">
-        <v>-6.837910539396596e-07</v>
+        <v>0.0001047062796587329</v>
       </c>
       <c r="I8" t="n">
-        <v>1.340215330119991e-05</v>
+        <v>0.0001040690819372233</v>
       </c>
       <c r="J8" t="n">
-        <v>9.241342402308745e-06</v>
+        <v>0.0001047137104157147</v>
       </c>
       <c r="K8" t="n">
-        <v>1.27629644612859e-05</v>
+        <v>6.619388464197325e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>1.06423519414396e-05</v>
+        <v>0.0001442020425335729</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7.791924133717763e-05</v>
+      </c>
+      <c r="C9" t="n">
+        <v>9.740128148733343e-05</v>
+      </c>
+      <c r="D9" t="n">
+        <v>9.74246726845056e-05</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0001192963071450992</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9.678745735433743e-05</v>
+      </c>
+      <c r="G9" t="n">
+        <v>9.732562532515549e-05</v>
+      </c>
+      <c r="H9" t="n">
+        <v>9.742467290997734e-05</v>
+      </c>
+      <c r="I9" t="n">
+        <v>9.678747518860811e-05</v>
+      </c>
+      <c r="J9" t="n">
+        <v>9.742467290997734e-05</v>
+      </c>
+      <c r="K9" t="n">
+        <v>8.566463207270095e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9.742467290997734e-05</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>7.286895710624524e-06</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-1.06511258080396e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5.645784548414508e-06</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.340215330119992e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.340215330119992e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.152068940621398e-06</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-6.837910539396744e-07</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.340215330119992e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>9.241342402308802e-06</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.276296446128645e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.06423519414396e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>8.263613452194674e-06</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.674728272220222e-06</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.043267619358144e-05</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="B11" t="n">
+        <v>8.263613452194667e-06</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.674728272220235e-06</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.043267619358149e-05</v>
+      </c>
+      <c r="E11" t="n">
         <v>1.414139487607292e-05</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>1.414139487607292e-05</v>
       </c>
-      <c r="G9" t="n">
-        <v>8.630851052868014e-06</v>
-      </c>
-      <c r="H9" t="n">
-        <v>7.868101100630875e-06</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>8.630851052868034e-06</v>
+      </c>
+      <c r="H11" t="n">
+        <v>7.868101100630915e-06</v>
+      </c>
+      <c r="I11" t="n">
         <v>1.414139487607292e-05</v>
       </c>
-      <c r="J9" t="n">
-        <v>1.414770746548133e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.339977897440083e-05</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.190783628544543e-05</v>
+      <c r="J11" t="n">
+        <v>1.414770746548143e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.339977897440121e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.190783628544544e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2423,7 +2823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2491,321 +2891,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.488604145089558e-05</v>
+        <v>9.908590138504295e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>6.465742919179273e-05</v>
+        <v>1.072779262862081e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0004018851405982591</v>
+        <v>1.353576685411925e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>8.007503068300592e-05</v>
+        <v>1.397583443837418e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>8.007503068300592e-05</v>
+        <v>1.397583443837418e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008298795636990617</v>
+        <v>1.373173560338852e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001989710194278254</v>
+        <v>1.506663219447076e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>8.007503068300592e-05</v>
+        <v>1.397583443837418e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002044132191766197</v>
+        <v>2.093011922998439e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008910405209275354</v>
+        <v>1.805095490175997e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001112486247866451</v>
+        <v>1.362057447298242e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.837349270442137e-06</v>
+        <v>9.915413658033971e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>9.127457633658525e-06</v>
+        <v>1.074169154923044e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>9.837349270442137e-06</v>
+        <v>1.321452987320165e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>8.901643950412474e-06</v>
+        <v>1.402884113114344e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>8.901643950412472e-06</v>
+        <v>1.402884113114344e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>9.724297015790779e-06</v>
+        <v>1.295851597362346e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>9.837349270442137e-06</v>
+        <v>1.321452987320165e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>9.110436095070172e-06</v>
+        <v>1.402884113114344e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>9.837349270442137e-06</v>
+        <v>1.898419483216884e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>9.837349270442137e-06</v>
+        <v>1.725686348017513e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>9.837349270442137e-06</v>
+        <v>1.265381651647314e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.415910374172894e-05</v>
+        <v>4.488604145089552e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.284821807415048e-05</v>
+        <v>6.465742919179281e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.38472194813548e-05</v>
+        <v>0.0004018851405982596</v>
       </c>
       <c r="E4" t="n">
-        <v>1.202439717600041e-05</v>
+        <v>8.007503068300751e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.335268050129527e-05</v>
+        <v>8.007503068300751e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.404605148707756e-05</v>
+        <v>0.0008298795636990589</v>
       </c>
       <c r="H4" t="n">
-        <v>2.88193060792393e-05</v>
+        <v>0.001989710194278251</v>
       </c>
       <c r="I4" t="n">
-        <v>2.62810688703959e-05</v>
+        <v>8.007503068300751e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.521486260132705e-05</v>
+        <v>0.002044132191766199</v>
       </c>
       <c r="K4" t="n">
-        <v>1.483065615087982e-05</v>
+        <v>0.0008910405209275346</v>
       </c>
       <c r="L4" t="n">
-        <v>1.447982425232475e-05</v>
+        <v>0.001112486247866451</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.863322194401431e-05</v>
+        <v>9.83734927044215e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>2.856438685456274e-05</v>
+        <v>9.127457633658412e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>2.862468940715691e-05</v>
+        <v>9.83734927044215e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>2.79976554086032e-05</v>
+        <v>8.901643950412442e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>2.79976554086032e-05</v>
+        <v>8.901643950412445e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>2.852016968936293e-05</v>
+        <v>9.724297015790804e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>2.863322194401431e-05</v>
+        <v>9.83734927044215e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>2.790630876864234e-05</v>
+        <v>9.110436095070207e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>2.863322194401431e-05</v>
+        <v>9.83734927044215e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>2.863322194401431e-05</v>
+        <v>9.83734927044215e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>2.863322194401431e-05</v>
+        <v>9.83734927044215e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.014954436148254e-05</v>
+        <v>1.415910374172888e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001109760058527498</v>
+        <v>1.284821807415503e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001193966754686252</v>
+        <v>1.384721948135477e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>9.914891695651643e-05</v>
+        <v>1.202439717600046e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>7.077516926998536e-05</v>
+        <v>1.335268050129528e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001108257126227953</v>
+        <v>1.404605148707757e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001109387648774599</v>
+        <v>2.881930607923922e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001102118517020746</v>
+        <v>2.628106887039599e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00011094678112937</v>
+        <v>1.521486260132699e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>6.939186364913315e-05</v>
+        <v>1.483065615087979e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001535465164467381</v>
+        <v>1.44798242523247e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.819109187134972e-05</v>
+        <v>2.86332219440143e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001236309392289293</v>
+        <v>2.856438685456284e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001236997775224394</v>
+        <v>2.862468940715679e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001524093083138256</v>
+        <v>2.799765540860329e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001229728336245096</v>
+        <v>2.799765540860329e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001235867220637296</v>
+        <v>2.852016968936297e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.000123699774318381</v>
+        <v>2.86332219440143e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.000122972861143009</v>
+        <v>2.790630876864237e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.000123699774318381</v>
+        <v>2.86332219440143e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001089199448758951</v>
+        <v>2.86332219440143e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.000123699774318381</v>
+        <v>2.86332219440143e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.196166291639008e-06</v>
+        <v>7.014954436148256e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>9.994870742411503e-06</v>
+        <v>0.0001109760058527498</v>
       </c>
       <c r="D8" t="n">
-        <v>4.644187887909004e-06</v>
+        <v>0.0001193966754686254</v>
       </c>
       <c r="E8" t="n">
-        <v>1.289375656658078e-05</v>
+        <v>9.914891695651652e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.289375656658078e-05</v>
+        <v>7.077516926998537e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.960218635225995e-06</v>
+        <v>0.0001108257126227954</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.666815050414504e-05</v>
+        <v>0.00011093876487746</v>
       </c>
       <c r="I8" t="n">
-        <v>1.289375656658078e-05</v>
+        <v>0.0001102118517020748</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.516752957763999e-05</v>
+        <v>0.0001109467811293701</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.533208640291087e-06</v>
+        <v>6.939186364913311e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>-8.906522630709396e-06</v>
+        <v>0.0001535465164467382</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>9.819109187135e-05</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001236309392289297</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0001236997775224398</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.000152409308313826</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001229728336245099</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0001235867220637298</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001236997743183813</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001229728611430092</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001236997743183813</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001089199448758953</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001236997743183813</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9.19616629163903e-06</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9.994870742411508e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.644187887909031e-06</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.28937565665808e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.28937565665808e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-4.960218635225948e-06</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-2.666815050414505e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.28937565665808e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-2.516752957763989e-05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-2.533208640290809e-06</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-8.906522630709374e-06</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>9.581330294689221e-06</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.038798678154147e-05</v>
-      </c>
-      <c r="D9" t="n">
-        <v>9.636233938751682e-06</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.345936734419825e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.345936734419825e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5.57865425274298e-06</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-3.080114475783112e-06</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.345936734419825e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>8.40943920324087e-07</v>
-      </c>
-      <c r="K9" t="n">
-        <v>9.046409019729837e-06</v>
-      </c>
-      <c r="L9" t="n">
-        <v>3.810551452290242e-06</v>
+      <c r="B11" t="n">
+        <v>9.581330294689252e-06</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.03879867815415e-05</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.636233938751714e-06</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.345936734419829e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.345936734419829e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5.578654252743034e-06</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-3.080114475783085e-06</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.345936734419829e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8.409439203241866e-07</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9.046409019730081e-06</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.810551452290269e-06</v>
       </c>
     </row>
   </sheetData>
@@ -2819,7 +3299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,321 +3367,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.242629805913569e-05</v>
+        <v>8.869811682021908e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>6.364876402139399e-05</v>
+        <v>9.461214044442533e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>7.816799584446071e-05</v>
+        <v>1.155609528568934e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>7.147146719400688e-05</v>
+        <v>1.244453816392651e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>7.147146719400688e-05</v>
+        <v>1.244453816392651e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001106994204780353</v>
+        <v>1.058298414326172e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001613708002425069</v>
+        <v>1.163560735614474e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>7.147146719400688e-05</v>
+        <v>1.244453816392651e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0005393588531035166</v>
+        <v>1.571084542808761e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>5.9384485224009e-05</v>
+        <v>1.208426688274743e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001797121980093142</v>
+        <v>1.082683657127171e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.384536544944514e-06</v>
+        <v>8.874944599289767e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>8.236465837971622e-06</v>
+        <v>9.466183732477226e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.384536544944514e-06</v>
+        <v>1.157552256142657e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>8.157893919842854e-06</v>
+        <v>1.248706448440972e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>8.157893919842852e-06</v>
+        <v>1.248706448440972e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>8.295997780204838e-06</v>
+        <v>1.055113593490005e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>8.384536544944514e-06</v>
+        <v>1.157552256142657e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>7.813692539055843e-06</v>
+        <v>1.248706448440972e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>8.384536544944514e-06</v>
+        <v>1.527750111884993e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>8.384536544944514e-06</v>
+        <v>1.213451028300827e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>8.384536544944514e-06</v>
+        <v>1.073836114400456e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.069867130908958e-05</v>
+        <v>4.242629805913572e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.051660267520216e-05</v>
+        <v>6.364876402139403e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>2.055832298194946e-05</v>
+        <v>7.816799584446064e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>9.919606955658811e-06</v>
+        <v>7.147146719400699e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.01580796406328e-05</v>
+        <v>7.147146719400699e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.061013254434987e-05</v>
+        <v>0.000110699420478037</v>
       </c>
       <c r="H4" t="n">
-        <v>2.143873324520656e-05</v>
+        <v>0.000161370800242507</v>
       </c>
       <c r="I4" t="n">
-        <v>1.933408110717414e-05</v>
+        <v>7.147146719400699e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.050791922019393e-05</v>
+        <v>0.0005393588531035164</v>
       </c>
       <c r="K4" t="n">
-        <v>1.06823735330466e-05</v>
+        <v>5.938448522400911e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.073965016353538e-05</v>
+        <v>0.0001797121980093141</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.351252422654252e-05</v>
+        <v>8.384536544944523e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>2.347579423339498e-05</v>
+        <v>8.236465837971628e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>2.350445047179568e-05</v>
+        <v>8.384536544944517e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>2.307601119519342e-05</v>
+        <v>8.157893919842921e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>2.307601119519342e-05</v>
+        <v>8.157893919842925e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>2.342398546180283e-05</v>
+        <v>8.295997780204828e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>2.351252422654252e-05</v>
+        <v>8.384536544944523e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>2.294168022065391e-05</v>
+        <v>7.813692539055907e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>2.351252422654252e-05</v>
+        <v>8.384536544944523e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>2.351252422654252e-05</v>
+        <v>8.384536544944523e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>2.351252422654252e-05</v>
+        <v>8.384536544944523e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.050999025028815e-05</v>
+        <v>1.069867130908955e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>9.557001297509007e-05</v>
+        <v>1.051660267520218e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001027086511858814</v>
+        <v>2.055832298194957e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>8.545944167149259e-05</v>
+        <v>9.919606955658835e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>6.113199932462803e-05</v>
+        <v>1.015807964063282e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>9.537273590932075e-05</v>
+        <v>1.061013254434992e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>9.54612746741151e-05</v>
+        <v>2.14387332452066e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>9.489043066817156e-05</v>
+        <v>1.933408110717442e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>9.546814360432488e-05</v>
+        <v>2.050791922019397e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.986075219801001e-05</v>
+        <v>1.068237353304675e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001319708138349817</v>
+        <v>1.073965016353539e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.211384843238426e-05</v>
+        <v>2.351252422654251e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>9.049889277947937e-05</v>
+        <v>2.347579423339497e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>9.053562519907018e-05</v>
+        <v>2.350445047179571e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001112231116610934</v>
+        <v>2.307601119519346e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>8.996477374024044e-05</v>
+        <v>2.307601119519346e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>9.044708400788733e-05</v>
+        <v>2.342398546180284e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>9.053562277262688e-05</v>
+        <v>2.351252422654251e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.996477876673832e-05</v>
+        <v>2.29416802206539e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>9.053562277262688e-05</v>
+        <v>2.351252422654251e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>7.986197539258555e-05</v>
+        <v>2.351252422654251e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>9.053562277262688e-05</v>
+        <v>2.351252422654251e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.14713962664509e-06</v>
+        <v>6.050999025028811e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.638623041448185e-06</v>
+        <v>9.557001297509024e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>1.036156578322371e-05</v>
+        <v>0.0001027086511858812</v>
       </c>
       <c r="E8" t="n">
-        <v>1.143647752318736e-05</v>
+        <v>8.545944167149271e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.143647752318735e-05</v>
+        <v>6.113199932462832e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.602708949150912e-06</v>
+        <v>9.53727359093207e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.750327940326893e-06</v>
+        <v>9.546127467411509e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.143647752318736e-05</v>
+        <v>9.489043066817171e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>3.457333982136705e-06</v>
+        <v>9.546814360432493e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.138330987765744e-05</v>
+        <v>5.986075219800993e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>7.590048111066774e-06</v>
+        <v>0.0001319708138349817</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7.211384843238433e-05</v>
+      </c>
+      <c r="C9" t="n">
+        <v>9.049889277947958e-05</v>
+      </c>
+      <c r="D9" t="n">
+        <v>9.053562519907032e-05</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0001112231116610935</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8.996477374024047e-05</v>
+      </c>
+      <c r="G9" t="n">
+        <v>9.044708400788748e-05</v>
+      </c>
+      <c r="H9" t="n">
+        <v>9.053562277262705e-05</v>
+      </c>
+      <c r="I9" t="n">
+        <v>8.996477876673841e-05</v>
+      </c>
+      <c r="J9" t="n">
+        <v>9.053562277262705e-05</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7.986197539258575e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9.053562277262705e-05</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>8.147139626645107e-06</v>
+      </c>
+      <c r="C10" t="n">
+        <v>8.638623041448195e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.036156578322374e-05</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.143647752318736e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.143647752318736e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>8.602708949150923e-06</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8.750327940326881e-06</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.143647752318736e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.457333982136706e-06</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.13833098776576e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>7.590048111066769e-06</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>8.538658100091747e-06</v>
-      </c>
-      <c r="C9" t="n">
-        <v>9.084671292744855e-06</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>8.538658100091758e-06</v>
+      </c>
+      <c r="C11" t="n">
+        <v>9.084671292744868e-06</v>
+      </c>
+      <c r="D11" t="n">
         <v>1.100374108295631e-05</v>
       </c>
-      <c r="E9" t="n">
-        <v>1.196651774854835e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.196651774854835e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>9.696443655477414e-06</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="E11" t="n">
+        <v>1.196651774854834e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.196651774854834e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9.696443655477476e-06</v>
+      </c>
+      <c r="H11" t="n">
         <v>1.035013480018333e-05</v>
       </c>
-      <c r="I9" t="n">
-        <v>1.196651774854835e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.033263171224546e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.174246830437909e-05</v>
-      </c>
-      <c r="L9" t="n">
-        <v>9.39434410820667e-06</v>
+      <c r="I11" t="n">
+        <v>1.196651774854834e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.033263171224549e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.174246830437923e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9.394344108206685e-06</v>
       </c>
     </row>
   </sheetData>
@@ -3215,7 +3775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3283,321 +3843,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.170949703456696e-05</v>
+        <v>9.154482905336535e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>6.564560715821159e-05</v>
+        <v>9.287856343840485e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>7.588601361327199e-05</v>
+        <v>1.130686002319414e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>6.663111812640805e-05</v>
+        <v>1.210536432807007e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>6.663111812640805e-05</v>
+        <v>1.210536432807007e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>7.120098169542848e-05</v>
+        <v>1.027694040922666e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>8.786367362065479e-05</v>
+        <v>1.131209606168192e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>6.663111812640805e-05</v>
+        <v>1.210536432807007e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>8.10478011626809e-05</v>
+        <v>1.447185700124745e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>5.848691758886705e-05</v>
+        <v>1.176456354706413e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>7.486548857938441e-05</v>
+        <v>1.044467824754645e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.408881705338018e-06</v>
+        <v>9.166246255834502e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>8.306435898245113e-06</v>
+        <v>9.289053177483095e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.408881705338018e-06</v>
+        <v>1.1326298617037e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>8.123566143127685e-06</v>
+        <v>1.214920548833689e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>8.123566143127685e-06</v>
+        <v>1.214920548833689e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>8.321380838247115e-06</v>
+        <v>1.02869793544581e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>8.408881705338018e-06</v>
+        <v>1.1326298617037e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>7.844850864155464e-06</v>
+        <v>1.214920548833689e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>8.408881705338018e-06</v>
+        <v>1.453893666203319e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>8.408881705338018e-06</v>
+        <v>1.181205575055514e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>8.408881705338018e-06</v>
+        <v>1.046037074805123e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.975337388189941e-05</v>
+        <v>4.170949703456707e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.041226337359198e-05</v>
+        <v>6.564560715821162e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.057337240111272e-05</v>
+        <v>7.588601361327206e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>9.807059477730693e-06</v>
+        <v>6.663111812640817e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>9.997386805845007e-06</v>
+        <v>6.663111812640817e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.966587301480872e-05</v>
+        <v>7.120098169542944e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.054007395468282e-05</v>
+        <v>8.786367362065484e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.918934304071686e-05</v>
+        <v>6.663111812640817e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.078805997923003e-05</v>
+        <v>8.104780116268101e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.056506196927127e-05</v>
+        <v>5.848691758886725e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.054191449098941e-05</v>
+        <v>7.486548857938449e-05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.313647412253273e-05</v>
+        <v>8.408881705338225e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>2.310110661808776e-05</v>
+        <v>8.306435898245021e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>2.312839945099954e-05</v>
+        <v>8.408881705338225e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>2.268750861498315e-05</v>
+        <v>8.123566143127656e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>2.268750861498315e-05</v>
+        <v>8.123566143127658e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>2.304897325544182e-05</v>
+        <v>8.321380838247418e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>2.313647412253273e-05</v>
+        <v>8.408881705338225e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>2.257244328135003e-05</v>
+        <v>7.844850864155483e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>2.313647412253273e-05</v>
+        <v>8.408881705338223e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>2.313647412253273e-05</v>
+        <v>8.408881705338225e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>2.313647412253273e-05</v>
+        <v>8.408881705338225e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.991987578609595e-05</v>
+        <v>1.975337388189961e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>9.455327574669429e-05</v>
+        <v>1.041226337359197e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001016240919801443</v>
+        <v>1.057337240111273e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>8.456207647664612e-05</v>
+        <v>9.807059477730693e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>6.052422431836457e-05</v>
+        <v>9.997386805844905e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>9.437413263251782e-05</v>
+        <v>1.966587301480882e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>9.446163349968259e-05</v>
+        <v>1.054007395468275e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>9.389760265842581e-05</v>
+        <v>1.918934304071687e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>9.446842194500074e-05</v>
+        <v>1.078805997923005e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.927824490277946e-05</v>
+        <v>1.056506196927124e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001305433877666282</v>
+        <v>1.05419144909896e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.737987708167044e-05</v>
+        <v>2.313647412253273e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>8.444203159510636e-05</v>
+        <v>2.310110661808774e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>8.447740123165102e-05</v>
+        <v>2.312839945099956e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001036435429506324</v>
+        <v>2.268750861498312e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>8.39133641641184e-05</v>
+        <v>2.268750861498312e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>8.438989823246049e-05</v>
+        <v>2.304897325544191e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>8.447739909955119e-05</v>
+        <v>2.313647412253273e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.391336825836859e-05</v>
+        <v>2.257244328134998e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>8.447739909955119e-05</v>
+        <v>2.313647412253273e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>7.457102859202718e-05</v>
+        <v>2.313647412253273e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>8.447739909955119e-05</v>
+        <v>2.313647412253273e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.45433426296871e-06</v>
+        <v>5.991987578609606e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.413286332023273e-06</v>
+        <v>9.455327574669416e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>1.016656403068619e-05</v>
+        <v>0.0001016240919801444</v>
       </c>
       <c r="E8" t="n">
-        <v>1.121422514896354e-05</v>
+        <v>8.4562076476646e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.121422514896354e-05</v>
+        <v>6.052422431836451e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>9.272532349194788e-06</v>
+        <v>9.43741326325177e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.008135087582716e-05</v>
+        <v>9.44616334996825e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.121422514896354e-05</v>
+        <v>9.389760265842573e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.33335131222001e-05</v>
+        <v>9.446842194500093e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.108120669521146e-05</v>
+        <v>5.927824490277946e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>9.52200144517456e-06</v>
+        <v>0.000130543387766628</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6.737987708167037e-05</v>
+      </c>
+      <c r="C9" t="n">
+        <v>8.444203159510631e-05</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8.447740123165097e-05</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0001036435429506323</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8.391336416411834e-05</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8.438989823246048e-05</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8.447739909955146e-05</v>
+      </c>
+      <c r="I9" t="n">
+        <v>8.39133682583686e-05</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8.447739909955146e-05</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7.457102859202698e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8.447739909955146e-05</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>8.454334262968728e-06</v>
+      </c>
+      <c r="C10" t="n">
+        <v>8.413286332023252e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.016656403068618e-05</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.121422514896352e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.121422514896352e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9.272532349194824e-06</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.00813508758272e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.121422514896352e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.333351312220009e-05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.108120669521151e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.522001445174522e-06</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>8.830560679853711e-06</v>
-      </c>
-      <c r="C9" t="n">
-        <v>8.889379638252911e-06</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.077917709054974e-05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.167994529404965e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.167994529404965e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>9.815363788981036e-06</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.07456408720183e-05</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.167994529404965e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.392338544916651e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.143202489780492e-05</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.001771722433195e-05</v>
+      <c r="B11" t="n">
+        <v>8.830560679853701e-06</v>
+      </c>
+      <c r="C11" t="n">
+        <v>8.889379638252903e-06</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.077917709054969e-05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.167994529404964e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.167994529404964e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9.815363788981083e-06</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.07456408720184e-05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.167994529404964e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.39233854491665e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.143202489780501e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.001771722433202e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3611,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3679,321 +4319,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.206577201481754e-05</v>
+        <v>9.150154359260231e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>6.249337621558352e-05</v>
+        <v>9.792387815522284e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001209003134259541</v>
+        <v>1.199864897541099e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>7.646237682789581e-05</v>
+        <v>1.263662097610705e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>7.646237682789581e-05</v>
+        <v>1.263662097610705e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002868394912550191</v>
+        <v>1.125955654034543e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001641971716401324</v>
+        <v>1.349467550008354e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>7.646237682789581e-05</v>
+        <v>1.263662097610705e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>7.273090013936913e-05</v>
+        <v>1.530951439428768e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>6.173354071636951e-05</v>
+        <v>1.245317255966849e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008951274145840708</v>
+        <v>1.209226263765981e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.758641130132314e-06</v>
+        <v>9.159045516675913e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>8.452798056970317e-06</v>
+        <v>9.804254999046126e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.758641130132314e-06</v>
+        <v>1.197846482965599e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>8.357090327189364e-06</v>
+        <v>1.267877597699146e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>8.357090327189372e-06</v>
+        <v>1.267877597699146e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>8.663944417741929e-06</v>
+        <v>1.104956737741807e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>8.758641130132314e-06</v>
+        <v>1.197846482965599e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>8.148391219056512e-06</v>
+        <v>1.267877597699146e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>8.758641130132314e-06</v>
+        <v>1.539876926990835e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>8.758641130132314e-06</v>
+        <v>1.250671300321216e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>8.758641130132314e-06</v>
+        <v>1.132587160736235e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.123684487920104e-05</v>
+        <v>4.206577201481727e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.079152798402913e-05</v>
+        <v>6.249337621558356e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.111206838568605e-05</v>
+        <v>0.0001209003134259538</v>
       </c>
       <c r="E4" t="n">
-        <v>1.018629367405896e-05</v>
+        <v>7.646237682789586e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.063122640564931e-05</v>
+        <v>7.646237682789586e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.114214816681067e-05</v>
+        <v>0.0002868394912550198</v>
       </c>
       <c r="H4" t="n">
-        <v>2.385781247096673e-05</v>
+        <v>0.001641971716401322</v>
       </c>
       <c r="I4" t="n">
-        <v>1.062659496812556e-05</v>
+        <v>7.646237682789586e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.152437620571393e-05</v>
+        <v>7.273090013936882e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.101157146511353e-05</v>
+        <v>6.173354071636891e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.149287874907688e-05</v>
+        <v>0.0008951274145840703</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.530065490494614e-05</v>
+        <v>8.758641130132728e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>2.525635781853837e-05</v>
+        <v>8.452798056970332e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>2.529213318252287e-05</v>
+        <v>8.758641130132728e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>2.481233750126744e-05</v>
+        <v>8.357090327189272e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>2.481233750126744e-05</v>
+        <v>8.35709032718937e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>2.520595819255454e-05</v>
+        <v>8.663944417741161e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>2.530065490494614e-05</v>
+        <v>8.758641130132728e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>2.469040499387009e-05</v>
+        <v>8.148391219056527e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>2.530065490494614e-05</v>
+        <v>8.758641130132728e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>2.530065490494614e-05</v>
+        <v>8.758641130132728e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>2.530065490494614e-05</v>
+        <v>8.758641130132728e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.497733669490692e-05</v>
+        <v>1.123684487920175e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001028264007098941</v>
+        <v>1.079152798402915e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001105654946712364</v>
+        <v>1.111206838568639e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>9.191724101985901e-05</v>
+        <v>1.018629367405894e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>6.564180012034857e-05</v>
+        <v>1.06312264056492e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001026412948890555</v>
+        <v>1.114214816681017e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001027359916014571</v>
+        <v>2.385781247096619e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001021257416903712</v>
+        <v>1.062659496812544e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.000102743412260791</v>
+        <v>1.15243762057143e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>6.427595029460554e-05</v>
+        <v>1.101157146511317e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001421780639802952</v>
+        <v>1.149287874907639e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.485050932649186e-05</v>
+        <v>2.530065490494626e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001067368392955383</v>
+        <v>2.52563578185384e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001067811249744169</v>
+        <v>2.52921331825233e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001314783239263548</v>
+        <v>2.481233750126744e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001061708617908389</v>
+        <v>2.481233750126744e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001066864396695544</v>
+        <v>2.52059581925547e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001067811363819463</v>
+        <v>2.530065490494626e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001061708864708699</v>
+        <v>2.469040499386998e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001067811363819463</v>
+        <v>2.530065490494626e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>9.407444013987044e-05</v>
+        <v>2.530065490494626e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001067811363819463</v>
+        <v>2.530065490494626e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.489426980237255e-06</v>
+        <v>6.497733669490664e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>9.082308957527441e-06</v>
+        <v>0.0001028264007098942</v>
       </c>
       <c r="D8" t="n">
-        <v>9.876147962468649e-06</v>
+        <v>0.0001105654946712361</v>
       </c>
       <c r="E8" t="n">
-        <v>1.160351971524694e-05</v>
+        <v>9.191724101985916e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.160351971524694e-05</v>
+        <v>6.56418001203486e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>5.287196466863811e-06</v>
+        <v>0.000102641294889056</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.084060329792328e-05</v>
+        <v>0.0001027359916014569</v>
       </c>
       <c r="I8" t="n">
-        <v>1.160351971524694e-05</v>
+        <v>0.0001021257416903713</v>
       </c>
       <c r="J8" t="n">
-        <v>1.447509925473387e-05</v>
+        <v>0.0001027434122607916</v>
       </c>
       <c r="K8" t="n">
-        <v>1.177614177881232e-05</v>
+        <v>6.427595029460515e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.915563087335285e-06</v>
+        <v>0.0001421780639802959</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8.485050932649174e-05</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001067368392955384</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0001067811249744174</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0001314783239263551</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001061708617908389</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0001066864396695547</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001067811363819463</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.00010617088647087</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001067811363819463</v>
+      </c>
+      <c r="K9" t="n">
+        <v>9.407444013987077e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001067811363819463</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>8.489426980237425e-06</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9.082308957527478e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.876147962468543e-06</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.160351971524696e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.160351971524696e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5.287196466864025e-06</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-2.084060329792327e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.160351971524696e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.447509925473366e-05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.177614177881222e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-5.915563087335339e-06</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>8.845475791232667e-06</v>
-      </c>
-      <c r="C9" t="n">
-        <v>9.463900065925753e-06</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.104208810115447e-05</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="B11" t="n">
+        <v>8.845475791233053e-06</v>
+      </c>
+      <c r="C11" t="n">
+        <v>9.463900065925771e-06</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.104208810115438e-05</v>
+      </c>
+      <c r="E11" t="n">
         <v>1.21473759503749e-05</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>1.21473759503749e-05</v>
       </c>
-      <c r="G9" t="n">
-        <v>8.637659412457017e-06</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-1.438105086129606e-06</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>8.63765941245683e-06</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-1.438105086129507e-06</v>
+      </c>
+      <c r="I11" t="n">
         <v>1.21473759503749e-05</v>
       </c>
-      <c r="J9" t="n">
-        <v>1.488924159382167e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.212076032437425e-05</v>
-      </c>
-      <c r="L9" t="n">
-        <v>4.247354906380113e-06</v>
+      <c r="J11" t="n">
+        <v>1.48892415938215e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.212076032437427e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.247354906380106e-06</v>
       </c>
     </row>
   </sheetData>
@@ -4007,7 +4727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4075,321 +4795,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.275446545046721e-05</v>
+        <v>1.091033566537593e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>6.478184777399776e-05</v>
+        <v>9.328959913857746e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>7.633969726299363e-05</v>
+        <v>1.114060669073607e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>7.263516237281823e-05</v>
+        <v>1.203822904566177e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>7.263516237281823e-05</v>
+        <v>1.203822904566177e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>7.150708273395795e-05</v>
+        <v>1.040890958880297e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>8.967227876163955e-05</v>
+        <v>1.114719747100752e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>7.263516237281823e-05</v>
+        <v>1.203822904566177e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>8.231240820507423e-05</v>
+        <v>1.423274690777843e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>6.09175462497052e-05</v>
+        <v>1.194974992044532e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>7.285576828711251e-05</v>
+        <v>1.032664473730991e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.219336646490697e-06</v>
+        <v>1.094836874796946e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>8.108231156662111e-06</v>
+        <v>9.331367842739534e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.219336646490697e-06</v>
+        <v>1.115636726312483e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>8.147208670730131e-06</v>
+        <v>1.207335828827233e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>8.147208670730131e-06</v>
+        <v>1.207335828827233e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>8.132456939982442e-06</v>
+        <v>1.04201654631874e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>8.219336646490697e-06</v>
+        <v>1.115636726312483e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>7.659014803274133e-06</v>
+        <v>1.207335828827233e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>8.219336646490697e-06</v>
+        <v>1.429409930425523e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>8.219336646490697e-06</v>
+        <v>1.199682461011055e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>8.219336646490697e-06</v>
+        <v>1.034206358590242e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.950091279287834e-05</v>
+        <v>4.27544654504672e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.025884062545063e-05</v>
+        <v>6.478184777399863e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.04226810312584e-05</v>
+        <v>7.633969726299521e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>9.705273735329606e-06</v>
+        <v>7.263516237281976e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>9.865986649219194e-06</v>
+        <v>7.263516237281976e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.029567458195023e-05</v>
+        <v>7.150708273395894e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.095699622042968e-05</v>
+        <v>8.967227876163994e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.894059094966178e-05</v>
+        <v>7.263516237281976e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.063198181937486e-05</v>
+        <v>8.231240820507554e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.042196394172243e-05</v>
+        <v>6.091754624970626e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.039035630542607e-05</v>
+        <v>7.285576828711316e-05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.2703037455907e-05</v>
+        <v>8.219336646491754e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>2.266837405259814e-05</v>
+        <v>8.108231156663947e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>2.269496678122508e-05</v>
+        <v>8.219336646491754e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>2.231142153777007e-05</v>
+        <v>8.147208670730689e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>2.231142153777007e-05</v>
+        <v>8.147208670730672e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>2.261615774939872e-05</v>
+        <v>8.132456939984068e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2703037455907e-05</v>
+        <v>8.219336646491754e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>2.214271561269041e-05</v>
+        <v>7.659014803274621e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2703037455907e-05</v>
+        <v>8.219336646491718e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2703037455907e-05</v>
+        <v>8.219336646491754e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>2.2703037455907e-05</v>
+        <v>8.219336646491754e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.913340439749087e-05</v>
+        <v>1.950091279287918e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>9.33654679656686e-05</v>
+        <v>1.025884062545258e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001002904671242642</v>
+        <v>1.042268103125959e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>8.349584005451789e-05</v>
+        <v>9.705273735331656e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>5.975909355775106e-05</v>
+        <v>9.865986649220934e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>9.313509938787667e-05</v>
+        <v>1.029567458195073e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>9.322197909442382e-05</v>
+        <v>2.095699622043192e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>9.266165725116832e-05</v>
+        <v>1.89405909496628e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>9.322867847686655e-05</v>
+        <v>1.063198181937576e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.850019162136398e-05</v>
+        <v>1.042196394172209e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001288303458063733</v>
+        <v>1.03903563054271e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.077474739463785e-05</v>
+        <v>2.270303745590819e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>8.879672791608297e-05</v>
+        <v>2.266837405259858e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>8.883139329964534e-05</v>
+        <v>2.269496678122667e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000109108050712941</v>
+        <v>2.231142153777148e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>8.827106565224989e-05</v>
+        <v>2.231142153777148e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>8.87445116128835e-05</v>
+        <v>2.261615774939998e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>8.88313913193917e-05</v>
+        <v>2.270303745590819e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.827106947617512e-05</v>
+        <v>2.214271561269192e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>8.88313913193917e-05</v>
+        <v>2.270303745590819e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>6.609485300538803e-05</v>
+        <v>2.270303745590819e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>8.88313913193917e-05</v>
+        <v>2.270303745590819e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.021045601403524e-05</v>
+        <v>5.913340439749164e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.475244155910026e-06</v>
+        <v>9.336546796566952e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>9.983262884756833e-06</v>
+        <v>0.0001002904671242655</v>
       </c>
       <c r="E8" t="n">
-        <v>1.099118639784653e-05</v>
+        <v>8.349584005451858e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.099118639784653e-05</v>
+        <v>5.975909355775234e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>9.396303646650133e-06</v>
+        <v>9.313509938787793e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>9.87044706187257e-06</v>
+        <v>9.32219790944236e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.099118639784653e-05</v>
+        <v>9.266165725116898e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.305718758011e-05</v>
+        <v>9.322867847686755e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.120462770066043e-05</v>
+        <v>5.850019162136525e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>9.444062009579363e-06</v>
+        <v>0.0001288303458063743</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7.077474739463954e-05</v>
+      </c>
+      <c r="C9" t="n">
+        <v>8.87967279160835e-05</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8.883139329964648e-05</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0001091080507129426</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8.827106565225136e-05</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8.874451161288451e-05</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8.883139131939276e-05</v>
+      </c>
+      <c r="I9" t="n">
+        <v>8.827106947617608e-05</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8.883139131939276e-05</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6.609485300539057e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8.883139131939276e-05</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.021045601403538e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>8.475244155910048e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.983262884756944e-06</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.099118639784653e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.099118639784653e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9.39630364665029e-06</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9.870447061872182e-06</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.099118639784653e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.305718758010995e-05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.120462770066012e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.444062009579271e-06</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1.057458301984703e-05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>8.939420908046026e-06</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.060684046011682e-05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.154583738684082e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.154583738684082e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>9.943049199424319e-06</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.05620996814531e-05</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.154583738684082e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.366994813148856e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.158929780206394e-05</v>
-      </c>
-      <c r="L9" t="n">
-        <v>9.918051158321854e-06</v>
+      <c r="B11" t="n">
+        <v>1.057458301984757e-05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>8.939420908046015e-06</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.060684046011693e-05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.154583738684083e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.154583738684083e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9.943049199424358e-06</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.056209968145309e-05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.154583738684083e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.36699481314886e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.1589297802064e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9.918051158321793e-06</v>
       </c>
     </row>
   </sheetData>
@@ -4403,7 +5203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4471,321 +5271,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.124780401014417e-05</v>
+        <v>1.708419817772365e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>6.505364350951293e-05</v>
+        <v>9.277578370743298e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3866155087026e-05</v>
+        <v>1.09617953777318e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>6.743636250185748e-05</v>
+        <v>1.18150939588336e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>6.743636250185748e-05</v>
+        <v>1.18150939588336e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>7.045924925553141e-05</v>
+        <v>1.082557837028385e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>8.806745098806616e-05</v>
+        <v>1.096959612345133e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>6.743636250185748e-05</v>
+        <v>1.18150939588336e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>8.28955760656337e-05</v>
+        <v>1.403419369718772e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>5.93344171815861e-05</v>
+        <v>1.161967580453243e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>7.356322383212379e-05</v>
+        <v>1.015315304921753e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.348576811218459e-06</v>
+        <v>1.722260201340713e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>8.282875548254054e-06</v>
+        <v>9.279389578262067e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.348576811218459e-06</v>
+        <v>1.097815639772238e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>8.132768829225874e-06</v>
+        <v>1.185337132807008e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>8.132768829225876e-06</v>
+        <v>1.185337132807008e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>8.261063131443364e-06</v>
+        <v>1.084521017096436e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>8.348576811218459e-06</v>
+        <v>1.097815639772238e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>7.784426986966763e-06</v>
+        <v>1.185337132807008e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>8.348576811218459e-06</v>
+        <v>1.409224195138718e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>8.348576811218459e-06</v>
+        <v>1.166388486029456e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>8.348576811218459e-06</v>
+        <v>1.016558426253747e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.97748412846158e-05</v>
+        <v>4.124780401014421e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.044884985329107e-05</v>
+        <v>6.505364350951301e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.060277468786758e-05</v>
+        <v>7.386615508702622e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>9.846192567298648e-06</v>
+        <v>6.743636250185748e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.003257235838465e-05</v>
+        <v>6.743636250185748e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.047466078733772e-05</v>
+        <v>7.045924925553353e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.137201614508207e-05</v>
+        <v>8.806745098806625e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>9.998024642861138e-06</v>
+        <v>6.743636250185748e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.039043499273463e-05</v>
+        <v>8.28955760656339e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.06027177614742e-05</v>
+        <v>5.933441718158602e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.05725107961873e-05</v>
+        <v>7.356322383212372e-05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.261385007300729e-05</v>
+        <v>8.3485768112184e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>2.257851165847207e-05</v>
+        <v>8.282875548254166e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>2.260577611710755e-05</v>
+        <v>8.3485768112184e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>2.218521310677641e-05</v>
+        <v>8.132768829225867e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>2.218521310677641e-05</v>
+        <v>8.132768829225867e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>2.252633639323227e-05</v>
+        <v>8.261063131443333e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>2.261385007300729e-05</v>
+        <v>8.3485768112184e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>2.204970024875564e-05</v>
+        <v>7.784426986966736e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>2.261385007300729e-05</v>
+        <v>8.3485768112184e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>2.261385007300729e-05</v>
+        <v>8.3485768112184e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>2.261385007300729e-05</v>
+        <v>8.3485768112184e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.889182917449825e-05</v>
+        <v>1.977484128461584e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>9.287545853527773e-05</v>
+        <v>1.044884985329109e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>9.978805890121366e-05</v>
+        <v>1.060277468786751e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>8.306507662094489e-05</v>
+        <v>9.846192567298645e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>5.948704301462155e-05</v>
+        <v>1.003257235838467e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>9.267685375427944e-05</v>
+        <v>1.047466078733775e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>9.276436743412174e-05</v>
+        <v>2.137201614508203e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>9.220021760980275e-05</v>
+        <v>9.998024642861178e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>9.277102435801834e-05</v>
+        <v>2.039043499273422e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.826262938618028e-05</v>
+        <v>1.060271776147421e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001281470660215936</v>
+        <v>1.057251079618734e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.69004842334293e-05</v>
+        <v>2.261385007300732e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>8.38231208330669e-05</v>
+        <v>2.257851165847213e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>8.385846121902866e-05</v>
+        <v>2.260577611710748e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001028634501466549</v>
+        <v>2.218521310677645e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>8.329430569685291e-05</v>
+        <v>2.218521310677645e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>8.377094556782706e-05</v>
+        <v>2.252633639323228e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>8.385845924760216e-05</v>
+        <v>2.261385007300732e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.329430942335038e-05</v>
+        <v>2.204970024875569e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>8.385845924760216e-05</v>
+        <v>2.261385007300732e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>7.363430905886556e-05</v>
+        <v>2.261385007300732e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>8.385845924760216e-05</v>
+        <v>2.261385007300732e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.652001801295642e-05</v>
+        <v>5.889182917449824e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.418020134321801e-06</v>
+        <v>9.28754585352779e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>9.866364562813635e-06</v>
+        <v>9.978805890121374e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.089760441776235e-05</v>
+        <v>8.3065076620945e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.089760441776235e-05</v>
+        <v>5.94870430146216e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>9.847035344292264e-06</v>
+        <v>9.267685375427946e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>9.727528148513288e-06</v>
+        <v>9.276436743412185e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.089760441776235e-05</v>
+        <v>9.220021760980289e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.284269620227358e-05</v>
+        <v>9.277102435801843e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.091110552719441e-05</v>
+        <v>5.826262938618035e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>9.253386596663476e-06</v>
+        <v>0.0001281470660215937</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6.690048423342945e-05</v>
+      </c>
+      <c r="C9" t="n">
+        <v>8.382312083306723e-05</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8.385846121902883e-05</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0001028634501466553</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8.32943056968531e-05</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8.377094556782729e-05</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8.385845924760234e-05</v>
+      </c>
+      <c r="I9" t="n">
+        <v>8.329430942335069e-05</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8.385845924760236e-05</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7.363430905886568e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8.385845924760234e-05</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.652001801295642e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>8.418020134321832e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.866364562813651e-06</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.089760441776237e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.089760441776237e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9.847035344292311e-06</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9.727528148513266e-06</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.089760441776237e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.284269620227358e-05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.091110552719483e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.253386596663522e-06</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1.676452021851621e-05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>8.88565252872893e-06</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.045592654977795e-05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.138021696879515e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.138021696879515e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.037140564315362e-05</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.040055628454539e-05</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.138021696879515e-05</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="B11" t="n">
+        <v>1.676452021851622e-05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>8.885652528728946e-06</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.045592654977796e-05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.138021696879518e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.138021696879518e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.037140564315364e-05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.040055628454542e-05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.138021696879518e-05</v>
+      </c>
+      <c r="J11" t="n">
         <v>1.3465646399275e-05</v>
       </c>
-      <c r="K9" t="n">
-        <v>1.127715880900615e-05</v>
-      </c>
-      <c r="L9" t="n">
-        <v>9.738100204243416e-06</v>
+      <c r="K11" t="n">
+        <v>1.127715880900664e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9.738100204243402e-06</v>
       </c>
     </row>
   </sheetData>
@@ -4799,7 +5679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4867,320 +5747,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.006194423608248024</v>
+        <v>2.919282757563718e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0009544972708599498</v>
+        <v>2.235747641915758e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001175349319702007</v>
+        <v>2.345567829375895e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0009544972708599498</v>
+        <v>2.235747641915758e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0009544972708599498</v>
+        <v>2.235747641915758e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002528567394018132</v>
+        <v>2.463134195290346e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.005056133404127899</v>
+        <v>2.718412149488521e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0009544972708599498</v>
+        <v>2.235747641915758e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001450248346737335</v>
+        <v>2.367466106415851e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002802366654982236</v>
+        <v>2.525168193974223e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001026263837836189</v>
+        <v>2.318692154720385e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.559090208655869e-05</v>
+        <v>2.239299936524504e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.333573116882373e-05</v>
+        <v>2.149659774268232e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.559090208655869e-05</v>
+        <v>2.239299936524504e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.353025544688376e-05</v>
+        <v>2.149659774268232e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.353025544688377e-05</v>
+        <v>2.149659774268232e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.544846136615299e-05</v>
+        <v>2.212629991168671e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.559090208655869e-05</v>
+        <v>2.239299936524504e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.467722758855832e-05</v>
+        <v>2.149659774268232e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.559090208655869e-05</v>
+        <v>2.239299936524504e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.559090208655869e-05</v>
+        <v>2.239299936524504e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.559090208655869e-05</v>
+        <v>2.239299936524504e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.523969511920195e-05</v>
+        <v>0.006194423608248009</v>
       </c>
       <c r="C4" t="n">
-        <v>2.16155941058478e-05</v>
+        <v>0.0009544972708599543</v>
       </c>
       <c r="D4" t="n">
-        <v>2.336986776820316e-05</v>
+        <v>0.00117534931970201</v>
       </c>
       <c r="E4" t="n">
-        <v>2.117680543101061e-05</v>
+        <v>0.0009544972708599543</v>
       </c>
       <c r="F4" t="n">
-        <v>2.386646249800768e-05</v>
+        <v>0.0009544972708599543</v>
       </c>
       <c r="G4" t="n">
-        <v>2.509725439879628e-05</v>
+        <v>0.00252856739401813</v>
       </c>
       <c r="H4" t="n">
-        <v>5.067642970303332e-05</v>
+        <v>0.005056133404127911</v>
       </c>
       <c r="I4" t="n">
-        <v>4.830968662599342e-05</v>
+        <v>0.0009544972708599543</v>
       </c>
       <c r="J4" t="n">
-        <v>2.590417281823846e-05</v>
+        <v>0.001450248346737334</v>
       </c>
       <c r="K4" t="n">
-        <v>2.661310441011126e-05</v>
+        <v>0.002802366654982239</v>
       </c>
       <c r="L4" t="n">
-        <v>2.640658967834734e-05</v>
+        <v>0.001026263837836185</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.108471258310927e-05</v>
+        <v>1.559090208655889e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.017103808510892e-05</v>
+        <v>1.333573116882372e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.107594197629018e-05</v>
+        <v>1.559090208655889e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.010987406325708e-05</v>
+        <v>1.353025544688372e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.010987406325708e-05</v>
+        <v>1.353025544688373e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.094227186270351e-05</v>
+        <v>1.544846136615294e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.108471258310927e-05</v>
+        <v>1.559090208655889e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.017103808510892e-05</v>
+        <v>1.467722758855831e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.108471258310927e-05</v>
+        <v>1.559090208655889e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.108471258310927e-05</v>
+        <v>1.559090208655889e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.108471258310927e-05</v>
+        <v>1.559090208655889e-05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.910466119877648e-05</v>
+        <v>2.523969511920197e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001386193694383864</v>
+        <v>2.161559410584771e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000150035013170685</v>
+        <v>2.336986776820318e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001248190220488583</v>
+        <v>2.117680543101061e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>8.97594230871682e-05</v>
+        <v>2.386646249800765e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001394281360928571</v>
+        <v>2.50972543987962e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001395705768132601</v>
+        <v>5.067642970303346e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001386569023152622</v>
+        <v>4.830968662599332e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001395804948099819</v>
+        <v>2.590417281823848e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>8.816723090725999e-05</v>
+        <v>2.661310441011248e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001922864455620159</v>
+        <v>2.640658967834723e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001502318306838185</v>
+        <v>4.108471258310936e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001881886422634709</v>
+        <v>4.01710380851089e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001891023290225818</v>
+        <v>4.107594197629014e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002330442912571238</v>
+        <v>4.010987406325715e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001881885791943404</v>
+        <v>4.010987406325715e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001889598760410653</v>
+        <v>4.094227186270354e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.000189102316761471</v>
+        <v>4.108471258310936e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001881886422634709</v>
+        <v>4.01710380851089e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.000189102316761471</v>
+        <v>4.108471258310936e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001665806096289137</v>
+        <v>4.108471258310936e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.000189102316761471</v>
+        <v>4.108471258310936e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.0001241207734610628</v>
+        <v>8.910466119877673e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.789016859150703e-07</v>
+        <v>0.0001386193694383863</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.854530001678229e-06</v>
+        <v>0.0001500350131706852</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.789016859150703e-07</v>
+        <v>0.0001248190220488583</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.789016859150703e-07</v>
+        <v>8.975942308716808e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.408940717584058e-05</v>
+        <v>0.0001394281360928573</v>
       </c>
       <c r="H8" t="n">
-        <v>-8.001853105691636e-05</v>
+        <v>0.0001395705768132603</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.789016859150703e-07</v>
+        <v>0.0001386569023152622</v>
       </c>
       <c r="J8" t="n">
-        <v>-8.213923240934514e-06</v>
+        <v>0.000139580494809982</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.144284925542624e-05</v>
+        <v>8.816723090726005e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.082552201313317e-06</v>
+        <v>0.0001922864455620158</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001502318306838185</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001881886422634708</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0001891023290225817</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0002330442912571235</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001881885791943403</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0001889598760410651</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001891023167614709</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001881886422634708</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001891023167614709</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001665806096289134</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001891023167614709</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.0001241207734610626</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-4.789016859151135e-07</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-3.854530001678268e-06</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-4.789016859151135e-07</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-4.789016859151135e-07</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-3.408940717584051e-05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-8.001853105691668e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-4.789016859151135e-07</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-8.213923240934553e-06</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-4.14428492554261e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.082552201313282e-06</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>-3.74714059720231e-05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.235855414738434e-05</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.151296878589581e-05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.235855414738434e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.235855414738434e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-9.469839207503294e-07</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-1.941345121338113e-05</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.235855414738434e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>9.748413739871772e-06</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-3.79383261544232e-06</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="B11" t="n">
+        <v>-3.747140597202299e-05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.23585541473843e-05</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.151296878589578e-05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.23585541473843e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.23585541473843e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-9.46983920750354e-07</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-1.94134512133812e-05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.23585541473843e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>9.748413739871791e-06</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-3.793832615442334e-06</v>
+      </c>
+      <c r="L11" t="n">
         <v>-2.360804517985084e-05</v>
       </c>
     </row>
@@ -5195,7 +6155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5263,321 +6223,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004798763319961986</v>
+        <v>2.879243402557797e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001367762792828116</v>
+        <v>2.516979675594379e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001079454390991908</v>
+        <v>2.434626297498202e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001367762792828116</v>
+        <v>2.516979675594379e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001367762792828116</v>
+        <v>2.516979675594379e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002349697532139547</v>
+        <v>2.564262534217644e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00427660902396823</v>
+        <v>2.760449421023516e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001367762792828116</v>
+        <v>2.516979675594379e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001232297110567384</v>
+        <v>2.443301412846538e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002519212619587678</v>
+        <v>2.622939902519894e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001335846319911896</v>
+        <v>2.449740717893004e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.745227404168349e-05</v>
+        <v>2.329696991367948e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.589391528115498e-05</v>
+        <v>2.371555169108946e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.745227404168346e-05</v>
+        <v>2.329696991367948e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.606890039462939e-05</v>
+        <v>2.371555169108946e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.606890039462939e-05</v>
+        <v>2.371555169108946e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.732900467438992e-05</v>
+        <v>2.312207003982469e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.745227404168346e-05</v>
+        <v>2.329696991367948e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.666111390466094e-05</v>
+        <v>2.371555169108946e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.745227404168346e-05</v>
+        <v>2.329696991367948e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.745227404168346e-05</v>
+        <v>2.329696991367948e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.745227404168346e-05</v>
+        <v>2.329696991367948e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.739174412530628e-05</v>
+        <v>0.004798763319961989</v>
       </c>
       <c r="C4" t="n">
-        <v>2.515554676654539e-05</v>
+        <v>0.001367762792828119</v>
       </c>
       <c r="D4" t="n">
-        <v>2.555484986407377e-05</v>
+        <v>0.001079454390991911</v>
       </c>
       <c r="E4" t="n">
-        <v>2.466877030787457e-05</v>
+        <v>0.001367762792828119</v>
       </c>
       <c r="F4" t="n">
-        <v>2.654480873899901e-05</v>
+        <v>0.001367762792828119</v>
       </c>
       <c r="G4" t="n">
-        <v>2.726847475801249e-05</v>
+        <v>0.002349697532139549</v>
       </c>
       <c r="H4" t="n">
-        <v>5.143002899212616e-05</v>
+        <v>0.00427660902396824</v>
       </c>
       <c r="I4" t="n">
-        <v>4.932076619916844e-05</v>
+        <v>0.001367762792828119</v>
       </c>
       <c r="J4" t="n">
-        <v>2.813525288045174e-05</v>
+        <v>0.001232297110567384</v>
       </c>
       <c r="K4" t="n">
-        <v>2.87236196898571e-05</v>
+        <v>0.002519212619587677</v>
       </c>
       <c r="L4" t="n">
-        <v>2.851042121134921e-05</v>
+        <v>0.001335846319911894</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.154134131544784e-05</v>
+        <v>1.74522740416836e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.07501811784249e-05</v>
+        <v>1.589391528115496e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.153309238102983e-05</v>
+        <v>1.745227404168358e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.073512470760109e-05</v>
+        <v>1.606890039462936e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.073512470760109e-05</v>
+        <v>1.606890039462942e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.141807194815376e-05</v>
+        <v>1.732900467438977e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.154134131544786e-05</v>
+        <v>1.745227404168358e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.07501811784249e-05</v>
+        <v>1.666111390466087e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.154134131544786e-05</v>
+        <v>1.745227404168358e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.154134131544786e-05</v>
+        <v>1.745227404168358e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.154134131544786e-05</v>
+        <v>1.745227404168358e-05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.617887070495941e-05</v>
+        <v>2.739174412530627e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001326719802360634</v>
+        <v>2.515554676654542e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001432614680352887</v>
+        <v>2.555484986407376e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001197388212617746</v>
+        <v>2.466877030787455e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>8.68823205436767e-05</v>
+        <v>2.654480873899898e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001333345919672364</v>
+        <v>2.726847475801267e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001334578613345249</v>
+        <v>5.143002899212628e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001326667011975078</v>
+        <v>4.932076619916847e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001334671530071568</v>
+        <v>2.81352528804519e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>8.530063918132693e-05</v>
+        <v>2.872361968985706e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001828447204484156</v>
+        <v>2.851042121134926e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001356672141740513</v>
+        <v>4.154134131544749e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001691406410840505</v>
+        <v>4.07501811784249e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001699318156544139</v>
+        <v>4.153309238102969e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002086811991450565</v>
+        <v>4.073512470760108e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001691405915542981</v>
+        <v>4.073512470760106e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001698085318537793</v>
+        <v>4.141807194815393e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.000169931801221073</v>
+        <v>4.154134131544748e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001691406410840505</v>
+        <v>4.07501811784249e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.000169931801221073</v>
+        <v>4.154134131544748e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001500787709892537</v>
+        <v>4.154134131544748e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.000169931801221073</v>
+        <v>4.154134131544748e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-9.606308793512144e-05</v>
+        <v>8.617887070495937e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.120156336257541e-05</v>
+        <v>0.0001326719802360634</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.85601786368015e-06</v>
+        <v>0.0001432614680352888</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.120156336257541e-05</v>
+        <v>0.0001197388212617744</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.120156336257541e-05</v>
+        <v>8.68823205436767e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.360240596678858e-05</v>
+        <v>0.0001333345919672365</v>
       </c>
       <c r="H8" t="n">
-        <v>-6.935469907145451e-05</v>
+        <v>0.0001334578613345249</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.120156336257541e-05</v>
+        <v>0.0001326667011975078</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.466500574403283e-06</v>
+        <v>0.0001334671530071567</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.226867607152795e-05</v>
+        <v>8.53006391813268e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.585959638166958e-06</v>
+        <v>0.0001828447204484157</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001356672141740513</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001691406410840505</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0001699318156544142</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0002086811991450568</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001691405915542982</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0001698085318537792</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001699318012210728</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001691406410840505</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001699318012210728</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001500787709892535</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001699318012210728</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-9.606308793512155e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-1.120156336257541e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-2.856017863680217e-06</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-1.120156336257541e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-1.120156336257541e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-3.360240596678858e-05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-6.935469907145455e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1.120156336257541e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-4.466500574403298e-06</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-4.226867607152811e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-5.585959638166937e-06</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>-2.551677267356139e-05</v>
       </c>
-      <c r="C9" t="n">
-        <v>9.282398132282922e-06</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.244657019165651e-05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>9.282398132282922e-06</v>
-      </c>
-      <c r="F9" t="n">
-        <v>9.282398132282922e-06</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-1.671920110118129e-07</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-1.45523104413507e-05</v>
-      </c>
-      <c r="I9" t="n">
-        <v>9.282398132282922e-06</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.180054657945697e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-3.603178843386647e-06</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-2.067934707199898e-05</v>
+      <c r="C11" t="n">
+        <v>9.282398132282964e-06</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.244657019165642e-05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9.282398132282964e-06</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9.282398132282964e-06</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-1.671920110117748e-07</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-1.455231044135066e-05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>9.282398132282964e-06</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.1800546579457e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-3.603178843386756e-06</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-2.067934707199903e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5591,7 +6631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5659,321 +6699,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003958922778925942</v>
+        <v>2.928124832299832e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002420548167498273</v>
+        <v>3.119394266557544e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001010667293359241</v>
+        <v>2.562998340345334e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002420548167498273</v>
+        <v>3.119394266557544e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002420548167498273</v>
+        <v>3.119394266557544e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00214936515232421</v>
+        <v>2.703917961126133e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003605045249973451</v>
+        <v>2.839078816733153e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002420548167498273</v>
+        <v>3.119394266557544e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001373248913517363</v>
+        <v>2.592116112693674e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002317845473557131</v>
+        <v>2.747453476677203e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001185982315958654</v>
+        <v>2.936266244035563e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.186872921843181e-05</v>
+        <v>2.464862819685728e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>2.191271635567948e-05</v>
+        <v>2.843088399563632e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>2.186872921843181e-05</v>
+        <v>2.464862819685728e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>2.203793145559554e-05</v>
+        <v>2.843088399563632e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.203793145559553e-05</v>
+        <v>2.843088399563632e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>2.179494914667287e-05</v>
+        <v>2.471282665782537e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>2.186872921843181e-05</v>
+        <v>2.464862819685728e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>2.139347464051572e-05</v>
+        <v>2.843088399563632e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.186872921843181e-05</v>
+        <v>2.464862819685728e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.186872921843181e-05</v>
+        <v>2.464862819685728e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.186872921843181e-05</v>
+        <v>2.464862819685728e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.372689893949763e-05</v>
+        <v>0.003958922778925932</v>
       </c>
       <c r="C4" t="n">
-        <v>3.438511640858989e-05</v>
+        <v>0.002420548167498276</v>
       </c>
       <c r="D4" t="n">
-        <v>3.175436981812786e-05</v>
+        <v>0.00101066729335924</v>
       </c>
       <c r="E4" t="n">
-        <v>3.37314356401446e-05</v>
+        <v>0.002420548167498276</v>
       </c>
       <c r="F4" t="n">
-        <v>3.392408032292909e-05</v>
+        <v>0.002420548167498276</v>
       </c>
       <c r="G4" t="n">
-        <v>5.605538090582093e-05</v>
+        <v>0.002149365152324206</v>
       </c>
       <c r="H4" t="n">
-        <v>5.737557483277999e-05</v>
+        <v>0.003605045249973451</v>
       </c>
       <c r="I4" t="n">
-        <v>3.325164436158164e-05</v>
+        <v>0.002420548167498276</v>
       </c>
       <c r="J4" t="n">
-        <v>5.638968635126292e-05</v>
+        <v>0.001373248913517364</v>
       </c>
       <c r="K4" t="n">
-        <v>3.486087266466964e-05</v>
+        <v>0.00231784547355713</v>
       </c>
       <c r="L4" t="n">
-        <v>3.486528069432253e-05</v>
+        <v>0.001185982315958658</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.653538181150119e-05</v>
+        <v>2.186872921843167e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.606012723358508e-05</v>
+        <v>2.191271635567945e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.652696503126036e-05</v>
+        <v>2.186872921843167e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.615676524360244e-05</v>
+        <v>2.203793145559547e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.615676524360244e-05</v>
+        <v>2.203793145559547e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>4.646160173974225e-05</v>
+        <v>2.17949491466728e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>4.653538181150116e-05</v>
+        <v>2.186872921843167e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>4.606012723358508e-05</v>
+        <v>2.139347464051567e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.653538181150116e-05</v>
+        <v>2.186872921843167e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.653538181150116e-05</v>
+        <v>2.186872921843167e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>4.653538181150116e-05</v>
+        <v>2.186872921843167e-05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.05521860986743e-05</v>
+        <v>3.372689893949768e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001374890219296868</v>
+        <v>3.438511640858969e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001476598878193917</v>
+        <v>3.175436981812788e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000124538769216251</v>
+        <v>3.373143564014454e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>9.163893190642626e-05</v>
+        <v>3.392408032292908e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001377781895127955</v>
+        <v>5.605538090582095e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001378519695845538</v>
+        <v>5.737557483277991e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001373767150066384</v>
+        <v>3.325164436158156e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001378612653419537</v>
+        <v>5.638968635126288e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>8.967356833719691e-05</v>
+        <v>3.486087266466972e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001872605485740243</v>
+        <v>3.486528069432257e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001350052143024039</v>
+        <v>4.653538181150133e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001674110614994613</v>
+        <v>4.606012723358513e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.000167886323947757</v>
+        <v>4.652696503126048e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002053551175414264</v>
+        <v>4.615676524360244e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001674110252361523</v>
+        <v>4.615676524360244e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001678125360056185</v>
+        <v>4.646160173974231e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001678863160773772</v>
+        <v>4.653538181150131e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001674110614994613</v>
+        <v>4.606012723358513e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001678863160773772</v>
+        <v>4.653538181150131e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001488348798851929</v>
+        <v>4.653538181150131e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001678863160773772</v>
+        <v>4.653538181150131e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-7.692330573557161e-05</v>
+        <v>9.055218609867469e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>-3.503505474845094e-05</v>
+        <v>0.0001374890219296868</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.782283342473498e-07</v>
+        <v>0.000147659887819392</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.503505474845094e-05</v>
+        <v>0.0001245387692162509</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.503505474845094e-05</v>
+        <v>9.163893190642625e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.825737936376468e-05</v>
+        <v>0.0001377781895127955</v>
       </c>
       <c r="H8" t="n">
-        <v>-5.667127404785098e-05</v>
+        <v>0.000137851969584554</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.503505474845094e-05</v>
+        <v>0.0001373767150066385</v>
       </c>
       <c r="J8" t="n">
-        <v>-6.247846772104464e-06</v>
+        <v>0.0001378612653419538</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.898366279952339e-05</v>
+        <v>8.9673568337197e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>-7.70148667635947e-05</v>
+        <v>0.0001872605485740245</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001350052143024041</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001674110614994614</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0001678863239477571</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0002053551175414265</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001674110252361523</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0001678125360056188</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001678863160773775</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001674110614994614</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001678863160773775</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.000148834879885193</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001678863160773775</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-7.692330573557161e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-3.503505474845094e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-3.782283342474388e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-3.503505474845094e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-3.503505474845094e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-2.825737936376473e-05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-5.667127404785102e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-3.503505474845094e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-6.247846772104533e-06</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-3.898366279952349e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-7.701486676359475e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>-1.693430530680444e-05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.316738283069485e-06</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.424268392594116e-05</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.316738283069485e-06</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.316738283069485e-06</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.937567065407243e-06</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="B11" t="n">
+        <v>-1.69343053068044e-05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.316738283069479e-06</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.424268392594117e-05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.316738283069479e-06</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.316738283069479e-06</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.937567065407183e-06</v>
+      </c>
+      <c r="H11" t="n">
         <v>-8.61002650516273e-06</v>
       </c>
-      <c r="I9" t="n">
-        <v>2.316738283069485e-06</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.186316655483543e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-1.478360420660658e-06</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-1.68945517489853e-05</v>
+      <c r="I11" t="n">
+        <v>2.316738283069479e-06</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.186316655483548e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-1.478360420660653e-06</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-1.689455174898528e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5987,7 +7107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6055,321 +7175,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0006056877093879701</v>
+        <v>1.391338596545953e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002407477064330082</v>
+        <v>1.438812023364612e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0004183231040152456</v>
+        <v>1.370926261993997e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002407477064330082</v>
+        <v>1.438812023364612e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002407477064330082</v>
+        <v>1.438812023364612e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0006653874257805852</v>
+        <v>1.389250639646605e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001454432271098965</v>
+        <v>1.481621508621957e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002407477064330082</v>
+        <v>1.438812023364612e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008080067291811156</v>
+        <v>1.407046915376199e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0005121877297782637</v>
+        <v>1.381720479207052e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001788191881699816</v>
+        <v>1.335175953584273e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.167070376294052e-06</v>
+        <v>1.335530365310777e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>8.096971182418911e-06</v>
+        <v>1.427257599794259e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>9.167070376294052e-06</v>
+        <v>1.335530365310777e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>8.17578300532654e-06</v>
+        <v>1.427257599794259e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>8.175783005326549e-06</v>
+        <v>1.427257599794259e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>9.064377007194035e-06</v>
+        <v>1.326870146278379e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>9.167070376294052e-06</v>
+        <v>1.335530365310777e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>8.506288680405123e-06</v>
+        <v>1.427257599794259e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>9.167070376294052e-06</v>
+        <v>1.335530365310777e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>9.167070376294052e-06</v>
+        <v>1.335530365310777e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>9.167070376294052e-06</v>
+        <v>1.335530365310777e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.675789730852742e-05</v>
+        <v>0.0006056877093879687</v>
       </c>
       <c r="C4" t="n">
-        <v>1.196376537108994e-05</v>
+        <v>0.0002407477064330082</v>
       </c>
       <c r="D4" t="n">
-        <v>2.691031765637142e-05</v>
+        <v>0.0004183231040152451</v>
       </c>
       <c r="E4" t="n">
-        <v>1.173839165488898e-05</v>
+        <v>0.0002407477064330082</v>
       </c>
       <c r="F4" t="n">
-        <v>1.265696782998461e-05</v>
+        <v>0.0002407477064330082</v>
       </c>
       <c r="G4" t="n">
-        <v>2.665520393942747e-05</v>
+        <v>0.0006653874257805862</v>
       </c>
       <c r="H4" t="n">
-        <v>1.379994318345036e-05</v>
+        <v>0.001454432271098963</v>
       </c>
       <c r="I4" t="n">
-        <v>2.60971156126385e-05</v>
+        <v>0.0002407477064330082</v>
       </c>
       <c r="J4" t="n">
-        <v>2.688878904168829e-05</v>
+        <v>0.0008080067291811163</v>
       </c>
       <c r="K4" t="n">
-        <v>1.341816816433392e-05</v>
+        <v>0.0005121877297782634</v>
       </c>
       <c r="L4" t="n">
-        <v>1.386122336083323e-05</v>
+        <v>0.001788191881699811</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.630514631111023e-05</v>
+        <v>9.167070376293986e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>2.56443646152213e-05</v>
+        <v>8.096971182418911e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>2.629643806049815e-05</v>
+        <v>9.167070376293986e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>2.564736768175908e-05</v>
+        <v>8.175783005326561e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>2.564736768175908e-05</v>
+        <v>8.175783005326561e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>2.620245294201026e-05</v>
+        <v>9.064377007194023e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>2.630514631111023e-05</v>
+        <v>9.167070376294001e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>2.56443646152213e-05</v>
+        <v>8.50628868040506e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>2.630514631111023e-05</v>
+        <v>9.167070376293987e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>2.630514631111023e-05</v>
+        <v>9.167070376293986e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>2.630514631111023e-05</v>
+        <v>9.167070376293986e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.675067592279887e-05</v>
+        <v>2.675789730852742e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001048259511993007</v>
+        <v>1.196376537108992e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001134929929893225</v>
+        <v>2.691031765637138e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>9.423321636443356e-05</v>
+        <v>1.173839165488896e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>6.732407344088187e-05</v>
+        <v>1.265696782998462e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001053625763867455</v>
+        <v>2.665520393942734e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001054652697558445</v>
+        <v>1.379994318345036e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001048044880599566</v>
+        <v>2.609711561263822e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001054728782836744</v>
+        <v>2.688878904168823e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>6.603153246628883e-05</v>
+        <v>1.341816816433391e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001459059002767319</v>
+        <v>1.386122336083321e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.640417345904202e-05</v>
+        <v>2.630514631111024e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001207948806286026</v>
+        <v>2.56443646152213e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001214556634295073</v>
+        <v>2.629643806049817e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001497037403216831</v>
+        <v>2.564736768175905e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001207948580051659</v>
+        <v>2.564736768175905e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001213529689553917</v>
+        <v>2.620245294201027e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001214556623244916</v>
+        <v>2.630514631111024e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001207948806286026</v>
+        <v>2.56443646152213e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001214556623244916</v>
+        <v>2.630514631111024e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001069407317558629</v>
+        <v>2.630514631111024e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001214556623244916</v>
+        <v>2.630514631111024e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-3.197427714137027e-07</v>
+        <v>6.675067592279886e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>9.486442805966318e-06</v>
+        <v>0.0001048259511993006</v>
       </c>
       <c r="D8" t="n">
-        <v>3.963968348671871e-06</v>
+        <v>0.0001134929929893224</v>
       </c>
       <c r="E8" t="n">
-        <v>9.486442805966318e-06</v>
+        <v>9.423321636443349e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>9.486442805966318e-06</v>
+        <v>6.732407344088188e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.709443088349331e-06</v>
+        <v>0.0001053625763867455</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.861838591977245e-05</v>
+        <v>0.0001054652697558446</v>
       </c>
       <c r="I8" t="n">
-        <v>9.486442805966318e-06</v>
+        <v>0.0001048044880599565</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.477269338977736e-06</v>
+        <v>0.0001054728782836745</v>
       </c>
       <c r="K8" t="n">
-        <v>1.70919775698691e-06</v>
+        <v>6.603153246628889e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.247555332760935e-05</v>
+        <v>0.0001459059002767318</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>9.640417345904187e-05</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001207948806286025</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0001214556634295073</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0001497037403216831</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001207948580051658</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0001213529689553916</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001214556623244914</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001207948806286025</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001214556623244914</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001069407317558628</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001214556623244914</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-3.197427714136692e-07</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9.486442805966377e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.963968348671898e-06</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9.486442805966377e-06</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9.486442805966377e-06</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-1.7094430883493e-06</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-1.861838591977242e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>9.486442805966377e-06</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-3.477269338977729e-06</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.709197756986975e-06</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-2.24755533276093e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>7.691196262515057e-06</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.221041437879542e-05</v>
-      </c>
-      <c r="D9" t="n">
-        <v>9.436175128011762e-06</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.221041437879542e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.221041437879542e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>7.077402893185948e-06</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.680844364561686e-07</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.221041437879542e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>6.41159480013575e-06</v>
-      </c>
-      <c r="K9" t="n">
-        <v>8.518189495398128e-06</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-1.305550128618804e-06</v>
+      <c r="B11" t="n">
+        <v>7.691196262515074e-06</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.221041437879546e-05</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.436175128011804e-06</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.221041437879546e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.221041437879546e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>7.077402893185977e-06</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.680844364562004e-07</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.221041437879546e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>6.411594800135782e-06</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8.518189495398172e-06</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-1.305550128618752e-06</v>
       </c>
     </row>
   </sheetData>
@@ -6383,7 +7583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6451,321 +7651,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.480254881416515e-05</v>
+        <v>1.106080726522758e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000137158005081783</v>
+        <v>1.254907796387367e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001423610220240773</v>
+        <v>1.113278380999357e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000137158005081783</v>
+        <v>1.254907796387367e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000137158005081783</v>
+        <v>1.254907796387367e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001699555984351171</v>
+        <v>1.115375899416132e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001642166508622436</v>
+        <v>1.114358987118568e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000137158005081783</v>
+        <v>1.254907796387367e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002496475261902112</v>
+        <v>1.126159308853849e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001141664179590864</v>
+        <v>1.110609991696839e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>6.828165478231911e-05</v>
+        <v>1.103928241801887e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.661044615340653e-06</v>
+        <v>1.107992277814634e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>7.009158382974487e-06</v>
+        <v>1.252306385906979e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>7.661044615340653e-06</v>
+        <v>1.107992277814634e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>7.058895386165307e-06</v>
+        <v>1.252306385906979e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>7.058895386165323e-06</v>
+        <v>1.252306385906979e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>7.572989604558701e-06</v>
+        <v>1.106268254619169e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>7.661044615340653e-06</v>
+        <v>1.107992277814634e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>7.093505962847452e-06</v>
+        <v>1.252306385906979e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>7.661044615340653e-06</v>
+        <v>1.107992277814634e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.661044615340653e-06</v>
+        <v>1.107992277814634e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>7.661044615340653e-06</v>
+        <v>1.107992277814634e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.012651801282918e-05</v>
+        <v>7.480254881416525e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>9.669266837254812e-06</v>
+        <v>0.0001371580050817829</v>
       </c>
       <c r="D4" t="n">
-        <v>1.03604240684082e-05</v>
+        <v>0.0001423610220240772</v>
       </c>
       <c r="E4" t="n">
-        <v>9.51026858512517e-06</v>
+        <v>0.0001371580050817829</v>
       </c>
       <c r="F4" t="n">
-        <v>9.789672149331462e-06</v>
+        <v>0.0001371580050817829</v>
       </c>
       <c r="G4" t="n">
-        <v>2.003846300204719e-05</v>
+        <v>0.0001699555984351159</v>
       </c>
       <c r="H4" t="n">
-        <v>2.069193157887842e-05</v>
+        <v>0.0001642166508622437</v>
       </c>
       <c r="I4" t="n">
-        <v>1.955897936033594e-05</v>
+        <v>0.0001371580050817829</v>
       </c>
       <c r="J4" t="n">
-        <v>1.065202638829645e-05</v>
+        <v>0.0002496475261902104</v>
       </c>
       <c r="K4" t="n">
-        <v>1.030974712624936e-05</v>
+        <v>0.0001141664179590865</v>
       </c>
       <c r="L4" t="n">
-        <v>1.035863180247005e-05</v>
+        <v>6.828165478231907e-05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.148054516808568e-05</v>
+        <v>7.661044615340712e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>2.09130065155925e-05</v>
+        <v>7.009158382974481e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>2.147244654831118e-05</v>
+        <v>7.661044615340712e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>2.093090459511335e-05</v>
+        <v>7.058895386165298e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>2.093090459511335e-05</v>
+        <v>7.058895386165299e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>2.139249015730375e-05</v>
+        <v>7.572989604558751e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>2.148054516808568e-05</v>
+        <v>7.661044615340712e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>2.09130065155925e-05</v>
+        <v>7.09350596284744e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>2.148054516808568e-05</v>
+        <v>7.661044615340712e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>2.148054516808568e-05</v>
+        <v>7.661044615340712e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>2.148054516808568e-05</v>
+        <v>7.661044615340712e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.712661590851929e-05</v>
+        <v>2.012651801282914e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>8.963094714202175e-05</v>
+        <v>9.669266837254751e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>9.701530984760781e-05</v>
+        <v>1.036042406840823e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>8.058954478147115e-05</v>
+        <v>9.510268585125154e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>5.762184043205788e-05</v>
+        <v>9.78967214933143e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>9.007660182722974e-05</v>
+        <v>2.003846300204714e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>9.016465683801222e-05</v>
+        <v>2.069193157887841e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>8.959711818551852e-05</v>
+        <v>1.955897936033587e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>9.017114976035851e-05</v>
+        <v>1.065202638829645e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.651291733652937e-05</v>
+        <v>1.030974712624937e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001246756531853627</v>
+        <v>1.035863180247004e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.226311886891971e-05</v>
+        <v>2.148054516808571e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>9.026157801865109e-05</v>
+        <v>2.091300651559249e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>9.082912044637223e-05</v>
+        <v>2.14724465483112e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001116863450272444</v>
+        <v>2.09309045951133e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>9.02615746544492e-05</v>
+        <v>2.09309045951133e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>9.074106166036246e-05</v>
+        <v>2.139249015730378e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>9.082911667114434e-05</v>
+        <v>2.148054516808571e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>9.026157801865109e-05</v>
+        <v>2.091300651559249e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>9.082911667114434e-05</v>
+        <v>2.148054516808571e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>8.007190621811493e-05</v>
+        <v>2.148054516808571e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>9.082911667114434e-05</v>
+        <v>2.148054516808571e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.000234094472941e-05</v>
+        <v>5.712661590851929e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.00056689810156e-05</v>
+        <v>8.963094714202184e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>8.495165314728324e-06</v>
+        <v>9.70153098476079e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.00056689810156e-05</v>
+        <v>8.058954478147121e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.00056689810156e-05</v>
+        <v>5.762184043205785e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.692404080009298e-06</v>
+        <v>9.007660182722981e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.321869643322192e-06</v>
+        <v>9.016465683801218e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.00056689810156e-05</v>
+        <v>8.959711818551842e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>5.836114528818363e-06</v>
+        <v>9.017114976035851e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>9.055294967628933e-06</v>
+        <v>5.651291733652937e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>1.046382220098201e-05</v>
+        <v>0.0001246756531853627</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7.226311886891967e-05</v>
+      </c>
+      <c r="C9" t="n">
+        <v>9.026157801865086e-05</v>
+      </c>
+      <c r="D9" t="n">
+        <v>9.082912044637211e-05</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0001116863450272441</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9.026157465444902e-05</v>
+      </c>
+      <c r="G9" t="n">
+        <v>9.074106166036233e-05</v>
+      </c>
+      <c r="H9" t="n">
+        <v>9.08291166711443e-05</v>
+      </c>
+      <c r="I9" t="n">
+        <v>9.026157801865086e-05</v>
+      </c>
+      <c r="J9" t="n">
+        <v>9.08291166711443e-05</v>
+      </c>
+      <c r="K9" t="n">
+        <v>8.007190621811479e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9.08291166711443e-05</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.000234094472946e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.00056689810156e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>8.495165314728365e-06</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.00056689810156e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.00056689810156e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>7.692404080009332e-06</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8.321869643322249e-06</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.00056689810156e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5.836114528818413e-06</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9.055294967628963e-06</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.046382220098205e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1.057050409697331e-05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.140365527189755e-05</v>
-      </c>
-      <c r="D9" t="n">
-        <v>9.956710927005056e-06</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.140365527189755e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.140365527189755e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>9.620271551608147e-06</v>
-      </c>
-      <c r="H9" t="n">
-        <v>9.888666905446848e-06</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.140365527189755e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>8.875643624068869e-06</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.018488781107696e-05</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.075895469201307e-05</v>
+      <c r="B11" t="n">
+        <v>1.057050409697332e-05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.140365527189753e-05</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.956710927005078e-06</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.140365527189753e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.140365527189753e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9.620271551608161e-06</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9.888666905446878e-06</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.140365527189753e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8.875643624068911e-06</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.018488781107698e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.075895469201308e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6779,7 +8059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6847,321 +8127,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.997170021913438e-05</v>
+        <v>1.103012481099332e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001790933508991232</v>
+        <v>1.27140055073754e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>9.129510400319976e-05</v>
+        <v>1.102297559469921e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001790933508991232</v>
+        <v>1.27140055073754e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001790933508991232</v>
+        <v>1.27140055073754e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001445241779878957</v>
+        <v>1.10873189513296e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001579335231640556</v>
+        <v>1.109192936202829e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001790933508991232</v>
+        <v>1.27140055073754e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001100678600251331</v>
+        <v>1.104807193566165e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>9.239215959291064e-05</v>
+        <v>1.102859895341898e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001323052397383749</v>
+        <v>1.106762125533189e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.85917017385138e-06</v>
+        <v>1.103081193030928e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>7.281813580110724e-06</v>
+        <v>1.263419449864409e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>7.85917017385138e-06</v>
+        <v>1.103081193030928e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>7.332353398679767e-06</v>
+        <v>1.263419449864409e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>7.332353398679769e-06</v>
+        <v>1.263419449864409e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>7.773819652881697e-06</v>
+        <v>1.102681724883041e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>7.85917017385138e-06</v>
+        <v>1.103081193030928e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>7.308895517925488e-06</v>
+        <v>1.263419449864409e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>7.85917017385138e-06</v>
+        <v>1.103081193030928e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.85917017385138e-06</v>
+        <v>1.103081193030928e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>7.85917017385138e-06</v>
+        <v>1.103081193030928e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.051132828344738e-05</v>
+        <v>8.997170021913427e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>9.985471685011823e-06</v>
+        <v>0.0001790933508991234</v>
       </c>
       <c r="D4" t="n">
-        <v>1.044402543999657e-05</v>
+        <v>9.129510400319954e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>9.825699142338368e-06</v>
+        <v>0.0001790933508991234</v>
       </c>
       <c r="F4" t="n">
-        <v>1.00091717684849e-05</v>
+        <v>0.0001790933508991234</v>
       </c>
       <c r="G4" t="n">
-        <v>1.042597776247772e-05</v>
+        <v>0.0001445241779878974</v>
       </c>
       <c r="H4" t="n">
-        <v>2.093061471619384e-05</v>
+        <v>0.0001579335231640556</v>
       </c>
       <c r="I4" t="n">
-        <v>9.961053627521528e-06</v>
+        <v>0.0001790933508991234</v>
       </c>
       <c r="J4" t="n">
-        <v>1.077726316669546e-05</v>
+        <v>0.0001100678600251333</v>
       </c>
       <c r="K4" t="n">
-        <v>1.04502702261135e-05</v>
+        <v>9.239215959291086e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.057768241866412e-05</v>
+        <v>0.0001323052397383749</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.159430334231226e-05</v>
+        <v>7.859170173851317e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>2.104402868638631e-05</v>
+        <v>7.281813580110705e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>2.158620141350617e-05</v>
+        <v>7.859170173851319e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>2.106569746051026e-05</v>
+        <v>7.332353398679738e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>2.106569746051026e-05</v>
+        <v>7.332353398679735e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>2.150895282134251e-05</v>
+        <v>7.773819652881624e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>2.159430334231226e-05</v>
+        <v>7.859170173851319e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>2.104402868638631e-05</v>
+        <v>7.308895517925457e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>2.159430334231226e-05</v>
+        <v>7.859170173851319e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>2.159430334231226e-05</v>
+        <v>7.859170173851319e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>2.159430334231226e-05</v>
+        <v>7.859170173851319e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.706268176195731e-05</v>
+        <v>1.051132828344738e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>8.943624908614931e-05</v>
+        <v>9.985471685011806e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>9.676832954575153e-05</v>
+        <v>1.044402543999654e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>8.043592855681511e-05</v>
+        <v>9.825699142338332e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>5.757261588638867e-05</v>
+        <v>1.000917176848487e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>8.986376313613607e-05</v>
+        <v>1.042597776247768e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>8.994911365711057e-05</v>
+        <v>2.093061471619378e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>8.93988390011798e-05</v>
+        <v>9.961053627521516e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>8.99555767834851e-05</v>
+        <v>1.077726316669535e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.645179940565221e-05</v>
+        <v>1.045027022611338e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001243017416903324</v>
+        <v>1.05776824186641e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.850683217484016e-05</v>
+        <v>2.159430334231212e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>8.54354295743901e-05</v>
+        <v>2.104402868638631e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>8.598570653867664e-05</v>
+        <v>2.158620141350608e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000105605675565525</v>
+        <v>2.106569746051023e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>8.543542650580204e-05</v>
+        <v>2.106569746051023e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>8.590035370934628e-05</v>
+        <v>2.15089528213425e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>8.598570423031603e-05</v>
+        <v>2.159430334231212e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.54354295743901e-05</v>
+        <v>2.104402868638631e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>8.598570423031603e-05</v>
+        <v>2.159430334231212e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>7.544749957943859e-05</v>
+        <v>2.159430334231212e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>8.598570423031603e-05</v>
+        <v>2.159430334231212e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.583237595257177e-06</v>
+        <v>5.706268176195724e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>8.968055095708011e-06</v>
+        <v>8.94362490861494e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>9.733834903348742e-06</v>
+        <v>9.676832954575138e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>8.968055095708011e-06</v>
+        <v>8.043592855681522e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>8.968055095708011e-06</v>
+        <v>5.757261588638865e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>8.310415039525202e-06</v>
+        <v>8.986376313613597e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.341134065620635e-06</v>
+        <v>8.994911365711024e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>8.968055095708011e-06</v>
+        <v>8.939883900117997e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>9.221871709309098e-06</v>
+        <v>8.995557678348508e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>9.616838159804918e-06</v>
+        <v>5.645179940565217e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>5.530067441315109e-06</v>
+        <v>0.0001243017416903322</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6.850683217484018e-05</v>
+      </c>
+      <c r="C9" t="n">
+        <v>8.543542957439014e-05</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8.59857065386767e-05</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0001056056755655251</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8.543542650580218e-05</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8.590035370934629e-05</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8.598570423031603e-05</v>
+      </c>
+      <c r="I9" t="n">
+        <v>8.543542957439014e-05</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8.5985704230316e-05</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7.544749957943855e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8.5985704230316e-05</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9.583237595257145e-06</v>
+      </c>
+      <c r="C10" t="n">
+        <v>8.96805509570802e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.733834903348706e-06</v>
+      </c>
+      <c r="E10" t="n">
+        <v>8.96805509570802e-06</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8.96805509570802e-06</v>
+      </c>
+      <c r="G10" t="n">
+        <v>8.310415039525182e-06</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8.341134065620601e-06</v>
+      </c>
+      <c r="I10" t="n">
+        <v>8.96805509570802e-06</v>
+      </c>
+      <c r="J10" t="n">
+        <v>9.221871709309069e-06</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9.616838159804907e-06</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.530067441315091e-06</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1.037147387539896e-05</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>1.037147387539893e-05</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.10459003957464e-05</v>
       </c>
-      <c r="D9" t="n">
-        <v>1.043284691421163e-05</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>1.04328469142116e-05</v>
+      </c>
+      <c r="E11" t="n">
         <v>1.10459003957464e-05</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>1.10459003957464e-05</v>
       </c>
-      <c r="G9" t="n">
-        <v>9.851347289435532e-06</v>
-      </c>
-      <c r="H9" t="n">
-        <v>9.868117362100203e-06</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>9.851347289435514e-06</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9.868117362100154e-06</v>
+      </c>
+      <c r="I11" t="n">
         <v>1.10459003957464e-05</v>
       </c>
-      <c r="J9" t="n">
-        <v>1.022499837035616e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.038523638177249e-05</v>
-      </c>
-      <c r="L9" t="n">
-        <v>8.724841888205833e-06</v>
+      <c r="J11" t="n">
+        <v>1.022499837035611e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.038523638177246e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>8.724841888205793e-06</v>
       </c>
     </row>
   </sheetData>
@@ -7175,7 +8535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7243,321 +8603,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003260648478018179</v>
+        <v>2.289816443041012e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000695897873735311</v>
+        <v>1.954354753020175e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001071225790579775</v>
+        <v>2.039935083220878e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000695897873735311</v>
+        <v>1.954354753020175e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000695897873735311</v>
+        <v>1.954354753020175e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002004128555050526</v>
+        <v>2.117218644581152e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004415548160127147</v>
+        <v>2.394717775111188e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000695897873735311</v>
+        <v>1.954354753020175e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001308060791377402</v>
+        <v>2.054071763413843e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001858217122870226</v>
+        <v>2.127447807886643e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004294201613404338</v>
+        <v>2.393500556487388e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.349728075125433e-05</v>
+        <v>1.937015080599897e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.149815865097791e-05</v>
+        <v>1.895017111176345e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.349728075125432e-05</v>
+        <v>1.937015080599897e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.166093478368386e-05</v>
+        <v>1.895017111176345e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.166093478368381e-05</v>
+        <v>1.895017111176345e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.336239861793561e-05</v>
+        <v>1.913613943377322e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.349728075125433e-05</v>
+        <v>1.937015080599897e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.263157778304369e-05</v>
+        <v>1.895017111176345e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.349728075125432e-05</v>
+        <v>1.937015080599897e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.349728075125432e-05</v>
+        <v>1.937015080599897e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.349728075125432e-05</v>
+        <v>1.937015080599897e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.159510140242312e-05</v>
+        <v>0.003260648478018176</v>
       </c>
       <c r="C4" t="n">
-        <v>1.845565206804008e-05</v>
+        <v>0.0006958978737353086</v>
       </c>
       <c r="D4" t="n">
-        <v>2.052540887716883e-05</v>
+        <v>0.001071225790579777</v>
       </c>
       <c r="E4" t="n">
-        <v>1.808319347409865e-05</v>
+        <v>0.0006958978737353086</v>
       </c>
       <c r="F4" t="n">
-        <v>2.037737063347694e-05</v>
+        <v>0.0006958978737353086</v>
       </c>
       <c r="G4" t="n">
-        <v>4.254362408354519e-05</v>
+        <v>0.002004128555050529</v>
       </c>
       <c r="H4" t="n">
-        <v>4.430360942117252e-05</v>
+        <v>0.004415548160127148</v>
       </c>
       <c r="I4" t="n">
-        <v>4.18128032486533e-05</v>
+        <v>0.0006958978737353086</v>
       </c>
       <c r="J4" t="n">
-        <v>4.310005306790734e-05</v>
+        <v>0.001308060791377401</v>
       </c>
       <c r="K4" t="n">
-        <v>2.208672100919151e-05</v>
+        <v>0.001858217122870229</v>
       </c>
       <c r="L4" t="n">
-        <v>2.269675685280432e-05</v>
+        <v>0.0004294201613404459</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.622871804164963e-05</v>
+        <v>1.349728075125434e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>3.536301507343894e-05</v>
+        <v>1.149815865097786e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>3.621997039729022e-05</v>
+        <v>1.349728075125434e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>3.53239844417929e-05</v>
+        <v>1.16609347836839e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>3.53239844417929e-05</v>
+        <v>1.166093478368391e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>3.60938359083307e-05</v>
+        <v>1.336239861793561e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>3.622871804164963e-05</v>
+        <v>1.349728075125434e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.536301507343894e-05</v>
+        <v>1.263157778304363e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>3.622871804164963e-05</v>
+        <v>1.349728075125434e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>3.622871804164963e-05</v>
+        <v>1.349728075125434e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>3.622871804164963e-05</v>
+        <v>1.349728075125434e-05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.184532858545329e-05</v>
+        <v>2.159510140242313e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001276246494951749</v>
+        <v>1.845565206803998e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001381831916986584</v>
+        <v>2.052540887716883e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000114862428718025</v>
+        <v>1.808319347409856e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>8.24406787739104e-05</v>
+        <v>2.037737063347688e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001283726066687752</v>
+        <v>4.254362408354513e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001285074888021004</v>
+        <v>4.430360942117256e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001276417858338827</v>
+        <v>4.181280324865316e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.000128516659252523</v>
+        <v>4.310005306790719e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>8.097855500325635e-05</v>
+        <v>2.208672100919097e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001772500169735356</v>
+        <v>2.269675685280438e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001351155692758178</v>
+        <v>3.622871804164965e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001692918919730505</v>
+        <v>3.536301507343892e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001701575960011178</v>
+        <v>3.621997039729032e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002097295705020988</v>
+        <v>3.532398444179298e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001692918303441669</v>
+        <v>3.532398444179298e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001700227128079413</v>
+        <v>3.609383590833091e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001701575949412628</v>
+        <v>3.622871804164965e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001692918919730505</v>
+        <v>3.536301507343892e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001701575949412628</v>
+        <v>3.622871804164965e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001498541080958583</v>
+        <v>3.622871804164965e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001701575949412628</v>
+        <v>3.622871804164965e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-5.784268538408771e-05</v>
+        <v>8.184532858545343e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>3.170933983038281e-06</v>
+        <v>0.0001276246494951752</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.453295310756729e-06</v>
+        <v>0.0001381831916986591</v>
       </c>
       <c r="E8" t="n">
-        <v>3.170933983038281e-06</v>
+        <v>0.000114862428718025</v>
       </c>
       <c r="F8" t="n">
-        <v>3.170933983038281e-06</v>
+        <v>8.244067877391052e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.657814408780577e-05</v>
+        <v>0.0001283726066687751</v>
       </c>
       <c r="H8" t="n">
-        <v>-7.793051511974869e-05</v>
+        <v>0.0001285074888021007</v>
       </c>
       <c r="I8" t="n">
-        <v>3.170933983038281e-06</v>
+        <v>0.0001276417858338831</v>
       </c>
       <c r="J8" t="n">
-        <v>-8.20927316312478e-06</v>
+        <v>0.0001285166592525227</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.376205870275958e-05</v>
+        <v>8.097855500325647e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>-7.802789830342124e-05</v>
+        <v>0.0001772500169735362</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001351155692758184</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001692918919730495</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0001701575960011182</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0002097295705020995</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001692918303441684</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0001700227128079411</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001701575949412601</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001692918919730495</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001701575949412601</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001498541080958586</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001701575949412601</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-5.78426853840879e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.170933983038353e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-5.453295310756788e-06</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.170933983038353e-06</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.170933983038353e-06</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-2.657814408780586e-05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-7.793051511974881e-05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.170933983038353e-06</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-8.20927316312479e-06</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-2.376205870275964e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-7.802789830342149e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>-1.223392209878844e-05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.236394435118674e-05</v>
-      </c>
-      <c r="D9" t="n">
-        <v>9.104603741455904e-06</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.236394435118674e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.236394435118674e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3.720417607153709e-07</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-2.032493532392751e-05</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.236394435118674e-05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>7.991991837777814e-06</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.649185298185261e-06</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.59313856219942e-05</v>
+      <c r="B11" t="n">
+        <v>-1.223392209878845e-05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.236394435118673e-05</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.104603741455954e-06</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.236394435118673e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.236394435118673e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.720417607153404e-07</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-2.032493532392745e-05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.236394435118673e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7.991991837777823e-06</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.649185298185217e-06</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.593138562199414e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7571,7 +9011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7639,321 +9079,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.118346846942058e-05</v>
+        <v>1.396751936559648e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001475172459251992</v>
+        <v>1.450664142094265e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007200285803588787</v>
+        <v>1.47983503999825e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001475172459251992</v>
+        <v>1.450664142094265e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001475172459251992</v>
+        <v>1.450664142094265e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0009309615243772281</v>
+        <v>1.486449370046156e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0006026361400259362</v>
+        <v>1.457824196121726e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001475172459251992</v>
+        <v>1.450664142094265e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0003540400575296459</v>
+        <v>1.42852639215232e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002443275290516773</v>
+        <v>1.418316661160877e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002867978356284166</v>
+        <v>1.410256271115603e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.364979948887113e-06</v>
+        <v>1.402101098544564e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>7.883621542086889e-06</v>
+        <v>1.449034818454776e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>9.364979948887113e-06</v>
+        <v>1.402101098544564e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>7.989807464667249e-06</v>
+        <v>1.449034818454776e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>7.989807464667245e-06</v>
+        <v>1.449034818454776e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>9.247279459614131e-06</v>
+        <v>1.385953510635373e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>9.364979948887113e-06</v>
+        <v>1.402101098544564e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>8.608724799874115e-06</v>
+        <v>1.449034818454776e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>9.364979948887113e-06</v>
+        <v>1.402101098544564e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>9.364979948887113e-06</v>
+        <v>1.402101098544564e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>9.364979948887113e-06</v>
+        <v>1.402101098544564e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.795428521077512e-05</v>
+        <v>7.118346846942064e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.135176573208343e-05</v>
+        <v>0.0001475172459251992</v>
       </c>
       <c r="D4" t="n">
-        <v>1.366751387415522e-05</v>
+        <v>0.0007200285803588777</v>
       </c>
       <c r="E4" t="n">
-        <v>1.115677026604989e-05</v>
+        <v>0.0001475172459251992</v>
       </c>
       <c r="F4" t="n">
-        <v>1.250016399041011e-05</v>
+        <v>0.0001475172459251992</v>
       </c>
       <c r="G4" t="n">
-        <v>2.783658472150215e-05</v>
+        <v>0.0009309615243772284</v>
       </c>
       <c r="H4" t="n">
-        <v>2.876178297160509e-05</v>
+        <v>0.000602636140025937</v>
       </c>
       <c r="I4" t="n">
-        <v>2.719803006176216e-05</v>
+        <v>0.0001475172459251992</v>
       </c>
       <c r="J4" t="n">
-        <v>1.382621913695217e-05</v>
+        <v>0.0003540400575296459</v>
       </c>
       <c r="K4" t="n">
-        <v>1.258879756569562e-05</v>
+        <v>0.0002443275290516773</v>
       </c>
       <c r="L4" t="n">
-        <v>1.421807797211514e-05</v>
+        <v>0.002867978356284158</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.637826972865687e-05</v>
+        <v>9.364979948887109e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>2.562201457964392e-05</v>
+        <v>7.883621542086947e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>2.637016801965546e-05</v>
+        <v>9.364979948887109e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>2.560824172149302e-05</v>
+        <v>7.989807464667242e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>2.560824172149302e-05</v>
+        <v>7.989807464667266e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>2.626056923938388e-05</v>
+        <v>9.247279459614129e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>2.637826972865687e-05</v>
+        <v>9.364979948887109e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>2.562201457964392e-05</v>
+        <v>8.608724799874125e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>2.637826972865687e-05</v>
+        <v>9.364979948887109e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>2.637826972865687e-05</v>
+        <v>9.364979948887109e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>2.637826972865687e-05</v>
+        <v>9.364979948887109e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.528739750160773e-05</v>
+        <v>2.795428521077512e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001023427843184463</v>
+        <v>1.135176573208339e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001109341231467676</v>
+        <v>1.366751387415521e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>9.200019074956145e-05</v>
+        <v>1.11567702660499e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>6.572618795511299e-05</v>
+        <v>1.250016399041013e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001029768609286813</v>
+        <v>2.783658472150218e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.000103094561417947</v>
+        <v>2.876178297160523e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001023383062689414</v>
+        <v>2.719803006176217e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001031019916087445</v>
+        <v>1.382621913695219e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>6.458511002175857e-05</v>
+        <v>1.258879756569567e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001425873055118507</v>
+        <v>1.421807797211509e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.090457832905031e-05</v>
+        <v>2.637826972865686e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001136885638832049</v>
+        <v>2.562201457964392e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001144448423231215</v>
+        <v>2.637016801965544e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000140853510288128</v>
+        <v>2.56082417214931e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001136885532532981</v>
+        <v>2.56082417214931e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001143271185429447</v>
+        <v>2.626056923938394e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001144448190322178</v>
+        <v>2.637826972865686e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001136885638832049</v>
+        <v>2.562201457964392e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001144448190322178</v>
+        <v>2.637826972865686e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00010080552091524</v>
+        <v>2.637826972865686e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001144448190322178</v>
+        <v>2.637826972865686e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.309353056322615e-05</v>
+        <v>6.528739750160798e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.178248953820095e-05</v>
+        <v>0.0001023427843184467</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.310603159872597e-06</v>
+        <v>0.000110934123146768</v>
       </c>
       <c r="E8" t="n">
-        <v>1.178248953820095e-05</v>
+        <v>9.200019074956184e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.178248953820095e-05</v>
+        <v>6.572618795511331e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>-9.138940794872163e-06</v>
+        <v>0.0001029768609286817</v>
       </c>
       <c r="H8" t="n">
-        <v>5.563139019857371e-07</v>
+        <v>0.0001030945614179475</v>
       </c>
       <c r="I8" t="n">
-        <v>1.178248953820095e-05</v>
+        <v>0.0001023383062689418</v>
       </c>
       <c r="J8" t="n">
-        <v>6.494101643935426e-06</v>
+        <v>0.0001031019916087449</v>
       </c>
       <c r="K8" t="n">
-        <v>8.579614817102157e-06</v>
+        <v>6.458511002175883e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.738903654398923e-05</v>
+        <v>0.0001425873055118514</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>9.090457832905019e-05</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0001136885638832047</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0001144448423231213</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0001408535102881278</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001136885532532978</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0001143271185429447</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0001144448190322176</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001136885638832047</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0001144448190322176</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001008055209152401</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001144448190322176</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.309353056322615e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.178248953820096e-05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-4.310603159872561e-06</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.178248953820096e-05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.178248953820096e-05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-9.138940794872043e-06</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.563139019857494e-07</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.178248953820096e-05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6.494101643935409e-06</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8.579614817102196e-06</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-4.738903654398911e-05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1.354551281778185e-05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.327455710742135e-05</v>
-      </c>
-      <c r="D9" t="n">
-        <v>6.45740754447466e-06</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.327455710742135e-05</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.327455710742135e-05</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.400113873609799e-06</v>
-      </c>
-      <c r="H9" t="n">
-        <v>8.451761878799382e-06</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.327455710742135e-05</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="B11" t="n">
+        <v>1.354551281778188e-05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.327455710742137e-05</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.457407544474696e-06</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.327455710742137e-05</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.327455710742137e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.400113873609806e-06</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8.451761878799389e-06</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.327455710742137e-05</v>
+      </c>
+      <c r="J11" t="n">
         <v>1.08604961842992e-05</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K11" t="n">
         <v>1.170731401431179e-05</v>
       </c>
-      <c r="L9" t="n">
-        <v>-1.104210132563642e-05</v>
+      <c r="L11" t="n">
+        <v>-1.10421013256364e-05</v>
       </c>
     </row>
   </sheetData>
